--- a/Bell_Nozzle_Divergent_Profile.xlsx
+++ b/Bell_Nozzle_Divergent_Profile.xlsx
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.459888</v>
+        <v>14.444748</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.013051</v>
+        <v>0.029183</v>
       </c>
       <c r="B3" t="n">
-        <v>6.459922</v>
+        <v>14.444825</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.026102</v>
+        <v>0.058366</v>
       </c>
       <c r="B4" t="n">
-        <v>6.460026</v>
+        <v>14.445056</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.039152</v>
+        <v>0.087547</v>
       </c>
       <c r="B5" t="n">
-        <v>6.460198</v>
+        <v>14.445442</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.052201</v>
+        <v>0.116725</v>
       </c>
       <c r="B6" t="n">
-        <v>6.46044</v>
+        <v>14.445983</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.065249</v>
+        <v>0.1459</v>
       </c>
       <c r="B7" t="n">
-        <v>6.46075</v>
+        <v>14.446677</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.078294</v>
+        <v>0.175071</v>
       </c>
       <c r="B8" t="n">
-        <v>6.46113</v>
+        <v>14.447526</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.091338</v>
+        <v>0.204238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.461579</v>
+        <v>14.448529</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.104379</v>
+        <v>0.233398</v>
       </c>
       <c r="B10" t="n">
-        <v>6.462096</v>
+        <v>14.449686</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.117417</v>
+        <v>0.262552</v>
       </c>
       <c r="B11" t="n">
-        <v>6.462683</v>
+        <v>14.450998</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.130452</v>
+        <v>0.291699</v>
       </c>
       <c r="B12" t="n">
-        <v>6.463338</v>
+        <v>14.452463</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.143483</v>
+        <v>0.320837</v>
       </c>
       <c r="B13" t="n">
-        <v>6.464063</v>
+        <v>14.454083</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.15651</v>
+        <v>0.349966</v>
       </c>
       <c r="B14" t="n">
-        <v>6.464856</v>
+        <v>14.455857</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.169532</v>
+        <v>0.379086</v>
       </c>
       <c r="B15" t="n">
-        <v>6.465718</v>
+        <v>14.457785</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.18255</v>
+        <v>0.408195</v>
       </c>
       <c r="B16" t="n">
-        <v>6.466649</v>
+        <v>14.459867</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.195563</v>
+        <v>0.437293</v>
       </c>
       <c r="B17" t="n">
-        <v>6.467649</v>
+        <v>14.462103</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.208571</v>
+        <v>0.466378</v>
       </c>
       <c r="B18" t="n">
-        <v>6.468718</v>
+        <v>14.464493</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.221572</v>
+        <v>0.495451</v>
       </c>
       <c r="B19" t="n">
-        <v>6.469855</v>
+        <v>14.467036</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.234568</v>
+        <v>0.524509</v>
       </c>
       <c r="B20" t="n">
-        <v>6.471061</v>
+        <v>14.469733</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.247556</v>
+        <v>0.553553</v>
       </c>
       <c r="B21" t="n">
-        <v>6.472336</v>
+        <v>14.472584</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.260538</v>
+        <v>0.582581</v>
       </c>
       <c r="B22" t="n">
-        <v>6.47368</v>
+        <v>14.475589</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.273513</v>
+        <v>0.6115930000000001</v>
       </c>
       <c r="B23" t="n">
-        <v>6.475092</v>
+        <v>14.478746</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.28648</v>
+        <v>0.640588</v>
       </c>
       <c r="B24" t="n">
-        <v>6.476573</v>
+        <v>14.482058</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.299439</v>
+        <v>0.669565</v>
       </c>
       <c r="B25" t="n">
-        <v>6.478123</v>
+        <v>14.485522</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.312389</v>
+        <v>0.698524</v>
       </c>
       <c r="B26" t="n">
-        <v>6.479741</v>
+        <v>14.48914</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.325331</v>
+        <v>0.7274620000000001</v>
       </c>
       <c r="B27" t="n">
-        <v>6.481427</v>
+        <v>14.492911</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.338264</v>
+        <v>0.756381</v>
       </c>
       <c r="B28" t="n">
-        <v>6.483182</v>
+        <v>14.496835</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.351187</v>
+        <v>0.785278</v>
       </c>
       <c r="B29" t="n">
-        <v>6.485005</v>
+        <v>14.500912</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.3641</v>
+        <v>0.814153</v>
       </c>
       <c r="B30" t="n">
-        <v>6.486897</v>
+        <v>14.505142</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.377004</v>
+        <v>0.843006</v>
       </c>
       <c r="B31" t="n">
-        <v>6.488856</v>
+        <v>14.509524</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.389896</v>
+        <v>0.871835</v>
       </c>
       <c r="B32" t="n">
-        <v>6.490884</v>
+        <v>14.514059</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.402778</v>
+        <v>0.900639</v>
       </c>
       <c r="B33" t="n">
-        <v>6.492981</v>
+        <v>14.518746</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.415649</v>
+        <v>0.929419</v>
       </c>
       <c r="B34" t="n">
-        <v>6.495145</v>
+        <v>14.523585</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.428508</v>
+        <v>0.958172</v>
       </c>
       <c r="B35" t="n">
-        <v>6.497377</v>
+        <v>14.528577</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.441355</v>
+        <v>0.986899</v>
       </c>
       <c r="B36" t="n">
-        <v>6.499677</v>
+        <v>14.533721</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.454189</v>
+        <v>1.015598</v>
       </c>
       <c r="B37" t="n">
-        <v>6.502046</v>
+        <v>14.539016</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.467011</v>
+        <v>1.044268</v>
       </c>
       <c r="B38" t="n">
-        <v>6.504482</v>
+        <v>14.544463</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.47982</v>
+        <v>1.07291</v>
       </c>
       <c r="B39" t="n">
-        <v>6.506986</v>
+        <v>14.550062</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.492615</v>
+        <v>1.101521</v>
       </c>
       <c r="B40" t="n">
-        <v>6.509557</v>
+        <v>14.555812</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.505397</v>
+        <v>1.130101</v>
       </c>
       <c r="B41" t="n">
-        <v>6.512196</v>
+        <v>14.561714</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.518164</v>
+        <v>1.15865</v>
       </c>
       <c r="B42" t="n">
-        <v>6.514903</v>
+        <v>14.567766</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.530917</v>
+        <v>1.187167</v>
       </c>
       <c r="B43" t="n">
-        <v>6.517677</v>
+        <v>14.573969</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.543655</v>
+        <v>1.21565</v>
       </c>
       <c r="B44" t="n">
-        <v>6.520519</v>
+        <v>14.580324</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.556378</v>
+        <v>1.244099</v>
       </c>
       <c r="B45" t="n">
-        <v>6.523428</v>
+        <v>14.586828</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.569085</v>
+        <v>1.272514</v>
       </c>
       <c r="B46" t="n">
-        <v>6.526404</v>
+        <v>14.593483</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.581777</v>
+        <v>1.300893</v>
       </c>
       <c r="B47" t="n">
-        <v>6.529448</v>
+        <v>14.600289</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.594452</v>
+        <v>1.329235</v>
       </c>
       <c r="B48" t="n">
-        <v>6.532558</v>
+        <v>14.607244</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.607111</v>
+        <v>1.357541</v>
       </c>
       <c r="B49" t="n">
-        <v>6.535735</v>
+        <v>14.614349</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.619752</v>
+        <v>1.385808</v>
       </c>
       <c r="B50" t="n">
-        <v>6.53898</v>
+        <v>14.621603</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.632376</v>
+        <v>1.414036</v>
       </c>
       <c r="B51" t="n">
-        <v>6.542291</v>
+        <v>14.629007</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.644983</v>
+        <v>1.442225</v>
       </c>
       <c r="B52" t="n">
-        <v>6.545669</v>
+        <v>14.636561</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.657571</v>
+        <v>1.470374</v>
       </c>
       <c r="B53" t="n">
-        <v>6.549113</v>
+        <v>14.644263</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.670141</v>
+        <v>1.498482</v>
       </c>
       <c r="B54" t="n">
-        <v>6.552625</v>
+        <v>14.652114</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.682693</v>
+        <v>1.526547</v>
       </c>
       <c r="B55" t="n">
-        <v>6.556202</v>
+        <v>14.660113</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.695225</v>
+        <v>1.55457</v>
       </c>
       <c r="B56" t="n">
-        <v>6.559846</v>
+        <v>14.668261</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.707738</v>
+        <v>1.58255</v>
       </c>
       <c r="B57" t="n">
-        <v>6.563556</v>
+        <v>14.676557</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.720231</v>
+        <v>1.610485</v>
       </c>
       <c r="B58" t="n">
-        <v>6.567332</v>
+        <v>14.685001</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.732704</v>
+        <v>1.638375</v>
       </c>
       <c r="B59" t="n">
-        <v>6.571174</v>
+        <v>14.693592</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.745156</v>
+        <v>1.666219</v>
       </c>
       <c r="B60" t="n">
-        <v>6.575082</v>
+        <v>14.702331</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.757587</v>
+        <v>1.694017</v>
       </c>
       <c r="B61" t="n">
-        <v>6.579056</v>
+        <v>14.711217</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.769998</v>
+        <v>1.721767</v>
       </c>
       <c r="B62" t="n">
-        <v>6.583096</v>
+        <v>14.72025</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.7823870000000001</v>
+        <v>1.74947</v>
       </c>
       <c r="B63" t="n">
-        <v>6.587201</v>
+        <v>14.72943</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.794753</v>
+        <v>1.777123</v>
       </c>
       <c r="B64" t="n">
-        <v>6.591372</v>
+        <v>14.738755</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.807098</v>
+        <v>1.804726</v>
       </c>
       <c r="B65" t="n">
-        <v>6.595608</v>
+        <v>14.748227</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.81942</v>
+        <v>1.832279</v>
       </c>
       <c r="B66" t="n">
-        <v>6.599909</v>
+        <v>14.757845</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.831719</v>
+        <v>1.859781</v>
       </c>
       <c r="B67" t="n">
-        <v>6.604275</v>
+        <v>14.767609</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.8439950000000001</v>
+        <v>1.887231</v>
       </c>
       <c r="B68" t="n">
-        <v>6.608707</v>
+        <v>14.777517</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.856248</v>
+        <v>1.914628</v>
       </c>
       <c r="B69" t="n">
-        <v>6.613203</v>
+        <v>14.787571</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.868476</v>
+        <v>1.941971</v>
       </c>
       <c r="B70" t="n">
-        <v>6.617764</v>
+        <v>14.79777</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.88068</v>
+        <v>1.96926</v>
       </c>
       <c r="B71" t="n">
-        <v>6.622389</v>
+        <v>14.808113</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.892859</v>
+        <v>1.996494</v>
       </c>
       <c r="B72" t="n">
-        <v>6.627079</v>
+        <v>14.8186</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.905014</v>
+        <v>2.023672</v>
       </c>
       <c r="B73" t="n">
-        <v>6.631834</v>
+        <v>14.829231</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.917143</v>
+        <v>2.050794</v>
       </c>
       <c r="B74" t="n">
-        <v>6.636652</v>
+        <v>14.840006</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.929246</v>
+        <v>2.077858</v>
       </c>
       <c r="B75" t="n">
-        <v>6.641535</v>
+        <v>14.850924</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.941324</v>
+        <v>2.104864</v>
       </c>
       <c r="B76" t="n">
-        <v>6.646482</v>
+        <v>14.861985</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.953375</v>
+        <v>2.131811</v>
       </c>
       <c r="B77" t="n">
-        <v>6.651492</v>
+        <v>14.873189</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.965399</v>
+        <v>2.158699</v>
       </c>
       <c r="B78" t="n">
-        <v>6.656566</v>
+        <v>14.884535</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.977397</v>
+        <v>2.185526</v>
       </c>
       <c r="B79" t="n">
-        <v>6.661704</v>
+        <v>14.896023</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.989367</v>
+        <v>2.212292</v>
       </c>
       <c r="B80" t="n">
-        <v>6.666905</v>
+        <v>14.907652</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1.00131</v>
+        <v>2.238996</v>
       </c>
       <c r="B81" t="n">
-        <v>6.672169</v>
+        <v>14.919424</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1.013224</v>
+        <v>2.265638</v>
       </c>
       <c r="B82" t="n">
-        <v>6.677496</v>
+        <v>14.931336</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.02511</v>
+        <v>2.292216</v>
       </c>
       <c r="B83" t="n">
-        <v>6.682887</v>
+        <v>14.943389</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.036968</v>
+        <v>2.31873</v>
       </c>
       <c r="B84" t="n">
-        <v>6.68834</v>
+        <v>14.955582</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.048796</v>
+        <v>2.345179</v>
       </c>
       <c r="B85" t="n">
-        <v>6.693855</v>
+        <v>14.967916</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.060595</v>
+        <v>2.371563</v>
       </c>
       <c r="B86" t="n">
-        <v>6.699434</v>
+        <v>14.980389</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1.072364</v>
+        <v>2.39788</v>
       </c>
       <c r="B87" t="n">
-        <v>6.705074</v>
+        <v>14.993001</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.084104</v>
+        <v>2.42413</v>
       </c>
       <c r="B88" t="n">
-        <v>6.710777</v>
+        <v>15.005753</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.095813</v>
+        <v>2.450312</v>
       </c>
       <c r="B89" t="n">
-        <v>6.716541</v>
+        <v>15.018643</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1.107491</v>
+        <v>2.476426</v>
       </c>
       <c r="B90" t="n">
-        <v>6.722368</v>
+        <v>15.031672</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.119139</v>
+        <v>2.502471</v>
       </c>
       <c r="B91" t="n">
-        <v>6.728256</v>
+        <v>15.044838</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.130755</v>
+        <v>2.528445</v>
       </c>
       <c r="B92" t="n">
-        <v>6.734206</v>
+        <v>15.058142</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.14234</v>
+        <v>2.554349</v>
       </c>
       <c r="B93" t="n">
-        <v>6.740217</v>
+        <v>15.071583</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.153892</v>
+        <v>2.580181</v>
       </c>
       <c r="B94" t="n">
-        <v>6.746289</v>
+        <v>15.085161</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.165412</v>
+        <v>2.605942</v>
       </c>
       <c r="B95" t="n">
-        <v>6.752422</v>
+        <v>15.098876</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.1769</v>
+        <v>2.631629</v>
       </c>
       <c r="B96" t="n">
-        <v>6.758617</v>
+        <v>15.112726</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1.188355</v>
+        <v>2.657243</v>
       </c>
       <c r="B97" t="n">
-        <v>6.764871</v>
+        <v>15.126712</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1.199777</v>
+        <v>2.682782</v>
       </c>
       <c r="B98" t="n">
-        <v>6.771187</v>
+        <v>15.140834</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1.211165</v>
+        <v>2.708246</v>
       </c>
       <c r="B99" t="n">
-        <v>6.777562</v>
+        <v>15.15509</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.222519</v>
+        <v>2.733635</v>
       </c>
       <c r="B100" t="n">
-        <v>6.783998</v>
+        <v>15.169481</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1.233839</v>
+        <v>2.758947</v>
       </c>
       <c r="B101" t="n">
-        <v>6.790494</v>
+        <v>15.184005</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2.01656</v>
+        <v>4.509165</v>
       </c>
       <c r="B102" t="n">
-        <v>7.240706</v>
+        <v>16.190712</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2.799281</v>
+        <v>6.259383</v>
       </c>
       <c r="B103" t="n">
-        <v>7.687536</v>
+        <v>17.189854</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>3.582003</v>
+        <v>8.009601</v>
       </c>
       <c r="B104" t="n">
-        <v>8.130983000000001</v>
+        <v>18.18143</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4.364724</v>
+        <v>9.759819</v>
       </c>
       <c r="B105" t="n">
-        <v>8.571046000000001</v>
+        <v>19.165442</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5.147445</v>
+        <v>11.510038</v>
       </c>
       <c r="B106" t="n">
-        <v>9.007726999999999</v>
+        <v>20.14189</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5.930167</v>
+        <v>13.260256</v>
       </c>
       <c r="B107" t="n">
-        <v>9.441024000000001</v>
+        <v>21.110772</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6.712888</v>
+        <v>15.010474</v>
       </c>
       <c r="B108" t="n">
-        <v>9.870939</v>
+        <v>22.07209</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>7.495609</v>
+        <v>16.760692</v>
       </c>
       <c r="B109" t="n">
-        <v>10.29747</v>
+        <v>23.025842</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>8.278331</v>
+        <v>18.51091</v>
       </c>
       <c r="B110" t="n">
-        <v>10.720618</v>
+        <v>23.97203</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>9.061052</v>
+        <v>20.261128</v>
       </c>
       <c r="B111" t="n">
-        <v>11.140383</v>
+        <v>24.910654</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>9.843773000000001</v>
+        <v>22.011346</v>
       </c>
       <c r="B112" t="n">
-        <v>11.556765</v>
+        <v>25.841712</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>10.626495</v>
+        <v>23.761564</v>
       </c>
       <c r="B113" t="n">
-        <v>11.969764</v>
+        <v>26.765205</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>11.409216</v>
+        <v>25.511783</v>
       </c>
       <c r="B114" t="n">
-        <v>12.379379</v>
+        <v>27.681134</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>12.191937</v>
+        <v>27.262001</v>
       </c>
       <c r="B115" t="n">
-        <v>12.785612</v>
+        <v>28.589498</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>12.974659</v>
+        <v>29.012219</v>
       </c>
       <c r="B116" t="n">
-        <v>13.188462</v>
+        <v>29.490297</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>13.75738</v>
+        <v>30.762437</v>
       </c>
       <c r="B117" t="n">
-        <v>13.587928</v>
+        <v>30.383531</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>14.540101</v>
+        <v>32.512655</v>
       </c>
       <c r="B118" t="n">
-        <v>13.984012</v>
+        <v>31.269201</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>15.322823</v>
+        <v>34.262873</v>
       </c>
       <c r="B119" t="n">
-        <v>14.376712</v>
+        <v>32.147305</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>16.105544</v>
+        <v>36.013091</v>
       </c>
       <c r="B120" t="n">
-        <v>14.766029</v>
+        <v>33.017845</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>16.888265</v>
+        <v>37.76331</v>
       </c>
       <c r="B121" t="n">
-        <v>15.151963</v>
+        <v>33.88082</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>17.670987</v>
+        <v>39.513528</v>
       </c>
       <c r="B122" t="n">
-        <v>15.534514</v>
+        <v>34.73623</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>18.453708</v>
+        <v>41.263746</v>
       </c>
       <c r="B123" t="n">
-        <v>15.913682</v>
+        <v>35.584075</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>19.236429</v>
+        <v>43.013964</v>
       </c>
       <c r="B124" t="n">
-        <v>16.289467</v>
+        <v>36.424356</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>20.019151</v>
+        <v>44.764182</v>
       </c>
       <c r="B125" t="n">
-        <v>16.661869</v>
+        <v>37.257071</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>20.801872</v>
+        <v>46.5144</v>
       </c>
       <c r="B126" t="n">
-        <v>17.030888</v>
+        <v>38.082222</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>21.584594</v>
+        <v>48.264618</v>
       </c>
       <c r="B127" t="n">
-        <v>17.396523</v>
+        <v>38.899808</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>22.367315</v>
+        <v>50.014836</v>
       </c>
       <c r="B128" t="n">
-        <v>17.758776</v>
+        <v>39.70983</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>23.150036</v>
+        <v>51.765055</v>
       </c>
       <c r="B129" t="n">
-        <v>18.117645</v>
+        <v>40.512286</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>23.932758</v>
+        <v>53.515273</v>
       </c>
       <c r="B130" t="n">
-        <v>18.473131</v>
+        <v>41.307177</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>24.715479</v>
+        <v>55.265491</v>
       </c>
       <c r="B131" t="n">
-        <v>18.825235</v>
+        <v>42.094504</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>25.4982</v>
+        <v>57.015709</v>
       </c>
       <c r="B132" t="n">
-        <v>19.173955</v>
+        <v>42.874266</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>26.280922</v>
+        <v>58.765927</v>
       </c>
       <c r="B133" t="n">
-        <v>19.519292</v>
+        <v>43.646463</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>27.063643</v>
+        <v>60.516145</v>
       </c>
       <c r="B134" t="n">
-        <v>19.861246</v>
+        <v>44.411096</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>27.846364</v>
+        <v>62.266363</v>
       </c>
       <c r="B135" t="n">
-        <v>20.199817</v>
+        <v>45.168163</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>28.629086</v>
+        <v>64.016582</v>
       </c>
       <c r="B136" t="n">
-        <v>20.535004</v>
+        <v>45.917666</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>29.411807</v>
+        <v>65.7668</v>
       </c>
       <c r="B137" t="n">
-        <v>20.866809</v>
+        <v>46.659604</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>30.194528</v>
+        <v>67.51701799999999</v>
       </c>
       <c r="B138" t="n">
-        <v>21.195231</v>
+        <v>47.393977</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>30.97725</v>
+        <v>69.267236</v>
       </c>
       <c r="B139" t="n">
-        <v>21.520269</v>
+        <v>48.120785</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>31.759971</v>
+        <v>71.017454</v>
       </c>
       <c r="B140" t="n">
-        <v>21.841925</v>
+        <v>48.840028</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>32.542692</v>
+        <v>72.767672</v>
       </c>
       <c r="B141" t="n">
-        <v>22.160197</v>
+        <v>49.551707</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>33.325414</v>
+        <v>74.51788999999999</v>
       </c>
       <c r="B142" t="n">
-        <v>22.475086</v>
+        <v>50.255821</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>34.108135</v>
+        <v>76.268108</v>
       </c>
       <c r="B143" t="n">
-        <v>22.786592</v>
+        <v>50.952369</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>34.890856</v>
+        <v>78.018327</v>
       </c>
       <c r="B144" t="n">
-        <v>23.094715</v>
+        <v>51.641354</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>35.673578</v>
+        <v>79.768545</v>
       </c>
       <c r="B145" t="n">
-        <v>23.399455</v>
+        <v>52.322773</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>36.456299</v>
+        <v>81.51876300000001</v>
       </c>
       <c r="B146" t="n">
-        <v>23.700812</v>
+        <v>52.996627</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>37.23902</v>
+        <v>83.268981</v>
       </c>
       <c r="B147" t="n">
-        <v>23.998786</v>
+        <v>53.662917</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>38.021742</v>
+        <v>85.019199</v>
       </c>
       <c r="B148" t="n">
-        <v>24.293377</v>
+        <v>54.321642</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>38.804463</v>
+        <v>86.769417</v>
       </c>
       <c r="B149" t="n">
-        <v>24.584584</v>
+        <v>54.972802</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>39.587184</v>
+        <v>88.51963499999999</v>
       </c>
       <c r="B150" t="n">
-        <v>24.872409</v>
+        <v>55.616397</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>40.369906</v>
+        <v>90.269854</v>
       </c>
       <c r="B151" t="n">
-        <v>25.15685</v>
+        <v>56.252427</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>41.152627</v>
+        <v>92.020072</v>
       </c>
       <c r="B152" t="n">
-        <v>25.437909</v>
+        <v>56.880893</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41.935348</v>
+        <v>93.77029</v>
       </c>
       <c r="B153" t="n">
-        <v>25.715584</v>
+        <v>57.501794</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>42.71807</v>
+        <v>95.52050800000001</v>
       </c>
       <c r="B154" t="n">
-        <v>25.989876</v>
+        <v>58.11513</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>43.500791</v>
+        <v>97.270726</v>
       </c>
       <c r="B155" t="n">
-        <v>26.260785</v>
+        <v>58.720901</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>44.283513</v>
+        <v>99.020944</v>
       </c>
       <c r="B156" t="n">
-        <v>26.528311</v>
+        <v>59.319107</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>45.066234</v>
+        <v>100.771162</v>
       </c>
       <c r="B157" t="n">
-        <v>26.792454</v>
+        <v>59.909749</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>45.848955</v>
+        <v>102.521381</v>
       </c>
       <c r="B158" t="n">
-        <v>27.053214</v>
+        <v>60.492825</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>46.631677</v>
+        <v>104.271599</v>
       </c>
       <c r="B159" t="n">
-        <v>27.310591</v>
+        <v>61.068337</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>47.414398</v>
+        <v>106.021817</v>
       </c>
       <c r="B160" t="n">
-        <v>27.564584</v>
+        <v>61.636284</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>48.197119</v>
+        <v>107.772035</v>
       </c>
       <c r="B161" t="n">
-        <v>27.815195</v>
+        <v>62.196666</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>48.979841</v>
+        <v>109.522253</v>
       </c>
       <c r="B162" t="n">
-        <v>28.062422</v>
+        <v>62.749484</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>49.762562</v>
+        <v>111.272471</v>
       </c>
       <c r="B163" t="n">
-        <v>28.306267</v>
+        <v>63.294736</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>50.545283</v>
+        <v>113.022689</v>
       </c>
       <c r="B164" t="n">
-        <v>28.546728</v>
+        <v>63.832424</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>51.328005</v>
+        <v>114.772907</v>
       </c>
       <c r="B165" t="n">
-        <v>28.783806</v>
+        <v>64.36254700000001</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>52.110726</v>
+        <v>116.523126</v>
       </c>
       <c r="B166" t="n">
-        <v>29.017501</v>
+        <v>64.885105</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>52.893447</v>
+        <v>118.273344</v>
       </c>
       <c r="B167" t="n">
-        <v>29.247813</v>
+        <v>65.400098</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>53.676169</v>
+        <v>120.023562</v>
       </c>
       <c r="B168" t="n">
-        <v>29.474742</v>
+        <v>65.907527</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>54.45889</v>
+        <v>121.77378</v>
       </c>
       <c r="B169" t="n">
-        <v>29.698288</v>
+        <v>66.40739000000001</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>55.241611</v>
+        <v>123.523998</v>
       </c>
       <c r="B170" t="n">
-        <v>29.918451</v>
+        <v>66.899689</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>56.024333</v>
+        <v>125.274216</v>
       </c>
       <c r="B171" t="n">
-        <v>30.13523</v>
+        <v>67.384423</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>56.807054</v>
+        <v>127.024434</v>
       </c>
       <c r="B172" t="n">
-        <v>30.348627</v>
+        <v>67.861592</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>57.589775</v>
+        <v>128.774653</v>
       </c>
       <c r="B173" t="n">
-        <v>30.55864</v>
+        <v>68.331197</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>58.372497</v>
+        <v>130.524871</v>
       </c>
       <c r="B174" t="n">
-        <v>30.765271</v>
+        <v>68.79323599999999</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>59.155218</v>
+        <v>132.275089</v>
       </c>
       <c r="B175" t="n">
-        <v>30.968518</v>
+        <v>69.247711</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>59.937939</v>
+        <v>134.025307</v>
       </c>
       <c r="B176" t="n">
-        <v>31.168382</v>
+        <v>69.694621</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>60.720661</v>
+        <v>135.775525</v>
       </c>
       <c r="B177" t="n">
-        <v>31.364863</v>
+        <v>70.133966</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>61.503382</v>
+        <v>137.525743</v>
       </c>
       <c r="B178" t="n">
-        <v>31.557961</v>
+        <v>70.565746</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>62.286103</v>
+        <v>139.275961</v>
       </c>
       <c r="B179" t="n">
-        <v>31.747676</v>
+        <v>70.98996200000001</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>63.068825</v>
+        <v>141.026179</v>
       </c>
       <c r="B180" t="n">
-        <v>31.934008</v>
+        <v>71.406612</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>63.851546</v>
+        <v>142.776398</v>
       </c>
       <c r="B181" t="n">
-        <v>32.116957</v>
+        <v>71.815698</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>64.63426699999999</v>
+        <v>144.526616</v>
       </c>
       <c r="B182" t="n">
-        <v>32.296522</v>
+        <v>72.217219</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>65.416989</v>
+        <v>146.276834</v>
       </c>
       <c r="B183" t="n">
-        <v>32.472705</v>
+        <v>72.611175</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>66.19971</v>
+        <v>148.027052</v>
       </c>
       <c r="B184" t="n">
-        <v>32.645504</v>
+        <v>72.997567</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>66.982432</v>
+        <v>149.77727</v>
       </c>
       <c r="B185" t="n">
-        <v>32.814921</v>
+        <v>73.37639299999999</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>67.765153</v>
+        <v>151.527488</v>
       </c>
       <c r="B186" t="n">
-        <v>32.980954</v>
+        <v>73.74765499999999</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>68.54787399999999</v>
+        <v>153.277706</v>
       </c>
       <c r="B187" t="n">
-        <v>33.143604</v>
+        <v>74.111352</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>69.330596</v>
+        <v>155.027925</v>
       </c>
       <c r="B188" t="n">
-        <v>33.302871</v>
+        <v>74.467484</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>70.113317</v>
+        <v>156.778143</v>
       </c>
       <c r="B189" t="n">
-        <v>33.458755</v>
+        <v>74.816051</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>70.896038</v>
+        <v>158.528361</v>
       </c>
       <c r="B190" t="n">
-        <v>33.611256</v>
+        <v>75.157054</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>71.67876</v>
+        <v>160.278579</v>
       </c>
       <c r="B191" t="n">
-        <v>33.760374</v>
+        <v>75.49049100000001</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>72.46148100000001</v>
+        <v>162.028797</v>
       </c>
       <c r="B192" t="n">
-        <v>33.906109</v>
+        <v>75.81636399999999</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>73.244202</v>
+        <v>163.779015</v>
       </c>
       <c r="B193" t="n">
-        <v>34.04846</v>
+        <v>76.13467199999999</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>74.02692399999999</v>
+        <v>165.529233</v>
       </c>
       <c r="B194" t="n">
-        <v>34.187429</v>
+        <v>76.445415</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>74.809645</v>
+        <v>167.279452</v>
       </c>
       <c r="B195" t="n">
-        <v>34.323015</v>
+        <v>76.748594</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>75.592366</v>
+        <v>169.02967</v>
       </c>
       <c r="B196" t="n">
-        <v>34.455217</v>
+        <v>77.044207</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>76.37508800000001</v>
+        <v>170.779888</v>
       </c>
       <c r="B197" t="n">
-        <v>34.584036</v>
+        <v>77.332256</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>77.157809</v>
+        <v>172.530106</v>
       </c>
       <c r="B198" t="n">
-        <v>34.709472</v>
+        <v>77.61274</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>77.94053</v>
+        <v>174.280324</v>
       </c>
       <c r="B199" t="n">
-        <v>34.831526</v>
+        <v>77.885659</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>78.723252</v>
+        <v>176.030542</v>
       </c>
       <c r="B200" t="n">
-        <v>34.950196</v>
+        <v>78.15101300000001</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>

--- a/Bell_Nozzle_Divergent_Profile.xlsx
+++ b/Bell_Nozzle_Divergent_Profile.xlsx
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.444748</v>
+        <v>6.459888</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.029183</v>
+        <v>0.013051</v>
       </c>
       <c r="B3" t="n">
-        <v>14.444825</v>
+        <v>6.459922</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.058366</v>
+        <v>0.026102</v>
       </c>
       <c r="B4" t="n">
-        <v>14.445056</v>
+        <v>6.460026</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.087547</v>
+        <v>0.039152</v>
       </c>
       <c r="B5" t="n">
-        <v>14.445442</v>
+        <v>6.460198</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.116725</v>
+        <v>0.052201</v>
       </c>
       <c r="B6" t="n">
-        <v>14.445983</v>
+        <v>6.46044</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1459</v>
+        <v>0.065249</v>
       </c>
       <c r="B7" t="n">
-        <v>14.446677</v>
+        <v>6.46075</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.175071</v>
+        <v>0.078294</v>
       </c>
       <c r="B8" t="n">
-        <v>14.447526</v>
+        <v>6.46113</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.204238</v>
+        <v>0.091338</v>
       </c>
       <c r="B9" t="n">
-        <v>14.448529</v>
+        <v>6.461579</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.233398</v>
+        <v>0.104379</v>
       </c>
       <c r="B10" t="n">
-        <v>14.449686</v>
+        <v>6.462096</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.262552</v>
+        <v>0.117417</v>
       </c>
       <c r="B11" t="n">
-        <v>14.450998</v>
+        <v>6.462683</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.291699</v>
+        <v>0.130452</v>
       </c>
       <c r="B12" t="n">
-        <v>14.452463</v>
+        <v>6.463338</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.320837</v>
+        <v>0.143483</v>
       </c>
       <c r="B13" t="n">
-        <v>14.454083</v>
+        <v>6.464063</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.349966</v>
+        <v>0.15651</v>
       </c>
       <c r="B14" t="n">
-        <v>14.455857</v>
+        <v>6.464856</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.379086</v>
+        <v>0.169532</v>
       </c>
       <c r="B15" t="n">
-        <v>14.457785</v>
+        <v>6.465718</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.408195</v>
+        <v>0.18255</v>
       </c>
       <c r="B16" t="n">
-        <v>14.459867</v>
+        <v>6.466649</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.437293</v>
+        <v>0.195563</v>
       </c>
       <c r="B17" t="n">
-        <v>14.462103</v>
+        <v>6.467649</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.466378</v>
+        <v>0.208571</v>
       </c>
       <c r="B18" t="n">
-        <v>14.464493</v>
+        <v>6.468718</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.495451</v>
+        <v>0.221572</v>
       </c>
       <c r="B19" t="n">
-        <v>14.467036</v>
+        <v>6.469855</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.524509</v>
+        <v>0.234568</v>
       </c>
       <c r="B20" t="n">
-        <v>14.469733</v>
+        <v>6.471061</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.553553</v>
+        <v>0.247556</v>
       </c>
       <c r="B21" t="n">
-        <v>14.472584</v>
+        <v>6.472336</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.582581</v>
+        <v>0.260538</v>
       </c>
       <c r="B22" t="n">
-        <v>14.475589</v>
+        <v>6.47368</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.6115930000000001</v>
+        <v>0.273513</v>
       </c>
       <c r="B23" t="n">
-        <v>14.478746</v>
+        <v>6.475092</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.640588</v>
+        <v>0.28648</v>
       </c>
       <c r="B24" t="n">
-        <v>14.482058</v>
+        <v>6.476573</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.669565</v>
+        <v>0.299439</v>
       </c>
       <c r="B25" t="n">
-        <v>14.485522</v>
+        <v>6.478123</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.698524</v>
+        <v>0.312389</v>
       </c>
       <c r="B26" t="n">
-        <v>14.48914</v>
+        <v>6.479741</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.7274620000000001</v>
+        <v>0.325331</v>
       </c>
       <c r="B27" t="n">
-        <v>14.492911</v>
+        <v>6.481427</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.756381</v>
+        <v>0.338264</v>
       </c>
       <c r="B28" t="n">
-        <v>14.496835</v>
+        <v>6.483182</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.785278</v>
+        <v>0.351187</v>
       </c>
       <c r="B29" t="n">
-        <v>14.500912</v>
+        <v>6.485005</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.814153</v>
+        <v>0.3641</v>
       </c>
       <c r="B30" t="n">
-        <v>14.505142</v>
+        <v>6.486897</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.843006</v>
+        <v>0.377004</v>
       </c>
       <c r="B31" t="n">
-        <v>14.509524</v>
+        <v>6.488856</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.871835</v>
+        <v>0.389896</v>
       </c>
       <c r="B32" t="n">
-        <v>14.514059</v>
+        <v>6.490884</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.900639</v>
+        <v>0.402778</v>
       </c>
       <c r="B33" t="n">
-        <v>14.518746</v>
+        <v>6.492981</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.929419</v>
+        <v>0.415649</v>
       </c>
       <c r="B34" t="n">
-        <v>14.523585</v>
+        <v>6.495145</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.958172</v>
+        <v>0.428508</v>
       </c>
       <c r="B35" t="n">
-        <v>14.528577</v>
+        <v>6.497377</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.986899</v>
+        <v>0.441355</v>
       </c>
       <c r="B36" t="n">
-        <v>14.533721</v>
+        <v>6.499677</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.015598</v>
+        <v>0.454189</v>
       </c>
       <c r="B37" t="n">
-        <v>14.539016</v>
+        <v>6.502046</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.044268</v>
+        <v>0.467011</v>
       </c>
       <c r="B38" t="n">
-        <v>14.544463</v>
+        <v>6.504482</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.07291</v>
+        <v>0.47982</v>
       </c>
       <c r="B39" t="n">
-        <v>14.550062</v>
+        <v>6.506986</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1.101521</v>
+        <v>0.492615</v>
       </c>
       <c r="B40" t="n">
-        <v>14.555812</v>
+        <v>6.509557</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1.130101</v>
+        <v>0.505397</v>
       </c>
       <c r="B41" t="n">
-        <v>14.561714</v>
+        <v>6.512196</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1.15865</v>
+        <v>0.518164</v>
       </c>
       <c r="B42" t="n">
-        <v>14.567766</v>
+        <v>6.514903</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1.187167</v>
+        <v>0.530917</v>
       </c>
       <c r="B43" t="n">
-        <v>14.573969</v>
+        <v>6.517677</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1.21565</v>
+        <v>0.543655</v>
       </c>
       <c r="B44" t="n">
-        <v>14.580324</v>
+        <v>6.520519</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1.244099</v>
+        <v>0.556378</v>
       </c>
       <c r="B45" t="n">
-        <v>14.586828</v>
+        <v>6.523428</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1.272514</v>
+        <v>0.569085</v>
       </c>
       <c r="B46" t="n">
-        <v>14.593483</v>
+        <v>6.526404</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.300893</v>
+        <v>0.581777</v>
       </c>
       <c r="B47" t="n">
-        <v>14.600289</v>
+        <v>6.529448</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1.329235</v>
+        <v>0.594452</v>
       </c>
       <c r="B48" t="n">
-        <v>14.607244</v>
+        <v>6.532558</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1.357541</v>
+        <v>0.607111</v>
       </c>
       <c r="B49" t="n">
-        <v>14.614349</v>
+        <v>6.535735</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.385808</v>
+        <v>0.619752</v>
       </c>
       <c r="B50" t="n">
-        <v>14.621603</v>
+        <v>6.53898</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.414036</v>
+        <v>0.632376</v>
       </c>
       <c r="B51" t="n">
-        <v>14.629007</v>
+        <v>6.542291</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.442225</v>
+        <v>0.644983</v>
       </c>
       <c r="B52" t="n">
-        <v>14.636561</v>
+        <v>6.545669</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.470374</v>
+        <v>0.657571</v>
       </c>
       <c r="B53" t="n">
-        <v>14.644263</v>
+        <v>6.549113</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.498482</v>
+        <v>0.670141</v>
       </c>
       <c r="B54" t="n">
-        <v>14.652114</v>
+        <v>6.552625</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.526547</v>
+        <v>0.682693</v>
       </c>
       <c r="B55" t="n">
-        <v>14.660113</v>
+        <v>6.556202</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.55457</v>
+        <v>0.695225</v>
       </c>
       <c r="B56" t="n">
-        <v>14.668261</v>
+        <v>6.559846</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.58255</v>
+        <v>0.707738</v>
       </c>
       <c r="B57" t="n">
-        <v>14.676557</v>
+        <v>6.563556</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.610485</v>
+        <v>0.720231</v>
       </c>
       <c r="B58" t="n">
-        <v>14.685001</v>
+        <v>6.567332</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.638375</v>
+        <v>0.732704</v>
       </c>
       <c r="B59" t="n">
-        <v>14.693592</v>
+        <v>6.571174</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.666219</v>
+        <v>0.745156</v>
       </c>
       <c r="B60" t="n">
-        <v>14.702331</v>
+        <v>6.575082</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.694017</v>
+        <v>0.757587</v>
       </c>
       <c r="B61" t="n">
-        <v>14.711217</v>
+        <v>6.579056</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.721767</v>
+        <v>0.769998</v>
       </c>
       <c r="B62" t="n">
-        <v>14.72025</v>
+        <v>6.583096</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.74947</v>
+        <v>0.7823870000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>14.72943</v>
+        <v>6.587201</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.777123</v>
+        <v>0.794753</v>
       </c>
       <c r="B64" t="n">
-        <v>14.738755</v>
+        <v>6.591372</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.804726</v>
+        <v>0.807098</v>
       </c>
       <c r="B65" t="n">
-        <v>14.748227</v>
+        <v>6.595608</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.832279</v>
+        <v>0.81942</v>
       </c>
       <c r="B66" t="n">
-        <v>14.757845</v>
+        <v>6.599909</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.859781</v>
+        <v>0.831719</v>
       </c>
       <c r="B67" t="n">
-        <v>14.767609</v>
+        <v>6.604275</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.887231</v>
+        <v>0.8439950000000001</v>
       </c>
       <c r="B68" t="n">
-        <v>14.777517</v>
+        <v>6.608707</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.914628</v>
+        <v>0.856248</v>
       </c>
       <c r="B69" t="n">
-        <v>14.787571</v>
+        <v>6.613203</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.941971</v>
+        <v>0.868476</v>
       </c>
       <c r="B70" t="n">
-        <v>14.79777</v>
+        <v>6.617764</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.96926</v>
+        <v>0.88068</v>
       </c>
       <c r="B71" t="n">
-        <v>14.808113</v>
+        <v>6.622389</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1.996494</v>
+        <v>0.892859</v>
       </c>
       <c r="B72" t="n">
-        <v>14.8186</v>
+        <v>6.627079</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2.023672</v>
+        <v>0.905014</v>
       </c>
       <c r="B73" t="n">
-        <v>14.829231</v>
+        <v>6.631834</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2.050794</v>
+        <v>0.917143</v>
       </c>
       <c r="B74" t="n">
-        <v>14.840006</v>
+        <v>6.636652</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2.077858</v>
+        <v>0.929246</v>
       </c>
       <c r="B75" t="n">
-        <v>14.850924</v>
+        <v>6.641535</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2.104864</v>
+        <v>0.941324</v>
       </c>
       <c r="B76" t="n">
-        <v>14.861985</v>
+        <v>6.646482</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2.131811</v>
+        <v>0.953375</v>
       </c>
       <c r="B77" t="n">
-        <v>14.873189</v>
+        <v>6.651492</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2.158699</v>
+        <v>0.965399</v>
       </c>
       <c r="B78" t="n">
-        <v>14.884535</v>
+        <v>6.656566</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2.185526</v>
+        <v>0.977397</v>
       </c>
       <c r="B79" t="n">
-        <v>14.896023</v>
+        <v>6.661704</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2.212292</v>
+        <v>0.989367</v>
       </c>
       <c r="B80" t="n">
-        <v>14.907652</v>
+        <v>6.666905</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2.238996</v>
+        <v>1.00131</v>
       </c>
       <c r="B81" t="n">
-        <v>14.919424</v>
+        <v>6.672169</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2.265638</v>
+        <v>1.013224</v>
       </c>
       <c r="B82" t="n">
-        <v>14.931336</v>
+        <v>6.677496</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2.292216</v>
+        <v>1.02511</v>
       </c>
       <c r="B83" t="n">
-        <v>14.943389</v>
+        <v>6.682887</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2.31873</v>
+        <v>1.036968</v>
       </c>
       <c r="B84" t="n">
-        <v>14.955582</v>
+        <v>6.68834</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2.345179</v>
+        <v>1.048796</v>
       </c>
       <c r="B85" t="n">
-        <v>14.967916</v>
+        <v>6.693855</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2.371563</v>
+        <v>1.060595</v>
       </c>
       <c r="B86" t="n">
-        <v>14.980389</v>
+        <v>6.699434</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2.39788</v>
+        <v>1.072364</v>
       </c>
       <c r="B87" t="n">
-        <v>14.993001</v>
+        <v>6.705074</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2.42413</v>
+        <v>1.084104</v>
       </c>
       <c r="B88" t="n">
-        <v>15.005753</v>
+        <v>6.710777</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2.450312</v>
+        <v>1.095813</v>
       </c>
       <c r="B89" t="n">
-        <v>15.018643</v>
+        <v>6.716541</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2.476426</v>
+        <v>1.107491</v>
       </c>
       <c r="B90" t="n">
-        <v>15.031672</v>
+        <v>6.722368</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2.502471</v>
+        <v>1.119139</v>
       </c>
       <c r="B91" t="n">
-        <v>15.044838</v>
+        <v>6.728256</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2.528445</v>
+        <v>1.130755</v>
       </c>
       <c r="B92" t="n">
-        <v>15.058142</v>
+        <v>6.734206</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2.554349</v>
+        <v>1.14234</v>
       </c>
       <c r="B93" t="n">
-        <v>15.071583</v>
+        <v>6.740217</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2.580181</v>
+        <v>1.153892</v>
       </c>
       <c r="B94" t="n">
-        <v>15.085161</v>
+        <v>6.746289</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2.605942</v>
+        <v>1.165412</v>
       </c>
       <c r="B95" t="n">
-        <v>15.098876</v>
+        <v>6.752422</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2.631629</v>
+        <v>1.1769</v>
       </c>
       <c r="B96" t="n">
-        <v>15.112726</v>
+        <v>6.758617</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2.657243</v>
+        <v>1.188355</v>
       </c>
       <c r="B97" t="n">
-        <v>15.126712</v>
+        <v>6.764871</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2.682782</v>
+        <v>1.199777</v>
       </c>
       <c r="B98" t="n">
-        <v>15.140834</v>
+        <v>6.771187</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2.708246</v>
+        <v>1.211165</v>
       </c>
       <c r="B99" t="n">
-        <v>15.15509</v>
+        <v>6.777562</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2.733635</v>
+        <v>1.222519</v>
       </c>
       <c r="B100" t="n">
-        <v>15.169481</v>
+        <v>6.783998</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2.758947</v>
+        <v>1.233839</v>
       </c>
       <c r="B101" t="n">
-        <v>15.184005</v>
+        <v>6.790494</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4.509165</v>
+        <v>2.01656</v>
       </c>
       <c r="B102" t="n">
-        <v>16.190712</v>
+        <v>7.240706</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>6.259383</v>
+        <v>2.799281</v>
       </c>
       <c r="B103" t="n">
-        <v>17.189854</v>
+        <v>7.687536</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>8.009601</v>
+        <v>3.582003</v>
       </c>
       <c r="B104" t="n">
-        <v>18.18143</v>
+        <v>8.130983000000001</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>9.759819</v>
+        <v>4.364724</v>
       </c>
       <c r="B105" t="n">
-        <v>19.165442</v>
+        <v>8.571046000000001</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>11.510038</v>
+        <v>5.147445</v>
       </c>
       <c r="B106" t="n">
-        <v>20.14189</v>
+        <v>9.007726999999999</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>13.260256</v>
+        <v>5.930167</v>
       </c>
       <c r="B107" t="n">
-        <v>21.110772</v>
+        <v>9.441024000000001</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>15.010474</v>
+        <v>6.712888</v>
       </c>
       <c r="B108" t="n">
-        <v>22.07209</v>
+        <v>9.870939</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>16.760692</v>
+        <v>7.495609</v>
       </c>
       <c r="B109" t="n">
-        <v>23.025842</v>
+        <v>10.29747</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>18.51091</v>
+        <v>8.278331</v>
       </c>
       <c r="B110" t="n">
-        <v>23.97203</v>
+        <v>10.720618</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>20.261128</v>
+        <v>9.061052</v>
       </c>
       <c r="B111" t="n">
-        <v>24.910654</v>
+        <v>11.140383</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>22.011346</v>
+        <v>9.843773000000001</v>
       </c>
       <c r="B112" t="n">
-        <v>25.841712</v>
+        <v>11.556765</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>23.761564</v>
+        <v>10.626495</v>
       </c>
       <c r="B113" t="n">
-        <v>26.765205</v>
+        <v>11.969764</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>25.511783</v>
+        <v>11.409216</v>
       </c>
       <c r="B114" t="n">
-        <v>27.681134</v>
+        <v>12.379379</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>27.262001</v>
+        <v>12.191937</v>
       </c>
       <c r="B115" t="n">
-        <v>28.589498</v>
+        <v>12.785612</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>29.012219</v>
+        <v>12.974659</v>
       </c>
       <c r="B116" t="n">
-        <v>29.490297</v>
+        <v>13.188462</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>30.762437</v>
+        <v>13.75738</v>
       </c>
       <c r="B117" t="n">
-        <v>30.383531</v>
+        <v>13.587928</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>32.512655</v>
+        <v>14.540101</v>
       </c>
       <c r="B118" t="n">
-        <v>31.269201</v>
+        <v>13.984012</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>34.262873</v>
+        <v>15.322823</v>
       </c>
       <c r="B119" t="n">
-        <v>32.147305</v>
+        <v>14.376712</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>36.013091</v>
+        <v>16.105544</v>
       </c>
       <c r="B120" t="n">
-        <v>33.017845</v>
+        <v>14.766029</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>37.76331</v>
+        <v>16.888265</v>
       </c>
       <c r="B121" t="n">
-        <v>33.88082</v>
+        <v>15.151963</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>39.513528</v>
+        <v>17.670987</v>
       </c>
       <c r="B122" t="n">
-        <v>34.73623</v>
+        <v>15.534514</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>41.263746</v>
+        <v>18.453708</v>
       </c>
       <c r="B123" t="n">
-        <v>35.584075</v>
+        <v>15.913682</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>43.013964</v>
+        <v>19.236429</v>
       </c>
       <c r="B124" t="n">
-        <v>36.424356</v>
+        <v>16.289467</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>44.764182</v>
+        <v>20.019151</v>
       </c>
       <c r="B125" t="n">
-        <v>37.257071</v>
+        <v>16.661869</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>46.5144</v>
+        <v>20.801872</v>
       </c>
       <c r="B126" t="n">
-        <v>38.082222</v>
+        <v>17.030888</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>48.264618</v>
+        <v>21.584594</v>
       </c>
       <c r="B127" t="n">
-        <v>38.899808</v>
+        <v>17.396523</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>50.014836</v>
+        <v>22.367315</v>
       </c>
       <c r="B128" t="n">
-        <v>39.70983</v>
+        <v>17.758776</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>51.765055</v>
+        <v>23.150036</v>
       </c>
       <c r="B129" t="n">
-        <v>40.512286</v>
+        <v>18.117645</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>53.515273</v>
+        <v>23.932758</v>
       </c>
       <c r="B130" t="n">
-        <v>41.307177</v>
+        <v>18.473131</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>55.265491</v>
+        <v>24.715479</v>
       </c>
       <c r="B131" t="n">
-        <v>42.094504</v>
+        <v>18.825235</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>57.015709</v>
+        <v>25.4982</v>
       </c>
       <c r="B132" t="n">
-        <v>42.874266</v>
+        <v>19.173955</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>58.765927</v>
+        <v>26.280922</v>
       </c>
       <c r="B133" t="n">
-        <v>43.646463</v>
+        <v>19.519292</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>60.516145</v>
+        <v>27.063643</v>
       </c>
       <c r="B134" t="n">
-        <v>44.411096</v>
+        <v>19.861246</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>62.266363</v>
+        <v>27.846364</v>
       </c>
       <c r="B135" t="n">
-        <v>45.168163</v>
+        <v>20.199817</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>64.016582</v>
+        <v>28.629086</v>
       </c>
       <c r="B136" t="n">
-        <v>45.917666</v>
+        <v>20.535004</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>65.7668</v>
+        <v>29.411807</v>
       </c>
       <c r="B137" t="n">
-        <v>46.659604</v>
+        <v>20.866809</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>67.51701799999999</v>
+        <v>30.194528</v>
       </c>
       <c r="B138" t="n">
-        <v>47.393977</v>
+        <v>21.195231</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>69.267236</v>
+        <v>30.97725</v>
       </c>
       <c r="B139" t="n">
-        <v>48.120785</v>
+        <v>21.520269</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>71.017454</v>
+        <v>31.759971</v>
       </c>
       <c r="B140" t="n">
-        <v>48.840028</v>
+        <v>21.841925</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>72.767672</v>
+        <v>32.542692</v>
       </c>
       <c r="B141" t="n">
-        <v>49.551707</v>
+        <v>22.160197</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>74.51788999999999</v>
+        <v>33.325414</v>
       </c>
       <c r="B142" t="n">
-        <v>50.255821</v>
+        <v>22.475086</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>76.268108</v>
+        <v>34.108135</v>
       </c>
       <c r="B143" t="n">
-        <v>50.952369</v>
+        <v>22.786592</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>78.018327</v>
+        <v>34.890856</v>
       </c>
       <c r="B144" t="n">
-        <v>51.641354</v>
+        <v>23.094715</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>79.768545</v>
+        <v>35.673578</v>
       </c>
       <c r="B145" t="n">
-        <v>52.322773</v>
+        <v>23.399455</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>81.51876300000001</v>
+        <v>36.456299</v>
       </c>
       <c r="B146" t="n">
-        <v>52.996627</v>
+        <v>23.700812</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>83.268981</v>
+        <v>37.23902</v>
       </c>
       <c r="B147" t="n">
-        <v>53.662917</v>
+        <v>23.998786</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>85.019199</v>
+        <v>38.021742</v>
       </c>
       <c r="B148" t="n">
-        <v>54.321642</v>
+        <v>24.293377</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>86.769417</v>
+        <v>38.804463</v>
       </c>
       <c r="B149" t="n">
-        <v>54.972802</v>
+        <v>24.584584</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>88.51963499999999</v>
+        <v>39.587184</v>
       </c>
       <c r="B150" t="n">
-        <v>55.616397</v>
+        <v>24.872409</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>90.269854</v>
+        <v>40.369906</v>
       </c>
       <c r="B151" t="n">
-        <v>56.252427</v>
+        <v>25.15685</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>92.020072</v>
+        <v>41.152627</v>
       </c>
       <c r="B152" t="n">
-        <v>56.880893</v>
+        <v>25.437909</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>93.77029</v>
+        <v>41.935348</v>
       </c>
       <c r="B153" t="n">
-        <v>57.501794</v>
+        <v>25.715584</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>95.52050800000001</v>
+        <v>42.71807</v>
       </c>
       <c r="B154" t="n">
-        <v>58.11513</v>
+        <v>25.989876</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>97.270726</v>
+        <v>43.500791</v>
       </c>
       <c r="B155" t="n">
-        <v>58.720901</v>
+        <v>26.260785</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>99.020944</v>
+        <v>44.283513</v>
       </c>
       <c r="B156" t="n">
-        <v>59.319107</v>
+        <v>26.528311</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>100.771162</v>
+        <v>45.066234</v>
       </c>
       <c r="B157" t="n">
-        <v>59.909749</v>
+        <v>26.792454</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>102.521381</v>
+        <v>45.848955</v>
       </c>
       <c r="B158" t="n">
-        <v>60.492825</v>
+        <v>27.053214</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>104.271599</v>
+        <v>46.631677</v>
       </c>
       <c r="B159" t="n">
-        <v>61.068337</v>
+        <v>27.310591</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>106.021817</v>
+        <v>47.414398</v>
       </c>
       <c r="B160" t="n">
-        <v>61.636284</v>
+        <v>27.564584</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>107.772035</v>
+        <v>48.197119</v>
       </c>
       <c r="B161" t="n">
-        <v>62.196666</v>
+        <v>27.815195</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>109.522253</v>
+        <v>48.979841</v>
       </c>
       <c r="B162" t="n">
-        <v>62.749484</v>
+        <v>28.062422</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>111.272471</v>
+        <v>49.762562</v>
       </c>
       <c r="B163" t="n">
-        <v>63.294736</v>
+        <v>28.306267</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>113.022689</v>
+        <v>50.545283</v>
       </c>
       <c r="B164" t="n">
-        <v>63.832424</v>
+        <v>28.546728</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>114.772907</v>
+        <v>51.328005</v>
       </c>
       <c r="B165" t="n">
-        <v>64.36254700000001</v>
+        <v>28.783806</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>116.523126</v>
+        <v>52.110726</v>
       </c>
       <c r="B166" t="n">
-        <v>64.885105</v>
+        <v>29.017501</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118.273344</v>
+        <v>52.893447</v>
       </c>
       <c r="B167" t="n">
-        <v>65.400098</v>
+        <v>29.247813</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120.023562</v>
+        <v>53.676169</v>
       </c>
       <c r="B168" t="n">
-        <v>65.907527</v>
+        <v>29.474742</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121.77378</v>
+        <v>54.45889</v>
       </c>
       <c r="B169" t="n">
-        <v>66.40739000000001</v>
+        <v>29.698288</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>123.523998</v>
+        <v>55.241611</v>
       </c>
       <c r="B170" t="n">
-        <v>66.899689</v>
+        <v>29.918451</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125.274216</v>
+        <v>56.024333</v>
       </c>
       <c r="B171" t="n">
-        <v>67.384423</v>
+        <v>30.13523</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127.024434</v>
+        <v>56.807054</v>
       </c>
       <c r="B172" t="n">
-        <v>67.861592</v>
+        <v>30.348627</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128.774653</v>
+        <v>57.589775</v>
       </c>
       <c r="B173" t="n">
-        <v>68.331197</v>
+        <v>30.55864</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130.524871</v>
+        <v>58.372497</v>
       </c>
       <c r="B174" t="n">
-        <v>68.79323599999999</v>
+        <v>30.765271</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132.275089</v>
+        <v>59.155218</v>
       </c>
       <c r="B175" t="n">
-        <v>69.247711</v>
+        <v>30.968518</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134.025307</v>
+        <v>59.937939</v>
       </c>
       <c r="B176" t="n">
-        <v>69.694621</v>
+        <v>31.168382</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>135.775525</v>
+        <v>60.720661</v>
       </c>
       <c r="B177" t="n">
-        <v>70.133966</v>
+        <v>31.364863</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>137.525743</v>
+        <v>61.503382</v>
       </c>
       <c r="B178" t="n">
-        <v>70.565746</v>
+        <v>31.557961</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>139.275961</v>
+        <v>62.286103</v>
       </c>
       <c r="B179" t="n">
-        <v>70.98996200000001</v>
+        <v>31.747676</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>141.026179</v>
+        <v>63.068825</v>
       </c>
       <c r="B180" t="n">
-        <v>71.406612</v>
+        <v>31.934008</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>142.776398</v>
+        <v>63.851546</v>
       </c>
       <c r="B181" t="n">
-        <v>71.815698</v>
+        <v>32.116957</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>144.526616</v>
+        <v>64.63426699999999</v>
       </c>
       <c r="B182" t="n">
-        <v>72.217219</v>
+        <v>32.296522</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>146.276834</v>
+        <v>65.416989</v>
       </c>
       <c r="B183" t="n">
-        <v>72.611175</v>
+        <v>32.472705</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>148.027052</v>
+        <v>66.19971</v>
       </c>
       <c r="B184" t="n">
-        <v>72.997567</v>
+        <v>32.645504</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>149.77727</v>
+        <v>66.982432</v>
       </c>
       <c r="B185" t="n">
-        <v>73.37639299999999</v>
+        <v>32.814921</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>151.527488</v>
+        <v>67.765153</v>
       </c>
       <c r="B186" t="n">
-        <v>73.74765499999999</v>
+        <v>32.980954</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>153.277706</v>
+        <v>68.54787399999999</v>
       </c>
       <c r="B187" t="n">
-        <v>74.111352</v>
+        <v>33.143604</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>155.027925</v>
+        <v>69.330596</v>
       </c>
       <c r="B188" t="n">
-        <v>74.467484</v>
+        <v>33.302871</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>156.778143</v>
+        <v>70.113317</v>
       </c>
       <c r="B189" t="n">
-        <v>74.816051</v>
+        <v>33.458755</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>158.528361</v>
+        <v>70.896038</v>
       </c>
       <c r="B190" t="n">
-        <v>75.157054</v>
+        <v>33.611256</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>160.278579</v>
+        <v>71.67876</v>
       </c>
       <c r="B191" t="n">
-        <v>75.49049100000001</v>
+        <v>33.760374</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>162.028797</v>
+        <v>72.46148100000001</v>
       </c>
       <c r="B192" t="n">
-        <v>75.81636399999999</v>
+        <v>33.906109</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>163.779015</v>
+        <v>73.244202</v>
       </c>
       <c r="B193" t="n">
-        <v>76.13467199999999</v>
+        <v>34.04846</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>165.529233</v>
+        <v>74.02692399999999</v>
       </c>
       <c r="B194" t="n">
-        <v>76.445415</v>
+        <v>34.187429</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>167.279452</v>
+        <v>74.809645</v>
       </c>
       <c r="B195" t="n">
-        <v>76.748594</v>
+        <v>34.323015</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>169.02967</v>
+        <v>75.592366</v>
       </c>
       <c r="B196" t="n">
-        <v>77.044207</v>
+        <v>34.455217</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>170.779888</v>
+        <v>76.37508800000001</v>
       </c>
       <c r="B197" t="n">
-        <v>77.332256</v>
+        <v>34.584036</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>172.530106</v>
+        <v>77.157809</v>
       </c>
       <c r="B198" t="n">
-        <v>77.61274</v>
+        <v>34.709472</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>174.280324</v>
+        <v>77.94053</v>
       </c>
       <c r="B199" t="n">
-        <v>77.885659</v>
+        <v>34.831526</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>176.030542</v>
+        <v>78.723252</v>
       </c>
       <c r="B200" t="n">
-        <v>78.15101300000001</v>
+        <v>34.950196</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>

--- a/Bell_Nozzle_Divergent_Profile.xlsx
+++ b/Bell_Nozzle_Divergent_Profile.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C200"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.013051</v>
+        <v>0.051248</v>
       </c>
       <c r="B3" t="n">
-        <v>6.459922</v>
+        <v>6.460023</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.026102</v>
+        <v>0.102495</v>
       </c>
       <c r="B4" t="n">
-        <v>6.460026</v>
+        <v>6.46043</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.039152</v>
+        <v>0.153739</v>
       </c>
       <c r="B5" t="n">
-        <v>6.460198</v>
+        <v>6.461107</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.052201</v>
+        <v>0.204978</v>
       </c>
       <c r="B6" t="n">
-        <v>6.46044</v>
+        <v>6.462056</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.065249</v>
+        <v>0.256212</v>
       </c>
       <c r="B7" t="n">
-        <v>6.46075</v>
+        <v>6.463275</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.078294</v>
+        <v>0.307438</v>
       </c>
       <c r="B8" t="n">
-        <v>6.46113</v>
+        <v>6.464766</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.091338</v>
+        <v>0.358656</v>
       </c>
       <c r="B9" t="n">
-        <v>6.461579</v>
+        <v>6.466527</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.104379</v>
+        <v>0.409864</v>
       </c>
       <c r="B10" t="n">
-        <v>6.462096</v>
+        <v>6.46856</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.117417</v>
+        <v>0.461061</v>
       </c>
       <c r="B11" t="n">
-        <v>6.462683</v>
+        <v>6.470863</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.130452</v>
+        <v>0.512244</v>
       </c>
       <c r="B12" t="n">
-        <v>6.463338</v>
+        <v>6.473437</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.143483</v>
+        <v>0.563414</v>
       </c>
       <c r="B13" t="n">
-        <v>6.464063</v>
+        <v>6.476281</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.15651</v>
+        <v>0.614567</v>
       </c>
       <c r="B14" t="n">
-        <v>6.464856</v>
+        <v>6.479396</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.169532</v>
+        <v>0.665703</v>
       </c>
       <c r="B15" t="n">
-        <v>6.465718</v>
+        <v>6.482782</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.18255</v>
+        <v>0.716821</v>
       </c>
       <c r="B16" t="n">
-        <v>6.466649</v>
+        <v>6.486438</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.195563</v>
+        <v>0.767919</v>
       </c>
       <c r="B17" t="n">
-        <v>6.467649</v>
+        <v>6.490364</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.208571</v>
+        <v>0.818995</v>
       </c>
       <c r="B18" t="n">
-        <v>6.468718</v>
+        <v>6.494561</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.221572</v>
+        <v>0.870048</v>
       </c>
       <c r="B19" t="n">
-        <v>6.469855</v>
+        <v>6.499027</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.234568</v>
+        <v>0.921077</v>
       </c>
       <c r="B20" t="n">
-        <v>6.471061</v>
+        <v>6.503764</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.247556</v>
+        <v>0.9720800000000001</v>
       </c>
       <c r="B21" t="n">
-        <v>6.472336</v>
+        <v>6.50877</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.260538</v>
+        <v>1.023056</v>
       </c>
       <c r="B22" t="n">
-        <v>6.47368</v>
+        <v>6.514046</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.273513</v>
+        <v>1.074003</v>
       </c>
       <c r="B23" t="n">
-        <v>6.475092</v>
+        <v>6.519592</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.28648</v>
+        <v>1.124921</v>
       </c>
       <c r="B24" t="n">
-        <v>6.476573</v>
+        <v>6.525407</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.299439</v>
+        <v>1.175807</v>
       </c>
       <c r="B25" t="n">
-        <v>6.478123</v>
+        <v>6.531491</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.312389</v>
+        <v>1.22666</v>
       </c>
       <c r="B26" t="n">
-        <v>6.479741</v>
+        <v>6.537844</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.325331</v>
+        <v>1.277478</v>
       </c>
       <c r="B27" t="n">
-        <v>6.481427</v>
+        <v>6.544466</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.338264</v>
+        <v>1.328261</v>
       </c>
       <c r="B28" t="n">
-        <v>6.483182</v>
+        <v>6.551357</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.351187</v>
+        <v>1.379007</v>
       </c>
       <c r="B29" t="n">
-        <v>6.485005</v>
+        <v>6.558516</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.3641</v>
+        <v>1.429714</v>
       </c>
       <c r="B30" t="n">
-        <v>6.486897</v>
+        <v>6.565944</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.377004</v>
+        <v>1.480381</v>
       </c>
       <c r="B31" t="n">
-        <v>6.488856</v>
+        <v>6.573639</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.389896</v>
+        <v>1.531007</v>
       </c>
       <c r="B32" t="n">
-        <v>6.490884</v>
+        <v>6.581603</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.402778</v>
+        <v>1.58159</v>
       </c>
       <c r="B33" t="n">
-        <v>6.492981</v>
+        <v>6.589834</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.415649</v>
+        <v>1.632129</v>
       </c>
       <c r="B34" t="n">
-        <v>6.495145</v>
+        <v>6.598332</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.428508</v>
+        <v>1.682622</v>
       </c>
       <c r="B35" t="n">
-        <v>6.497377</v>
+        <v>6.607098</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.441355</v>
+        <v>1.733068</v>
       </c>
       <c r="B36" t="n">
-        <v>6.499677</v>
+        <v>6.616131</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.454189</v>
+        <v>1.783465</v>
       </c>
       <c r="B37" t="n">
-        <v>6.502046</v>
+        <v>6.62543</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.467011</v>
+        <v>1.833813</v>
       </c>
       <c r="B38" t="n">
-        <v>6.504482</v>
+        <v>6.634995</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.47982</v>
+        <v>1.884109</v>
       </c>
       <c r="B39" t="n">
-        <v>6.506986</v>
+        <v>6.644827</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.492615</v>
+        <v>1.934353</v>
       </c>
       <c r="B40" t="n">
-        <v>6.509557</v>
+        <v>6.654925</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.505397</v>
+        <v>1.984542</v>
       </c>
       <c r="B41" t="n">
-        <v>6.512196</v>
+        <v>6.665288</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.518164</v>
+        <v>2.034676</v>
       </c>
       <c r="B42" t="n">
-        <v>6.514903</v>
+        <v>6.675917</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.530917</v>
+        <v>2.084753</v>
       </c>
       <c r="B43" t="n">
-        <v>6.517677</v>
+        <v>6.686811</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.543655</v>
+        <v>2.134772</v>
       </c>
       <c r="B44" t="n">
-        <v>6.520519</v>
+        <v>6.697969</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.556378</v>
+        <v>2.184731</v>
       </c>
       <c r="B45" t="n">
-        <v>6.523428</v>
+        <v>6.709392</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.569085</v>
+        <v>2.234629</v>
       </c>
       <c r="B46" t="n">
-        <v>6.526404</v>
+        <v>6.721078</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.581777</v>
+        <v>2.284464</v>
       </c>
       <c r="B47" t="n">
-        <v>6.529448</v>
+        <v>6.733029</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.594452</v>
+        <v>2.334236</v>
       </c>
       <c r="B48" t="n">
-        <v>6.532558</v>
+        <v>6.745243</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.607111</v>
+        <v>2.383942</v>
       </c>
       <c r="B49" t="n">
-        <v>6.535735</v>
+        <v>6.75772</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.619752</v>
+        <v>2.433582</v>
       </c>
       <c r="B50" t="n">
-        <v>6.53898</v>
+        <v>6.770459</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.632376</v>
+        <v>2.483153</v>
       </c>
       <c r="B51" t="n">
-        <v>6.542291</v>
+        <v>6.783461</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.644983</v>
+        <v>2.532655</v>
       </c>
       <c r="B52" t="n">
-        <v>6.545669</v>
+        <v>6.796725</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.657571</v>
+        <v>2.582086</v>
       </c>
       <c r="B53" t="n">
-        <v>6.549113</v>
+        <v>6.810251</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.670141</v>
+        <v>2.631445</v>
       </c>
       <c r="B54" t="n">
-        <v>6.552625</v>
+        <v>6.824038</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.682693</v>
+        <v>2.680731</v>
       </c>
       <c r="B55" t="n">
-        <v>6.556202</v>
+        <v>6.838086</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.695225</v>
+        <v>2.729941</v>
       </c>
       <c r="B56" t="n">
-        <v>6.559846</v>
+        <v>6.852394</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.707738</v>
+        <v>2.779075</v>
       </c>
       <c r="B57" t="n">
-        <v>6.563556</v>
+        <v>6.866962</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.720231</v>
+        <v>2.828131</v>
       </c>
       <c r="B58" t="n">
-        <v>6.567332</v>
+        <v>6.88179</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.732704</v>
+        <v>2.877108</v>
       </c>
       <c r="B59" t="n">
-        <v>6.571174</v>
+        <v>6.896877</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.745156</v>
+        <v>2.926005</v>
       </c>
       <c r="B60" t="n">
-        <v>6.575082</v>
+        <v>6.912223</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.757587</v>
+        <v>2.97482</v>
       </c>
       <c r="B61" t="n">
-        <v>6.579056</v>
+        <v>6.927828</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.769998</v>
+        <v>3.023551</v>
       </c>
       <c r="B62" t="n">
-        <v>6.583096</v>
+        <v>6.94369</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.7823870000000001</v>
+        <v>3.072199</v>
       </c>
       <c r="B63" t="n">
-        <v>6.587201</v>
+        <v>6.95981</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.794753</v>
+        <v>3.12076</v>
       </c>
       <c r="B64" t="n">
-        <v>6.591372</v>
+        <v>6.976187</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.807098</v>
+        <v>3.169233</v>
       </c>
       <c r="B65" t="n">
-        <v>6.595608</v>
+        <v>6.99282</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.81942</v>
+        <v>3.217619</v>
       </c>
       <c r="B66" t="n">
-        <v>6.599909</v>
+        <v>7.00971</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.831719</v>
+        <v>3.265914</v>
       </c>
       <c r="B67" t="n">
-        <v>6.604275</v>
+        <v>7.026855</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.8439950000000001</v>
+        <v>3.314118</v>
       </c>
       <c r="B68" t="n">
-        <v>6.608707</v>
+        <v>7.044256</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.856248</v>
+        <v>3.362229</v>
       </c>
       <c r="B69" t="n">
-        <v>6.613203</v>
+        <v>7.061911</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.868476</v>
+        <v>3.410246</v>
       </c>
       <c r="B70" t="n">
-        <v>6.617764</v>
+        <v>7.079821</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.88068</v>
+        <v>3.458167</v>
       </c>
       <c r="B71" t="n">
-        <v>6.622389</v>
+        <v>7.097984</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.892859</v>
+        <v>3.505992</v>
       </c>
       <c r="B72" t="n">
-        <v>6.627079</v>
+        <v>7.1164</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.905014</v>
+        <v>3.553719</v>
       </c>
       <c r="B73" t="n">
-        <v>6.631834</v>
+        <v>7.135069</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.917143</v>
+        <v>3.601347</v>
       </c>
       <c r="B74" t="n">
-        <v>6.636652</v>
+        <v>7.15399</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.929246</v>
+        <v>3.648873</v>
       </c>
       <c r="B75" t="n">
-        <v>6.641535</v>
+        <v>7.173163</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.941324</v>
+        <v>3.696298</v>
       </c>
       <c r="B76" t="n">
-        <v>6.646482</v>
+        <v>7.192587</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.953375</v>
+        <v>3.743619</v>
       </c>
       <c r="B77" t="n">
-        <v>6.651492</v>
+        <v>7.212261</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.965399</v>
+        <v>3.790836</v>
       </c>
       <c r="B78" t="n">
-        <v>6.656566</v>
+        <v>7.232186</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.977397</v>
+        <v>3.837946</v>
       </c>
       <c r="B79" t="n">
-        <v>6.661704</v>
+        <v>7.25236</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.989367</v>
+        <v>3.884949</v>
       </c>
       <c r="B80" t="n">
-        <v>6.666905</v>
+        <v>7.272782</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1.00131</v>
+        <v>3.931844</v>
       </c>
       <c r="B81" t="n">
-        <v>6.672169</v>
+        <v>7.293454</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1.013224</v>
+        <v>3.978628</v>
       </c>
       <c r="B82" t="n">
-        <v>6.677496</v>
+        <v>7.314372</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.02511</v>
+        <v>4.025301</v>
       </c>
       <c r="B83" t="n">
-        <v>6.682887</v>
+        <v>7.335538</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.036968</v>
+        <v>4.071862</v>
       </c>
       <c r="B84" t="n">
-        <v>6.68834</v>
+        <v>7.356951</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.048796</v>
+        <v>4.118309</v>
       </c>
       <c r="B85" t="n">
-        <v>6.693855</v>
+        <v>7.378609</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.060595</v>
+        <v>4.16464</v>
       </c>
       <c r="B86" t="n">
-        <v>6.699434</v>
+        <v>7.400513</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1.072364</v>
+        <v>4.210855</v>
       </c>
       <c r="B87" t="n">
-        <v>6.705074</v>
+        <v>7.422662</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.084104</v>
+        <v>4.256952</v>
       </c>
       <c r="B88" t="n">
-        <v>6.710777</v>
+        <v>7.445054</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.095813</v>
+        <v>4.302931</v>
       </c>
       <c r="B89" t="n">
-        <v>6.716541</v>
+        <v>7.46769</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1.107491</v>
+        <v>4.348788</v>
       </c>
       <c r="B90" t="n">
-        <v>6.722368</v>
+        <v>7.490569</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.119139</v>
+        <v>4.394525</v>
       </c>
       <c r="B91" t="n">
-        <v>6.728256</v>
+        <v>7.513691</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.130755</v>
+        <v>4.440138</v>
       </c>
       <c r="B92" t="n">
-        <v>6.734206</v>
+        <v>7.537053</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.14234</v>
+        <v>4.485627</v>
       </c>
       <c r="B93" t="n">
-        <v>6.740217</v>
+        <v>7.560657</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.153892</v>
+        <v>4.53099</v>
       </c>
       <c r="B94" t="n">
-        <v>6.746289</v>
+        <v>7.584501</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.165412</v>
+        <v>4.576227</v>
       </c>
       <c r="B95" t="n">
-        <v>6.752422</v>
+        <v>7.608585</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.1769</v>
+        <v>4.621336</v>
       </c>
       <c r="B96" t="n">
-        <v>6.758617</v>
+        <v>7.632907</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1.188355</v>
+        <v>4.666315</v>
       </c>
       <c r="B97" t="n">
-        <v>6.764871</v>
+        <v>7.657468</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1.199777</v>
+        <v>4.711164</v>
       </c>
       <c r="B98" t="n">
-        <v>6.771187</v>
+        <v>7.682266</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1.211165</v>
+        <v>4.755882</v>
       </c>
       <c r="B99" t="n">
-        <v>6.777562</v>
+        <v>7.707301</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.222519</v>
+        <v>4.800466</v>
       </c>
       <c r="B100" t="n">
-        <v>6.783998</v>
+        <v>7.732572</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1.233839</v>
+        <v>4.844916</v>
       </c>
       <c r="B101" t="n">
-        <v>6.790494</v>
+        <v>7.758079</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2.01656</v>
+        <v>1.233839</v>
       </c>
       <c r="B102" t="n">
-        <v>7.240706</v>
+        <v>6.790494</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2.799281</v>
+        <v>2.01656</v>
       </c>
       <c r="B103" t="n">
-        <v>7.687536</v>
+        <v>7.240706</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>3.582003</v>
+        <v>2.799281</v>
       </c>
       <c r="B104" t="n">
-        <v>8.130983000000001</v>
+        <v>7.687536</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4.364724</v>
+        <v>3.582003</v>
       </c>
       <c r="B105" t="n">
-        <v>8.571046000000001</v>
+        <v>8.130983000000001</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5.147445</v>
+        <v>4.364724</v>
       </c>
       <c r="B106" t="n">
-        <v>9.007726999999999</v>
+        <v>8.571046000000001</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5.930167</v>
+        <v>5.147445</v>
       </c>
       <c r="B107" t="n">
-        <v>9.441024000000001</v>
+        <v>9.007726999999999</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6.712888</v>
+        <v>5.930167</v>
       </c>
       <c r="B108" t="n">
-        <v>9.870939</v>
+        <v>9.441024000000001</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>7.495609</v>
+        <v>6.712888</v>
       </c>
       <c r="B109" t="n">
-        <v>10.29747</v>
+        <v>9.870939</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>8.278331</v>
+        <v>7.495609</v>
       </c>
       <c r="B110" t="n">
-        <v>10.720618</v>
+        <v>10.29747</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>9.061052</v>
+        <v>8.278331</v>
       </c>
       <c r="B111" t="n">
-        <v>11.140383</v>
+        <v>10.720618</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>9.843773000000001</v>
+        <v>9.061052</v>
       </c>
       <c r="B112" t="n">
-        <v>11.556765</v>
+        <v>11.140383</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>10.626495</v>
+        <v>9.843773000000001</v>
       </c>
       <c r="B113" t="n">
-        <v>11.969764</v>
+        <v>11.556765</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>11.409216</v>
+        <v>10.626495</v>
       </c>
       <c r="B114" t="n">
-        <v>12.379379</v>
+        <v>11.969764</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>12.191937</v>
+        <v>11.409216</v>
       </c>
       <c r="B115" t="n">
-        <v>12.785612</v>
+        <v>12.379379</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>12.974659</v>
+        <v>12.191937</v>
       </c>
       <c r="B116" t="n">
-        <v>13.188462</v>
+        <v>12.785612</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>13.75738</v>
+        <v>12.974659</v>
       </c>
       <c r="B117" t="n">
-        <v>13.587928</v>
+        <v>13.188462</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>14.540101</v>
+        <v>13.75738</v>
       </c>
       <c r="B118" t="n">
-        <v>13.984012</v>
+        <v>13.587928</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>15.322823</v>
+        <v>14.540101</v>
       </c>
       <c r="B119" t="n">
-        <v>14.376712</v>
+        <v>13.984012</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>16.105544</v>
+        <v>15.322823</v>
       </c>
       <c r="B120" t="n">
-        <v>14.766029</v>
+        <v>14.376712</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>16.888265</v>
+        <v>16.105544</v>
       </c>
       <c r="B121" t="n">
-        <v>15.151963</v>
+        <v>14.766029</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>17.670987</v>
+        <v>16.888265</v>
       </c>
       <c r="B122" t="n">
-        <v>15.534514</v>
+        <v>15.151963</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>18.453708</v>
+        <v>17.670987</v>
       </c>
       <c r="B123" t="n">
-        <v>15.913682</v>
+        <v>15.534514</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>19.236429</v>
+        <v>18.453708</v>
       </c>
       <c r="B124" t="n">
-        <v>16.289467</v>
+        <v>15.913682</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>20.019151</v>
+        <v>19.236429</v>
       </c>
       <c r="B125" t="n">
-        <v>16.661869</v>
+        <v>16.289467</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>20.801872</v>
+        <v>20.019151</v>
       </c>
       <c r="B126" t="n">
-        <v>17.030888</v>
+        <v>16.661869</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>21.584594</v>
+        <v>20.801872</v>
       </c>
       <c r="B127" t="n">
-        <v>17.396523</v>
+        <v>17.030888</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>22.367315</v>
+        <v>21.584594</v>
       </c>
       <c r="B128" t="n">
-        <v>17.758776</v>
+        <v>17.396523</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>23.150036</v>
+        <v>22.367315</v>
       </c>
       <c r="B129" t="n">
-        <v>18.117645</v>
+        <v>17.758776</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>23.932758</v>
+        <v>23.150036</v>
       </c>
       <c r="B130" t="n">
-        <v>18.473131</v>
+        <v>18.117645</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>24.715479</v>
+        <v>23.932758</v>
       </c>
       <c r="B131" t="n">
-        <v>18.825235</v>
+        <v>18.473131</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>25.4982</v>
+        <v>24.715479</v>
       </c>
       <c r="B132" t="n">
-        <v>19.173955</v>
+        <v>18.825235</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>26.280922</v>
+        <v>25.4982</v>
       </c>
       <c r="B133" t="n">
-        <v>19.519292</v>
+        <v>19.173955</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>27.063643</v>
+        <v>26.280922</v>
       </c>
       <c r="B134" t="n">
-        <v>19.861246</v>
+        <v>19.519292</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>27.846364</v>
+        <v>27.063643</v>
       </c>
       <c r="B135" t="n">
-        <v>20.199817</v>
+        <v>19.861246</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>28.629086</v>
+        <v>27.846364</v>
       </c>
       <c r="B136" t="n">
-        <v>20.535004</v>
+        <v>20.199817</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>29.411807</v>
+        <v>28.629086</v>
       </c>
       <c r="B137" t="n">
-        <v>20.866809</v>
+        <v>20.535004</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>30.194528</v>
+        <v>29.411807</v>
       </c>
       <c r="B138" t="n">
-        <v>21.195231</v>
+        <v>20.866809</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>30.97725</v>
+        <v>30.194528</v>
       </c>
       <c r="B139" t="n">
-        <v>21.520269</v>
+        <v>21.195231</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>31.759971</v>
+        <v>30.97725</v>
       </c>
       <c r="B140" t="n">
-        <v>21.841925</v>
+        <v>21.520269</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>32.542692</v>
+        <v>31.759971</v>
       </c>
       <c r="B141" t="n">
-        <v>22.160197</v>
+        <v>21.841925</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>33.325414</v>
+        <v>32.542692</v>
       </c>
       <c r="B142" t="n">
-        <v>22.475086</v>
+        <v>22.160197</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>34.108135</v>
+        <v>33.325414</v>
       </c>
       <c r="B143" t="n">
-        <v>22.786592</v>
+        <v>22.475086</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>34.890856</v>
+        <v>34.108135</v>
       </c>
       <c r="B144" t="n">
-        <v>23.094715</v>
+        <v>22.786592</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>35.673578</v>
+        <v>34.890856</v>
       </c>
       <c r="B145" t="n">
-        <v>23.399455</v>
+        <v>23.094715</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>36.456299</v>
+        <v>35.673578</v>
       </c>
       <c r="B146" t="n">
-        <v>23.700812</v>
+        <v>23.399455</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>37.23902</v>
+        <v>36.456299</v>
       </c>
       <c r="B147" t="n">
-        <v>23.998786</v>
+        <v>23.700812</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>38.021742</v>
+        <v>37.23902</v>
       </c>
       <c r="B148" t="n">
-        <v>24.293377</v>
+        <v>23.998786</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>38.804463</v>
+        <v>38.021742</v>
       </c>
       <c r="B149" t="n">
-        <v>24.584584</v>
+        <v>24.293377</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>39.587184</v>
+        <v>38.804463</v>
       </c>
       <c r="B150" t="n">
-        <v>24.872409</v>
+        <v>24.584584</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>40.369906</v>
+        <v>39.587184</v>
       </c>
       <c r="B151" t="n">
-        <v>25.15685</v>
+        <v>24.872409</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>41.152627</v>
+        <v>40.369906</v>
       </c>
       <c r="B152" t="n">
-        <v>25.437909</v>
+        <v>25.15685</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41.935348</v>
+        <v>41.152627</v>
       </c>
       <c r="B153" t="n">
-        <v>25.715584</v>
+        <v>25.437909</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>42.71807</v>
+        <v>41.935348</v>
       </c>
       <c r="B154" t="n">
-        <v>25.989876</v>
+        <v>25.715584</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>43.500791</v>
+        <v>42.71807</v>
       </c>
       <c r="B155" t="n">
-        <v>26.260785</v>
+        <v>25.989876</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>44.283513</v>
+        <v>43.500791</v>
       </c>
       <c r="B156" t="n">
-        <v>26.528311</v>
+        <v>26.260785</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>45.066234</v>
+        <v>44.283513</v>
       </c>
       <c r="B157" t="n">
-        <v>26.792454</v>
+        <v>26.528311</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>45.848955</v>
+        <v>45.066234</v>
       </c>
       <c r="B158" t="n">
-        <v>27.053214</v>
+        <v>26.792454</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>46.631677</v>
+        <v>45.848955</v>
       </c>
       <c r="B159" t="n">
-        <v>27.310591</v>
+        <v>27.053214</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>47.414398</v>
+        <v>46.631677</v>
       </c>
       <c r="B160" t="n">
-        <v>27.564584</v>
+        <v>27.310591</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>48.197119</v>
+        <v>47.414398</v>
       </c>
       <c r="B161" t="n">
-        <v>27.815195</v>
+        <v>27.564584</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>48.979841</v>
+        <v>48.197119</v>
       </c>
       <c r="B162" t="n">
-        <v>28.062422</v>
+        <v>27.815195</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>49.762562</v>
+        <v>48.979841</v>
       </c>
       <c r="B163" t="n">
-        <v>28.306267</v>
+        <v>28.062422</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>50.545283</v>
+        <v>49.762562</v>
       </c>
       <c r="B164" t="n">
-        <v>28.546728</v>
+        <v>28.306267</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>51.328005</v>
+        <v>50.545283</v>
       </c>
       <c r="B165" t="n">
-        <v>28.783806</v>
+        <v>28.546728</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>52.110726</v>
+        <v>51.328005</v>
       </c>
       <c r="B166" t="n">
-        <v>29.017501</v>
+        <v>28.783806</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>52.893447</v>
+        <v>52.110726</v>
       </c>
       <c r="B167" t="n">
-        <v>29.247813</v>
+        <v>29.017501</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>53.676169</v>
+        <v>52.893447</v>
       </c>
       <c r="B168" t="n">
-        <v>29.474742</v>
+        <v>29.247813</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>54.45889</v>
+        <v>53.676169</v>
       </c>
       <c r="B169" t="n">
-        <v>29.698288</v>
+        <v>29.474742</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>55.241611</v>
+        <v>54.45889</v>
       </c>
       <c r="B170" t="n">
-        <v>29.918451</v>
+        <v>29.698288</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>56.024333</v>
+        <v>55.241611</v>
       </c>
       <c r="B171" t="n">
-        <v>30.13523</v>
+        <v>29.918451</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>56.807054</v>
+        <v>56.024333</v>
       </c>
       <c r="B172" t="n">
-        <v>30.348627</v>
+        <v>30.13523</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>57.589775</v>
+        <v>56.807054</v>
       </c>
       <c r="B173" t="n">
-        <v>30.55864</v>
+        <v>30.348627</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>58.372497</v>
+        <v>57.589775</v>
       </c>
       <c r="B174" t="n">
-        <v>30.765271</v>
+        <v>30.55864</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>59.155218</v>
+        <v>58.372497</v>
       </c>
       <c r="B175" t="n">
-        <v>30.968518</v>
+        <v>30.765271</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>59.937939</v>
+        <v>59.155218</v>
       </c>
       <c r="B176" t="n">
-        <v>31.168382</v>
+        <v>30.968518</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>60.720661</v>
+        <v>59.937939</v>
       </c>
       <c r="B177" t="n">
-        <v>31.364863</v>
+        <v>31.168382</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>61.503382</v>
+        <v>60.720661</v>
       </c>
       <c r="B178" t="n">
-        <v>31.557961</v>
+        <v>31.364863</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>62.286103</v>
+        <v>61.503382</v>
       </c>
       <c r="B179" t="n">
-        <v>31.747676</v>
+        <v>31.557961</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>63.068825</v>
+        <v>62.286103</v>
       </c>
       <c r="B180" t="n">
-        <v>31.934008</v>
+        <v>31.747676</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>63.851546</v>
+        <v>63.068825</v>
       </c>
       <c r="B181" t="n">
-        <v>32.116957</v>
+        <v>31.934008</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>64.63426699999999</v>
+        <v>63.851546</v>
       </c>
       <c r="B182" t="n">
-        <v>32.296522</v>
+        <v>32.116957</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>65.416989</v>
+        <v>64.63426699999999</v>
       </c>
       <c r="B183" t="n">
-        <v>32.472705</v>
+        <v>32.296522</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>66.19971</v>
+        <v>65.416989</v>
       </c>
       <c r="B184" t="n">
-        <v>32.645504</v>
+        <v>32.472705</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>66.982432</v>
+        <v>66.19971</v>
       </c>
       <c r="B185" t="n">
-        <v>32.814921</v>
+        <v>32.645504</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>67.765153</v>
+        <v>66.982432</v>
       </c>
       <c r="B186" t="n">
-        <v>32.980954</v>
+        <v>32.814921</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>68.54787399999999</v>
+        <v>67.765153</v>
       </c>
       <c r="B187" t="n">
-        <v>33.143604</v>
+        <v>32.980954</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>69.330596</v>
+        <v>68.54787399999999</v>
       </c>
       <c r="B188" t="n">
-        <v>33.302871</v>
+        <v>33.143604</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>70.113317</v>
+        <v>69.330596</v>
       </c>
       <c r="B189" t="n">
-        <v>33.458755</v>
+        <v>33.302871</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>70.896038</v>
+        <v>70.113317</v>
       </c>
       <c r="B190" t="n">
-        <v>33.611256</v>
+        <v>33.458755</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>71.67876</v>
+        <v>70.896038</v>
       </c>
       <c r="B191" t="n">
-        <v>33.760374</v>
+        <v>33.611256</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>72.46148100000001</v>
+        <v>71.67876</v>
       </c>
       <c r="B192" t="n">
-        <v>33.906109</v>
+        <v>33.760374</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>73.244202</v>
+        <v>72.46148100000001</v>
       </c>
       <c r="B193" t="n">
-        <v>34.04846</v>
+        <v>33.906109</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>74.02692399999999</v>
+        <v>73.244202</v>
       </c>
       <c r="B194" t="n">
-        <v>34.187429</v>
+        <v>34.04846</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>74.809645</v>
+        <v>74.02692399999999</v>
       </c>
       <c r="B195" t="n">
-        <v>34.323015</v>
+        <v>34.187429</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>75.592366</v>
+        <v>74.809645</v>
       </c>
       <c r="B196" t="n">
-        <v>34.455217</v>
+        <v>34.323015</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>76.37508800000001</v>
+        <v>75.592366</v>
       </c>
       <c r="B197" t="n">
-        <v>34.584036</v>
+        <v>34.455217</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>77.157809</v>
+        <v>76.37508800000001</v>
       </c>
       <c r="B198" t="n">
-        <v>34.709472</v>
+        <v>34.584036</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>77.94053</v>
+        <v>77.157809</v>
       </c>
       <c r="B199" t="n">
-        <v>34.831526</v>
+        <v>34.709472</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,12 +2625,23 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
+        <v>77.94053</v>
+      </c>
+      <c r="B200" t="n">
+        <v>34.831526</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
         <v>78.723252</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B201" t="n">
         <v>34.950196</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C201" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Bell_Nozzle_Divergent_Profile.xlsx
+++ b/Bell_Nozzle_Divergent_Profile.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.051248</v>
+        <v>0.013051</v>
       </c>
       <c r="B3" t="n">
-        <v>6.460023</v>
+        <v>6.459922</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.102495</v>
+        <v>0.026102</v>
       </c>
       <c r="B4" t="n">
-        <v>6.46043</v>
+        <v>6.460026</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.153739</v>
+        <v>0.039152</v>
       </c>
       <c r="B5" t="n">
-        <v>6.461107</v>
+        <v>6.460198</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.204978</v>
+        <v>0.052201</v>
       </c>
       <c r="B6" t="n">
-        <v>6.462056</v>
+        <v>6.46044</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.256212</v>
+        <v>0.065249</v>
       </c>
       <c r="B7" t="n">
-        <v>6.463275</v>
+        <v>6.46075</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.307438</v>
+        <v>0.078294</v>
       </c>
       <c r="B8" t="n">
-        <v>6.464766</v>
+        <v>6.46113</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.358656</v>
+        <v>0.091338</v>
       </c>
       <c r="B9" t="n">
-        <v>6.466527</v>
+        <v>6.461579</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.409864</v>
+        <v>0.104379</v>
       </c>
       <c r="B10" t="n">
-        <v>6.46856</v>
+        <v>6.462096</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.461061</v>
+        <v>0.117417</v>
       </c>
       <c r="B11" t="n">
-        <v>6.470863</v>
+        <v>6.462683</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.512244</v>
+        <v>0.130452</v>
       </c>
       <c r="B12" t="n">
-        <v>6.473437</v>
+        <v>6.463338</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.563414</v>
+        <v>0.143483</v>
       </c>
       <c r="B13" t="n">
-        <v>6.476281</v>
+        <v>6.464063</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.614567</v>
+        <v>0.15651</v>
       </c>
       <c r="B14" t="n">
-        <v>6.479396</v>
+        <v>6.464856</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.665703</v>
+        <v>0.169532</v>
       </c>
       <c r="B15" t="n">
-        <v>6.482782</v>
+        <v>6.465718</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.716821</v>
+        <v>0.18255</v>
       </c>
       <c r="B16" t="n">
-        <v>6.486438</v>
+        <v>6.466649</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.767919</v>
+        <v>0.195563</v>
       </c>
       <c r="B17" t="n">
-        <v>6.490364</v>
+        <v>6.467649</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.818995</v>
+        <v>0.208571</v>
       </c>
       <c r="B18" t="n">
-        <v>6.494561</v>
+        <v>6.468718</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.870048</v>
+        <v>0.221572</v>
       </c>
       <c r="B19" t="n">
-        <v>6.499027</v>
+        <v>6.469855</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.921077</v>
+        <v>0.234568</v>
       </c>
       <c r="B20" t="n">
-        <v>6.503764</v>
+        <v>6.471061</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.9720800000000001</v>
+        <v>0.247556</v>
       </c>
       <c r="B21" t="n">
-        <v>6.50877</v>
+        <v>6.472336</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1.023056</v>
+        <v>0.260538</v>
       </c>
       <c r="B22" t="n">
-        <v>6.514046</v>
+        <v>6.47368</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.074003</v>
+        <v>0.273513</v>
       </c>
       <c r="B23" t="n">
-        <v>6.519592</v>
+        <v>6.475092</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.124921</v>
+        <v>0.28648</v>
       </c>
       <c r="B24" t="n">
-        <v>6.525407</v>
+        <v>6.476573</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.175807</v>
+        <v>0.299439</v>
       </c>
       <c r="B25" t="n">
-        <v>6.531491</v>
+        <v>6.478123</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.22666</v>
+        <v>0.312389</v>
       </c>
       <c r="B26" t="n">
-        <v>6.537844</v>
+        <v>6.479741</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1.277478</v>
+        <v>0.325331</v>
       </c>
       <c r="B27" t="n">
-        <v>6.544466</v>
+        <v>6.481427</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1.328261</v>
+        <v>0.338264</v>
       </c>
       <c r="B28" t="n">
-        <v>6.551357</v>
+        <v>6.483182</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.379007</v>
+        <v>0.351187</v>
       </c>
       <c r="B29" t="n">
-        <v>6.558516</v>
+        <v>6.485005</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1.429714</v>
+        <v>0.3641</v>
       </c>
       <c r="B30" t="n">
-        <v>6.565944</v>
+        <v>6.486897</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1.480381</v>
+        <v>0.377004</v>
       </c>
       <c r="B31" t="n">
-        <v>6.573639</v>
+        <v>6.488856</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1.531007</v>
+        <v>0.389896</v>
       </c>
       <c r="B32" t="n">
-        <v>6.581603</v>
+        <v>6.490884</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.58159</v>
+        <v>0.402778</v>
       </c>
       <c r="B33" t="n">
-        <v>6.589834</v>
+        <v>6.492981</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1.632129</v>
+        <v>0.415649</v>
       </c>
       <c r="B34" t="n">
-        <v>6.598332</v>
+        <v>6.495145</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.682622</v>
+        <v>0.428508</v>
       </c>
       <c r="B35" t="n">
-        <v>6.607098</v>
+        <v>6.497377</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.733068</v>
+        <v>0.441355</v>
       </c>
       <c r="B36" t="n">
-        <v>6.616131</v>
+        <v>6.499677</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.783465</v>
+        <v>0.454189</v>
       </c>
       <c r="B37" t="n">
-        <v>6.62543</v>
+        <v>6.502046</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.833813</v>
+        <v>0.467011</v>
       </c>
       <c r="B38" t="n">
-        <v>6.634995</v>
+        <v>6.504482</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.884109</v>
+        <v>0.47982</v>
       </c>
       <c r="B39" t="n">
-        <v>6.644827</v>
+        <v>6.506986</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1.934353</v>
+        <v>0.492615</v>
       </c>
       <c r="B40" t="n">
-        <v>6.654925</v>
+        <v>6.509557</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1.984542</v>
+        <v>0.505397</v>
       </c>
       <c r="B41" t="n">
-        <v>6.665288</v>
+        <v>6.512196</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2.034676</v>
+        <v>0.518164</v>
       </c>
       <c r="B42" t="n">
-        <v>6.675917</v>
+        <v>6.514903</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2.084753</v>
+        <v>0.530917</v>
       </c>
       <c r="B43" t="n">
-        <v>6.686811</v>
+        <v>6.517677</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2.134772</v>
+        <v>0.543655</v>
       </c>
       <c r="B44" t="n">
-        <v>6.697969</v>
+        <v>6.520519</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2.184731</v>
+        <v>0.556378</v>
       </c>
       <c r="B45" t="n">
-        <v>6.709392</v>
+        <v>6.523428</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2.234629</v>
+        <v>0.569085</v>
       </c>
       <c r="B46" t="n">
-        <v>6.721078</v>
+        <v>6.526404</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2.284464</v>
+        <v>0.581777</v>
       </c>
       <c r="B47" t="n">
-        <v>6.733029</v>
+        <v>6.529448</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2.334236</v>
+        <v>0.594452</v>
       </c>
       <c r="B48" t="n">
-        <v>6.745243</v>
+        <v>6.532558</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2.383942</v>
+        <v>0.607111</v>
       </c>
       <c r="B49" t="n">
-        <v>6.75772</v>
+        <v>6.535735</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2.433582</v>
+        <v>0.619752</v>
       </c>
       <c r="B50" t="n">
-        <v>6.770459</v>
+        <v>6.53898</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2.483153</v>
+        <v>0.632376</v>
       </c>
       <c r="B51" t="n">
-        <v>6.783461</v>
+        <v>6.542291</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2.532655</v>
+        <v>0.644983</v>
       </c>
       <c r="B52" t="n">
-        <v>6.796725</v>
+        <v>6.545669</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2.582086</v>
+        <v>0.657571</v>
       </c>
       <c r="B53" t="n">
-        <v>6.810251</v>
+        <v>6.549113</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2.631445</v>
+        <v>0.670141</v>
       </c>
       <c r="B54" t="n">
-        <v>6.824038</v>
+        <v>6.552625</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2.680731</v>
+        <v>0.682693</v>
       </c>
       <c r="B55" t="n">
-        <v>6.838086</v>
+        <v>6.556202</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2.729941</v>
+        <v>0.695225</v>
       </c>
       <c r="B56" t="n">
-        <v>6.852394</v>
+        <v>6.559846</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2.779075</v>
+        <v>0.707738</v>
       </c>
       <c r="B57" t="n">
-        <v>6.866962</v>
+        <v>6.563556</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2.828131</v>
+        <v>0.720231</v>
       </c>
       <c r="B58" t="n">
-        <v>6.88179</v>
+        <v>6.567332</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2.877108</v>
+        <v>0.732704</v>
       </c>
       <c r="B59" t="n">
-        <v>6.896877</v>
+        <v>6.571174</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2.926005</v>
+        <v>0.745156</v>
       </c>
       <c r="B60" t="n">
-        <v>6.912223</v>
+        <v>6.575082</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2.97482</v>
+        <v>0.757587</v>
       </c>
       <c r="B61" t="n">
-        <v>6.927828</v>
+        <v>6.579056</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3.023551</v>
+        <v>0.769998</v>
       </c>
       <c r="B62" t="n">
-        <v>6.94369</v>
+        <v>6.583096</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3.072199</v>
+        <v>0.7823870000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>6.95981</v>
+        <v>6.587201</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3.12076</v>
+        <v>0.794753</v>
       </c>
       <c r="B64" t="n">
-        <v>6.976187</v>
+        <v>6.591372</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3.169233</v>
+        <v>0.807098</v>
       </c>
       <c r="B65" t="n">
-        <v>6.99282</v>
+        <v>6.595608</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3.217619</v>
+        <v>0.81942</v>
       </c>
       <c r="B66" t="n">
-        <v>7.00971</v>
+        <v>6.599909</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3.265914</v>
+        <v>0.831719</v>
       </c>
       <c r="B67" t="n">
-        <v>7.026855</v>
+        <v>6.604275</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3.314118</v>
+        <v>0.8439950000000001</v>
       </c>
       <c r="B68" t="n">
-        <v>7.044256</v>
+        <v>6.608707</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3.362229</v>
+        <v>0.856248</v>
       </c>
       <c r="B69" t="n">
-        <v>7.061911</v>
+        <v>6.613203</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>3.410246</v>
+        <v>0.868476</v>
       </c>
       <c r="B70" t="n">
-        <v>7.079821</v>
+        <v>6.617764</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3.458167</v>
+        <v>0.88068</v>
       </c>
       <c r="B71" t="n">
-        <v>7.097984</v>
+        <v>6.622389</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3.505992</v>
+        <v>0.892859</v>
       </c>
       <c r="B72" t="n">
-        <v>7.1164</v>
+        <v>6.627079</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3.553719</v>
+        <v>0.905014</v>
       </c>
       <c r="B73" t="n">
-        <v>7.135069</v>
+        <v>6.631834</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3.601347</v>
+        <v>0.917143</v>
       </c>
       <c r="B74" t="n">
-        <v>7.15399</v>
+        <v>6.636652</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3.648873</v>
+        <v>0.929246</v>
       </c>
       <c r="B75" t="n">
-        <v>7.173163</v>
+        <v>6.641535</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3.696298</v>
+        <v>0.941324</v>
       </c>
       <c r="B76" t="n">
-        <v>7.192587</v>
+        <v>6.646482</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3.743619</v>
+        <v>0.953375</v>
       </c>
       <c r="B77" t="n">
-        <v>7.212261</v>
+        <v>6.651492</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3.790836</v>
+        <v>0.965399</v>
       </c>
       <c r="B78" t="n">
-        <v>7.232186</v>
+        <v>6.656566</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3.837946</v>
+        <v>0.977397</v>
       </c>
       <c r="B79" t="n">
-        <v>7.25236</v>
+        <v>6.661704</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3.884949</v>
+        <v>0.989367</v>
       </c>
       <c r="B80" t="n">
-        <v>7.272782</v>
+        <v>6.666905</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3.931844</v>
+        <v>1.00131</v>
       </c>
       <c r="B81" t="n">
-        <v>7.293454</v>
+        <v>6.672169</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3.978628</v>
+        <v>1.013224</v>
       </c>
       <c r="B82" t="n">
-        <v>7.314372</v>
+        <v>6.677496</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4.025301</v>
+        <v>1.02511</v>
       </c>
       <c r="B83" t="n">
-        <v>7.335538</v>
+        <v>6.682887</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4.071862</v>
+        <v>1.036968</v>
       </c>
       <c r="B84" t="n">
-        <v>7.356951</v>
+        <v>6.68834</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4.118309</v>
+        <v>1.048796</v>
       </c>
       <c r="B85" t="n">
-        <v>7.378609</v>
+        <v>6.693855</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4.16464</v>
+        <v>1.060595</v>
       </c>
       <c r="B86" t="n">
-        <v>7.400513</v>
+        <v>6.699434</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4.210855</v>
+        <v>1.072364</v>
       </c>
       <c r="B87" t="n">
-        <v>7.422662</v>
+        <v>6.705074</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4.256952</v>
+        <v>1.084104</v>
       </c>
       <c r="B88" t="n">
-        <v>7.445054</v>
+        <v>6.710777</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4.302931</v>
+        <v>1.095813</v>
       </c>
       <c r="B89" t="n">
-        <v>7.46769</v>
+        <v>6.716541</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4.348788</v>
+        <v>1.107491</v>
       </c>
       <c r="B90" t="n">
-        <v>7.490569</v>
+        <v>6.722368</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4.394525</v>
+        <v>1.119139</v>
       </c>
       <c r="B91" t="n">
-        <v>7.513691</v>
+        <v>6.728256</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4.440138</v>
+        <v>1.130755</v>
       </c>
       <c r="B92" t="n">
-        <v>7.537053</v>
+        <v>6.734206</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4.485627</v>
+        <v>1.14234</v>
       </c>
       <c r="B93" t="n">
-        <v>7.560657</v>
+        <v>6.740217</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4.53099</v>
+        <v>1.153892</v>
       </c>
       <c r="B94" t="n">
-        <v>7.584501</v>
+        <v>6.746289</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4.576227</v>
+        <v>1.165412</v>
       </c>
       <c r="B95" t="n">
-        <v>7.608585</v>
+        <v>6.752422</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4.621336</v>
+        <v>1.1769</v>
       </c>
       <c r="B96" t="n">
-        <v>7.632907</v>
+        <v>6.758617</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4.666315</v>
+        <v>1.188355</v>
       </c>
       <c r="B97" t="n">
-        <v>7.657468</v>
+        <v>6.764871</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4.711164</v>
+        <v>1.199777</v>
       </c>
       <c r="B98" t="n">
-        <v>7.682266</v>
+        <v>6.771187</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4.755882</v>
+        <v>1.211165</v>
       </c>
       <c r="B99" t="n">
-        <v>7.707301</v>
+        <v>6.777562</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4.800466</v>
+        <v>1.222519</v>
       </c>
       <c r="B100" t="n">
-        <v>7.732572</v>
+        <v>6.783998</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4.844916</v>
+        <v>1.233839</v>
       </c>
       <c r="B101" t="n">
-        <v>7.758079</v>
+        <v>6.790494</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1.233839</v>
+        <v>2.01656</v>
       </c>
       <c r="B102" t="n">
-        <v>6.790494</v>
+        <v>7.240706</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2.01656</v>
+        <v>2.799281</v>
       </c>
       <c r="B103" t="n">
-        <v>7.240706</v>
+        <v>7.687536</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2.799281</v>
+        <v>3.582003</v>
       </c>
       <c r="B104" t="n">
-        <v>7.687536</v>
+        <v>8.130983000000001</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>3.582003</v>
+        <v>4.364724</v>
       </c>
       <c r="B105" t="n">
-        <v>8.130983000000001</v>
+        <v>8.571046000000001</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4.364724</v>
+        <v>5.147445</v>
       </c>
       <c r="B106" t="n">
-        <v>8.571046000000001</v>
+        <v>9.007726999999999</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5.147445</v>
+        <v>5.930167</v>
       </c>
       <c r="B107" t="n">
-        <v>9.007726999999999</v>
+        <v>9.441024000000001</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>5.930167</v>
+        <v>6.712888</v>
       </c>
       <c r="B108" t="n">
-        <v>9.441024000000001</v>
+        <v>9.870939</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6.712888</v>
+        <v>7.495609</v>
       </c>
       <c r="B109" t="n">
-        <v>9.870939</v>
+        <v>10.29747</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>7.495609</v>
+        <v>8.278331</v>
       </c>
       <c r="B110" t="n">
-        <v>10.29747</v>
+        <v>10.720618</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>8.278331</v>
+        <v>9.061052</v>
       </c>
       <c r="B111" t="n">
-        <v>10.720618</v>
+        <v>11.140383</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>9.061052</v>
+        <v>9.843773000000001</v>
       </c>
       <c r="B112" t="n">
-        <v>11.140383</v>
+        <v>11.556765</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>9.843773000000001</v>
+        <v>10.626495</v>
       </c>
       <c r="B113" t="n">
-        <v>11.556765</v>
+        <v>11.969764</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>10.626495</v>
+        <v>11.409216</v>
       </c>
       <c r="B114" t="n">
-        <v>11.969764</v>
+        <v>12.379379</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>11.409216</v>
+        <v>12.191937</v>
       </c>
       <c r="B115" t="n">
-        <v>12.379379</v>
+        <v>12.785612</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>12.191937</v>
+        <v>12.974659</v>
       </c>
       <c r="B116" t="n">
-        <v>12.785612</v>
+        <v>13.188462</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>12.974659</v>
+        <v>13.75738</v>
       </c>
       <c r="B117" t="n">
-        <v>13.188462</v>
+        <v>13.587928</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>13.75738</v>
+        <v>14.540101</v>
       </c>
       <c r="B118" t="n">
-        <v>13.587928</v>
+        <v>13.984012</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>14.540101</v>
+        <v>15.322823</v>
       </c>
       <c r="B119" t="n">
-        <v>13.984012</v>
+        <v>14.376712</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>15.322823</v>
+        <v>16.105544</v>
       </c>
       <c r="B120" t="n">
-        <v>14.376712</v>
+        <v>14.766029</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>16.105544</v>
+        <v>16.888265</v>
       </c>
       <c r="B121" t="n">
-        <v>14.766029</v>
+        <v>15.151963</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>16.888265</v>
+        <v>17.670987</v>
       </c>
       <c r="B122" t="n">
-        <v>15.151963</v>
+        <v>15.534514</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>17.670987</v>
+        <v>18.453708</v>
       </c>
       <c r="B123" t="n">
-        <v>15.534514</v>
+        <v>15.913682</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>18.453708</v>
+        <v>19.236429</v>
       </c>
       <c r="B124" t="n">
-        <v>15.913682</v>
+        <v>16.289467</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>19.236429</v>
+        <v>20.019151</v>
       </c>
       <c r="B125" t="n">
-        <v>16.289467</v>
+        <v>16.661869</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>20.019151</v>
+        <v>20.801872</v>
       </c>
       <c r="B126" t="n">
-        <v>16.661869</v>
+        <v>17.030888</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>20.801872</v>
+        <v>21.584594</v>
       </c>
       <c r="B127" t="n">
-        <v>17.030888</v>
+        <v>17.396523</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>21.584594</v>
+        <v>22.367315</v>
       </c>
       <c r="B128" t="n">
-        <v>17.396523</v>
+        <v>17.758776</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>22.367315</v>
+        <v>23.150036</v>
       </c>
       <c r="B129" t="n">
-        <v>17.758776</v>
+        <v>18.117645</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>23.150036</v>
+        <v>23.932758</v>
       </c>
       <c r="B130" t="n">
-        <v>18.117645</v>
+        <v>18.473131</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>23.932758</v>
+        <v>24.715479</v>
       </c>
       <c r="B131" t="n">
-        <v>18.473131</v>
+        <v>18.825235</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>24.715479</v>
+        <v>25.4982</v>
       </c>
       <c r="B132" t="n">
-        <v>18.825235</v>
+        <v>19.173955</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>25.4982</v>
+        <v>26.280922</v>
       </c>
       <c r="B133" t="n">
-        <v>19.173955</v>
+        <v>19.519292</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>26.280922</v>
+        <v>27.063643</v>
       </c>
       <c r="B134" t="n">
-        <v>19.519292</v>
+        <v>19.861246</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>27.063643</v>
+        <v>27.846364</v>
       </c>
       <c r="B135" t="n">
-        <v>19.861246</v>
+        <v>20.199817</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>27.846364</v>
+        <v>28.629086</v>
       </c>
       <c r="B136" t="n">
-        <v>20.199817</v>
+        <v>20.535004</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>28.629086</v>
+        <v>29.411807</v>
       </c>
       <c r="B137" t="n">
-        <v>20.535004</v>
+        <v>20.866809</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>29.411807</v>
+        <v>30.194528</v>
       </c>
       <c r="B138" t="n">
-        <v>20.866809</v>
+        <v>21.195231</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>30.194528</v>
+        <v>30.97725</v>
       </c>
       <c r="B139" t="n">
-        <v>21.195231</v>
+        <v>21.520269</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>30.97725</v>
+        <v>31.759971</v>
       </c>
       <c r="B140" t="n">
-        <v>21.520269</v>
+        <v>21.841925</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>31.759971</v>
+        <v>32.542692</v>
       </c>
       <c r="B141" t="n">
-        <v>21.841925</v>
+        <v>22.160197</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>32.542692</v>
+        <v>33.325414</v>
       </c>
       <c r="B142" t="n">
-        <v>22.160197</v>
+        <v>22.475086</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>33.325414</v>
+        <v>34.108135</v>
       </c>
       <c r="B143" t="n">
-        <v>22.475086</v>
+        <v>22.786592</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>34.108135</v>
+        <v>34.890856</v>
       </c>
       <c r="B144" t="n">
-        <v>22.786592</v>
+        <v>23.094715</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>34.890856</v>
+        <v>35.673578</v>
       </c>
       <c r="B145" t="n">
-        <v>23.094715</v>
+        <v>23.399455</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>35.673578</v>
+        <v>36.456299</v>
       </c>
       <c r="B146" t="n">
-        <v>23.399455</v>
+        <v>23.700812</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>36.456299</v>
+        <v>37.23902</v>
       </c>
       <c r="B147" t="n">
-        <v>23.700812</v>
+        <v>23.998786</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>37.23902</v>
+        <v>38.021742</v>
       </c>
       <c r="B148" t="n">
-        <v>23.998786</v>
+        <v>24.293377</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>38.021742</v>
+        <v>38.804463</v>
       </c>
       <c r="B149" t="n">
-        <v>24.293377</v>
+        <v>24.584584</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>38.804463</v>
+        <v>39.587184</v>
       </c>
       <c r="B150" t="n">
-        <v>24.584584</v>
+        <v>24.872409</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>39.587184</v>
+        <v>40.369906</v>
       </c>
       <c r="B151" t="n">
-        <v>24.872409</v>
+        <v>25.15685</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>40.369906</v>
+        <v>41.152627</v>
       </c>
       <c r="B152" t="n">
-        <v>25.15685</v>
+        <v>25.437909</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41.152627</v>
+        <v>41.935348</v>
       </c>
       <c r="B153" t="n">
-        <v>25.437909</v>
+        <v>25.715584</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>41.935348</v>
+        <v>42.71807</v>
       </c>
       <c r="B154" t="n">
-        <v>25.715584</v>
+        <v>25.989876</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>42.71807</v>
+        <v>43.500791</v>
       </c>
       <c r="B155" t="n">
-        <v>25.989876</v>
+        <v>26.260785</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>43.500791</v>
+        <v>44.283513</v>
       </c>
       <c r="B156" t="n">
-        <v>26.260785</v>
+        <v>26.528311</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>44.283513</v>
+        <v>45.066234</v>
       </c>
       <c r="B157" t="n">
-        <v>26.528311</v>
+        <v>26.792454</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>45.066234</v>
+        <v>45.848955</v>
       </c>
       <c r="B158" t="n">
-        <v>26.792454</v>
+        <v>27.053214</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>45.848955</v>
+        <v>46.631677</v>
       </c>
       <c r="B159" t="n">
-        <v>27.053214</v>
+        <v>27.310591</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>46.631677</v>
+        <v>47.414398</v>
       </c>
       <c r="B160" t="n">
-        <v>27.310591</v>
+        <v>27.564584</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>47.414398</v>
+        <v>48.197119</v>
       </c>
       <c r="B161" t="n">
-        <v>27.564584</v>
+        <v>27.815195</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>48.197119</v>
+        <v>48.979841</v>
       </c>
       <c r="B162" t="n">
-        <v>27.815195</v>
+        <v>28.062422</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>48.979841</v>
+        <v>49.762562</v>
       </c>
       <c r="B163" t="n">
-        <v>28.062422</v>
+        <v>28.306267</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>49.762562</v>
+        <v>50.545283</v>
       </c>
       <c r="B164" t="n">
-        <v>28.306267</v>
+        <v>28.546728</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>50.545283</v>
+        <v>51.328005</v>
       </c>
       <c r="B165" t="n">
-        <v>28.546728</v>
+        <v>28.783806</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>51.328005</v>
+        <v>52.110726</v>
       </c>
       <c r="B166" t="n">
-        <v>28.783806</v>
+        <v>29.017501</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>52.110726</v>
+        <v>52.893447</v>
       </c>
       <c r="B167" t="n">
-        <v>29.017501</v>
+        <v>29.247813</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>52.893447</v>
+        <v>53.676169</v>
       </c>
       <c r="B168" t="n">
-        <v>29.247813</v>
+        <v>29.474742</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>53.676169</v>
+        <v>54.45889</v>
       </c>
       <c r="B169" t="n">
-        <v>29.474742</v>
+        <v>29.698288</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>54.45889</v>
+        <v>55.241611</v>
       </c>
       <c r="B170" t="n">
-        <v>29.698288</v>
+        <v>29.918451</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>55.241611</v>
+        <v>56.024333</v>
       </c>
       <c r="B171" t="n">
-        <v>29.918451</v>
+        <v>30.13523</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>56.024333</v>
+        <v>56.807054</v>
       </c>
       <c r="B172" t="n">
-        <v>30.13523</v>
+        <v>30.348627</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>56.807054</v>
+        <v>57.589775</v>
       </c>
       <c r="B173" t="n">
-        <v>30.348627</v>
+        <v>30.55864</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>57.589775</v>
+        <v>58.372497</v>
       </c>
       <c r="B174" t="n">
-        <v>30.55864</v>
+        <v>30.765271</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>58.372497</v>
+        <v>59.155218</v>
       </c>
       <c r="B175" t="n">
-        <v>30.765271</v>
+        <v>30.968518</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>59.155218</v>
+        <v>59.937939</v>
       </c>
       <c r="B176" t="n">
-        <v>30.968518</v>
+        <v>31.168382</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>59.937939</v>
+        <v>60.720661</v>
       </c>
       <c r="B177" t="n">
-        <v>31.168382</v>
+        <v>31.364863</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>60.720661</v>
+        <v>61.503382</v>
       </c>
       <c r="B178" t="n">
-        <v>31.364863</v>
+        <v>31.557961</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>61.503382</v>
+        <v>62.286103</v>
       </c>
       <c r="B179" t="n">
-        <v>31.557961</v>
+        <v>31.747676</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>62.286103</v>
+        <v>63.068825</v>
       </c>
       <c r="B180" t="n">
-        <v>31.747676</v>
+        <v>31.934008</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>63.068825</v>
+        <v>63.851546</v>
       </c>
       <c r="B181" t="n">
-        <v>31.934008</v>
+        <v>32.116957</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>63.851546</v>
+        <v>64.63426699999999</v>
       </c>
       <c r="B182" t="n">
-        <v>32.116957</v>
+        <v>32.296522</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>64.63426699999999</v>
+        <v>65.416989</v>
       </c>
       <c r="B183" t="n">
-        <v>32.296522</v>
+        <v>32.472705</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>65.416989</v>
+        <v>66.19971</v>
       </c>
       <c r="B184" t="n">
-        <v>32.472705</v>
+        <v>32.645504</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>66.19971</v>
+        <v>66.982432</v>
       </c>
       <c r="B185" t="n">
-        <v>32.645504</v>
+        <v>32.814921</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>66.982432</v>
+        <v>67.765153</v>
       </c>
       <c r="B186" t="n">
-        <v>32.814921</v>
+        <v>32.980954</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>67.765153</v>
+        <v>68.54787399999999</v>
       </c>
       <c r="B187" t="n">
-        <v>32.980954</v>
+        <v>33.143604</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>68.54787399999999</v>
+        <v>69.330596</v>
       </c>
       <c r="B188" t="n">
-        <v>33.143604</v>
+        <v>33.302871</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>69.330596</v>
+        <v>70.113317</v>
       </c>
       <c r="B189" t="n">
-        <v>33.302871</v>
+        <v>33.458755</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>70.113317</v>
+        <v>70.896038</v>
       </c>
       <c r="B190" t="n">
-        <v>33.458755</v>
+        <v>33.611256</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>70.896038</v>
+        <v>71.67876</v>
       </c>
       <c r="B191" t="n">
-        <v>33.611256</v>
+        <v>33.760374</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>71.67876</v>
+        <v>72.46148100000001</v>
       </c>
       <c r="B192" t="n">
-        <v>33.760374</v>
+        <v>33.906109</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>72.46148100000001</v>
+        <v>73.244202</v>
       </c>
       <c r="B193" t="n">
-        <v>33.906109</v>
+        <v>34.04846</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>73.244202</v>
+        <v>74.02692399999999</v>
       </c>
       <c r="B194" t="n">
-        <v>34.04846</v>
+        <v>34.187429</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>74.02692399999999</v>
+        <v>74.809645</v>
       </c>
       <c r="B195" t="n">
-        <v>34.187429</v>
+        <v>34.323015</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>74.809645</v>
+        <v>75.592366</v>
       </c>
       <c r="B196" t="n">
-        <v>34.323015</v>
+        <v>34.455217</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>75.592366</v>
+        <v>76.37508800000001</v>
       </c>
       <c r="B197" t="n">
-        <v>34.455217</v>
+        <v>34.584036</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>76.37508800000001</v>
+        <v>77.157809</v>
       </c>
       <c r="B198" t="n">
-        <v>34.584036</v>
+        <v>34.709472</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>77.157809</v>
+        <v>77.94053</v>
       </c>
       <c r="B199" t="n">
-        <v>34.709472</v>
+        <v>34.831526</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,23 +2625,12 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>77.94053</v>
+        <v>78.723252</v>
       </c>
       <c r="B200" t="n">
-        <v>34.831526</v>
+        <v>34.950196</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>78.723252</v>
-      </c>
-      <c r="B201" t="n">
-        <v>34.950196</v>
-      </c>
-      <c r="C201" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Bell_Nozzle_Divergent_Profile.xlsx
+++ b/Bell_Nozzle_Divergent_Profile.xlsx
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.459888</v>
+        <v>11.188854</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.013051</v>
+        <v>0.022605</v>
       </c>
       <c r="B3" t="n">
-        <v>6.459922</v>
+        <v>11.188913</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.026102</v>
+        <v>0.04521</v>
       </c>
       <c r="B4" t="n">
-        <v>6.460026</v>
+        <v>11.189093</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.039152</v>
+        <v>0.067813</v>
       </c>
       <c r="B5" t="n">
-        <v>6.460198</v>
+        <v>11.189392</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.052201</v>
+        <v>0.090415</v>
       </c>
       <c r="B6" t="n">
-        <v>6.46044</v>
+        <v>11.18981</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.065249</v>
+        <v>0.113014</v>
       </c>
       <c r="B7" t="n">
-        <v>6.46075</v>
+        <v>11.190348</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.078294</v>
+        <v>0.13561</v>
       </c>
       <c r="B8" t="n">
-        <v>6.46113</v>
+        <v>11.191005</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.091338</v>
+        <v>0.158202</v>
       </c>
       <c r="B9" t="n">
-        <v>6.461579</v>
+        <v>11.191782</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.104379</v>
+        <v>0.180789</v>
       </c>
       <c r="B10" t="n">
-        <v>6.462096</v>
+        <v>11.192679</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.117417</v>
+        <v>0.203372</v>
       </c>
       <c r="B11" t="n">
-        <v>6.462683</v>
+        <v>11.193695</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.130452</v>
+        <v>0.225949</v>
       </c>
       <c r="B12" t="n">
-        <v>6.463338</v>
+        <v>11.19483</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.143483</v>
+        <v>0.248519</v>
       </c>
       <c r="B13" t="n">
-        <v>6.464063</v>
+        <v>11.196085</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.15651</v>
+        <v>0.271083</v>
       </c>
       <c r="B14" t="n">
-        <v>6.464856</v>
+        <v>11.197459</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.169532</v>
+        <v>0.293639</v>
       </c>
       <c r="B15" t="n">
-        <v>6.465718</v>
+        <v>11.198952</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.18255</v>
+        <v>0.316187</v>
       </c>
       <c r="B16" t="n">
-        <v>6.466649</v>
+        <v>11.200565</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.195563</v>
+        <v>0.338726</v>
       </c>
       <c r="B17" t="n">
-        <v>6.467649</v>
+        <v>11.202297</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.208571</v>
+        <v>0.361255</v>
       </c>
       <c r="B18" t="n">
-        <v>6.468718</v>
+        <v>11.204148</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.221572</v>
+        <v>0.383774</v>
       </c>
       <c r="B19" t="n">
-        <v>6.469855</v>
+        <v>11.206118</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.234568</v>
+        <v>0.406283</v>
       </c>
       <c r="B20" t="n">
-        <v>6.471061</v>
+        <v>11.208207</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.247556</v>
+        <v>0.42878</v>
       </c>
       <c r="B21" t="n">
-        <v>6.472336</v>
+        <v>11.210415</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.260538</v>
+        <v>0.451266</v>
       </c>
       <c r="B22" t="n">
-        <v>6.47368</v>
+        <v>11.212743</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.273513</v>
+        <v>0.473738</v>
       </c>
       <c r="B23" t="n">
-        <v>6.475092</v>
+        <v>11.215189</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.28648</v>
+        <v>0.496198</v>
       </c>
       <c r="B24" t="n">
-        <v>6.476573</v>
+        <v>11.217754</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.299439</v>
+        <v>0.518643</v>
       </c>
       <c r="B25" t="n">
-        <v>6.478123</v>
+        <v>11.220437</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.312389</v>
+        <v>0.5410740000000001</v>
       </c>
       <c r="B26" t="n">
-        <v>6.479741</v>
+        <v>11.22324</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.325331</v>
+        <v>0.56349</v>
       </c>
       <c r="B27" t="n">
-        <v>6.481427</v>
+        <v>11.226161</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.338264</v>
+        <v>0.58589</v>
       </c>
       <c r="B28" t="n">
-        <v>6.483182</v>
+        <v>11.2292</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.351187</v>
+        <v>0.608274</v>
       </c>
       <c r="B29" t="n">
-        <v>6.485005</v>
+        <v>11.232358</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.3641</v>
+        <v>0.630641</v>
       </c>
       <c r="B30" t="n">
-        <v>6.486897</v>
+        <v>11.235634</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.377004</v>
+        <v>0.65299</v>
       </c>
       <c r="B31" t="n">
-        <v>6.488856</v>
+        <v>11.239029</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.389896</v>
+        <v>0.67532</v>
       </c>
       <c r="B32" t="n">
-        <v>6.490884</v>
+        <v>11.242541</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.402778</v>
+        <v>0.697632</v>
       </c>
       <c r="B33" t="n">
-        <v>6.492981</v>
+        <v>11.246172</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.415649</v>
+        <v>0.719925</v>
       </c>
       <c r="B34" t="n">
-        <v>6.495145</v>
+        <v>11.249921</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.428508</v>
+        <v>0.742197</v>
       </c>
       <c r="B35" t="n">
-        <v>6.497377</v>
+        <v>11.253787</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.441355</v>
+        <v>0.764448</v>
       </c>
       <c r="B36" t="n">
-        <v>6.499677</v>
+        <v>11.257772</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.454189</v>
+        <v>0.786679</v>
       </c>
       <c r="B37" t="n">
-        <v>6.502046</v>
+        <v>11.261873</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.467011</v>
+        <v>0.808887</v>
       </c>
       <c r="B38" t="n">
-        <v>6.504482</v>
+        <v>11.266093</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.47982</v>
+        <v>0.831072</v>
       </c>
       <c r="B39" t="n">
-        <v>6.506986</v>
+        <v>11.27043</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.492615</v>
+        <v>0.853234</v>
       </c>
       <c r="B40" t="n">
-        <v>6.509557</v>
+        <v>11.274884</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.505397</v>
+        <v>0.875373</v>
       </c>
       <c r="B41" t="n">
-        <v>6.512196</v>
+        <v>11.279455</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.518164</v>
+        <v>0.897487</v>
       </c>
       <c r="B42" t="n">
-        <v>6.514903</v>
+        <v>11.284143</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.530917</v>
+        <v>0.919575</v>
       </c>
       <c r="B43" t="n">
-        <v>6.517677</v>
+        <v>11.288948</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.543655</v>
+        <v>0.941639</v>
       </c>
       <c r="B44" t="n">
-        <v>6.520519</v>
+        <v>11.29387</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.556378</v>
+        <v>0.9636749999999999</v>
       </c>
       <c r="B45" t="n">
-        <v>6.523428</v>
+        <v>11.298909</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.569085</v>
+        <v>0.985685</v>
       </c>
       <c r="B46" t="n">
-        <v>6.526404</v>
+        <v>11.304064</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.581777</v>
+        <v>1.007667</v>
       </c>
       <c r="B47" t="n">
-        <v>6.529448</v>
+        <v>11.309335</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.594452</v>
+        <v>1.029621</v>
       </c>
       <c r="B48" t="n">
-        <v>6.532558</v>
+        <v>11.314722</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.607111</v>
+        <v>1.051546</v>
       </c>
       <c r="B49" t="n">
-        <v>6.535735</v>
+        <v>11.320226</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.619752</v>
+        <v>1.073442</v>
       </c>
       <c r="B50" t="n">
-        <v>6.53898</v>
+        <v>11.325845</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.632376</v>
+        <v>1.095308</v>
       </c>
       <c r="B51" t="n">
-        <v>6.542291</v>
+        <v>11.33158</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.644983</v>
+        <v>1.117143</v>
       </c>
       <c r="B52" t="n">
-        <v>6.545669</v>
+        <v>11.337431</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.657571</v>
+        <v>1.138947</v>
       </c>
       <c r="B53" t="n">
-        <v>6.549113</v>
+        <v>11.343397</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.670141</v>
+        <v>1.160719</v>
       </c>
       <c r="B54" t="n">
-        <v>6.552625</v>
+        <v>11.349479</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.682693</v>
+        <v>1.182458</v>
       </c>
       <c r="B55" t="n">
-        <v>6.556202</v>
+        <v>11.355675</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.695225</v>
+        <v>1.204165</v>
       </c>
       <c r="B56" t="n">
-        <v>6.559846</v>
+        <v>11.361986</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.707738</v>
+        <v>1.225838</v>
       </c>
       <c r="B57" t="n">
-        <v>6.563556</v>
+        <v>11.368412</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.720231</v>
+        <v>1.247476</v>
       </c>
       <c r="B58" t="n">
-        <v>6.567332</v>
+        <v>11.374953</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.732704</v>
+        <v>1.26908</v>
       </c>
       <c r="B59" t="n">
-        <v>6.571174</v>
+        <v>11.381608</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.745156</v>
+        <v>1.290648</v>
       </c>
       <c r="B60" t="n">
-        <v>6.575082</v>
+        <v>11.388377</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.757587</v>
+        <v>1.31218</v>
       </c>
       <c r="B61" t="n">
-        <v>6.579056</v>
+        <v>11.39526</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.769998</v>
+        <v>1.333675</v>
       </c>
       <c r="B62" t="n">
-        <v>6.583096</v>
+        <v>11.402257</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.7823870000000001</v>
+        <v>1.355133</v>
       </c>
       <c r="B63" t="n">
-        <v>6.587201</v>
+        <v>11.409367</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.794753</v>
+        <v>1.376553</v>
       </c>
       <c r="B64" t="n">
-        <v>6.591372</v>
+        <v>11.416591</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.807098</v>
+        <v>1.397935</v>
       </c>
       <c r="B65" t="n">
-        <v>6.595608</v>
+        <v>11.423928</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.81942</v>
+        <v>1.419277</v>
       </c>
       <c r="B66" t="n">
-        <v>6.599909</v>
+        <v>11.431378</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.831719</v>
+        <v>1.44058</v>
       </c>
       <c r="B67" t="n">
-        <v>6.604275</v>
+        <v>11.438941</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.8439950000000001</v>
+        <v>1.461843</v>
       </c>
       <c r="B68" t="n">
-        <v>6.608707</v>
+        <v>11.446616</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.856248</v>
+        <v>1.483064</v>
       </c>
       <c r="B69" t="n">
-        <v>6.613203</v>
+        <v>11.454403</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.868476</v>
+        <v>1.504244</v>
       </c>
       <c r="B70" t="n">
-        <v>6.617764</v>
+        <v>11.462303</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.88068</v>
+        <v>1.525382</v>
       </c>
       <c r="B71" t="n">
-        <v>6.622389</v>
+        <v>11.470315</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.892859</v>
+        <v>1.546478</v>
       </c>
       <c r="B72" t="n">
-        <v>6.627079</v>
+        <v>11.478438</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.905014</v>
+        <v>1.56753</v>
       </c>
       <c r="B73" t="n">
-        <v>6.631834</v>
+        <v>11.486673</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.917143</v>
+        <v>1.588538</v>
       </c>
       <c r="B74" t="n">
-        <v>6.636652</v>
+        <v>11.495019</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.929246</v>
+        <v>1.609502</v>
       </c>
       <c r="B75" t="n">
-        <v>6.641535</v>
+        <v>11.503476</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.941324</v>
+        <v>1.630421</v>
       </c>
       <c r="B76" t="n">
-        <v>6.646482</v>
+        <v>11.512044</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.953375</v>
+        <v>1.651294</v>
       </c>
       <c r="B77" t="n">
-        <v>6.651492</v>
+        <v>11.520722</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.965399</v>
+        <v>1.672121</v>
       </c>
       <c r="B78" t="n">
-        <v>6.656566</v>
+        <v>11.529511</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.977397</v>
+        <v>1.692901</v>
       </c>
       <c r="B79" t="n">
-        <v>6.661704</v>
+        <v>11.53841</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.989367</v>
+        <v>1.713634</v>
       </c>
       <c r="B80" t="n">
-        <v>6.666905</v>
+        <v>11.547418</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1.00131</v>
+        <v>1.734319</v>
       </c>
       <c r="B81" t="n">
-        <v>6.672169</v>
+        <v>11.556536</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1.013224</v>
+        <v>1.754955</v>
       </c>
       <c r="B82" t="n">
-        <v>6.677496</v>
+        <v>11.565763</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.02511</v>
+        <v>1.775543</v>
       </c>
       <c r="B83" t="n">
-        <v>6.682887</v>
+        <v>11.575099</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.036968</v>
+        <v>1.79608</v>
       </c>
       <c r="B84" t="n">
-        <v>6.68834</v>
+        <v>11.584544</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.048796</v>
+        <v>1.816568</v>
       </c>
       <c r="B85" t="n">
-        <v>6.693855</v>
+        <v>11.594098</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.060595</v>
+        <v>1.837005</v>
       </c>
       <c r="B86" t="n">
-        <v>6.699434</v>
+        <v>11.603759</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1.072364</v>
+        <v>1.85739</v>
       </c>
       <c r="B87" t="n">
-        <v>6.705074</v>
+        <v>11.613529</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.084104</v>
+        <v>1.877723</v>
       </c>
       <c r="B88" t="n">
-        <v>6.710777</v>
+        <v>11.623406</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.095813</v>
+        <v>1.898004</v>
       </c>
       <c r="B89" t="n">
-        <v>6.716541</v>
+        <v>11.633391</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1.107491</v>
+        <v>1.918231</v>
       </c>
       <c r="B90" t="n">
-        <v>6.722368</v>
+        <v>11.643483</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.119139</v>
+        <v>1.938405</v>
       </c>
       <c r="B91" t="n">
-        <v>6.728256</v>
+        <v>11.653681</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.130755</v>
+        <v>1.958525</v>
       </c>
       <c r="B92" t="n">
-        <v>6.734206</v>
+        <v>11.663987</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.14234</v>
+        <v>1.97859</v>
       </c>
       <c r="B93" t="n">
-        <v>6.740217</v>
+        <v>11.674398</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.153892</v>
+        <v>1.9986</v>
       </c>
       <c r="B94" t="n">
-        <v>6.746289</v>
+        <v>11.684916</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.165412</v>
+        <v>2.018554</v>
       </c>
       <c r="B95" t="n">
-        <v>6.752422</v>
+        <v>11.695539</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.1769</v>
+        <v>2.038451</v>
       </c>
       <c r="B96" t="n">
-        <v>6.758617</v>
+        <v>11.706267</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1.188355</v>
+        <v>2.058291</v>
       </c>
       <c r="B97" t="n">
-        <v>6.764871</v>
+        <v>11.717101</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1.199777</v>
+        <v>2.078074</v>
       </c>
       <c r="B98" t="n">
-        <v>6.771187</v>
+        <v>11.728039</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1.211165</v>
+        <v>2.097798</v>
       </c>
       <c r="B99" t="n">
-        <v>6.777562</v>
+        <v>11.739082</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.222519</v>
+        <v>2.117464</v>
       </c>
       <c r="B100" t="n">
-        <v>6.783998</v>
+        <v>11.750229</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1.233839</v>
+        <v>2.137071</v>
       </c>
       <c r="B101" t="n">
-        <v>6.790494</v>
+        <v>11.76148</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2.01656</v>
+        <v>3.492784</v>
       </c>
       <c r="B102" t="n">
-        <v>7.240706</v>
+        <v>12.541271</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2.799281</v>
+        <v>4.848497</v>
       </c>
       <c r="B103" t="n">
-        <v>7.687536</v>
+        <v>13.315203</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>3.582003</v>
+        <v>6.20421</v>
       </c>
       <c r="B104" t="n">
-        <v>8.130983000000001</v>
+        <v>14.083275</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4.364724</v>
+        <v>7.559924</v>
       </c>
       <c r="B105" t="n">
-        <v>8.571046000000001</v>
+        <v>14.845488</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5.147445</v>
+        <v>8.915637</v>
       </c>
       <c r="B106" t="n">
-        <v>9.007726999999999</v>
+        <v>15.601841</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5.930167</v>
+        <v>10.27135</v>
       </c>
       <c r="B107" t="n">
-        <v>9.441024000000001</v>
+        <v>16.352334</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6.712888</v>
+        <v>11.627063</v>
       </c>
       <c r="B108" t="n">
-        <v>9.870939</v>
+        <v>17.096967</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>7.495609</v>
+        <v>12.982776</v>
       </c>
       <c r="B109" t="n">
-        <v>10.29747</v>
+        <v>17.835741</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>8.278331</v>
+        <v>14.338489</v>
       </c>
       <c r="B110" t="n">
-        <v>10.720618</v>
+        <v>18.568655</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>9.061052</v>
+        <v>15.694202</v>
       </c>
       <c r="B111" t="n">
-        <v>11.140383</v>
+        <v>19.295709</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>9.843773000000001</v>
+        <v>17.049916</v>
       </c>
       <c r="B112" t="n">
-        <v>11.556765</v>
+        <v>20.016904</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>10.626495</v>
+        <v>18.405629</v>
       </c>
       <c r="B113" t="n">
-        <v>11.969764</v>
+        <v>20.732239</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>11.409216</v>
+        <v>19.761342</v>
       </c>
       <c r="B114" t="n">
-        <v>12.379379</v>
+        <v>21.441714</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>12.191937</v>
+        <v>21.117055</v>
       </c>
       <c r="B115" t="n">
-        <v>12.785612</v>
+        <v>22.14533</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>12.974659</v>
+        <v>22.472768</v>
       </c>
       <c r="B116" t="n">
-        <v>13.188462</v>
+        <v>22.843086</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>13.75738</v>
+        <v>23.828481</v>
       </c>
       <c r="B117" t="n">
-        <v>13.587928</v>
+        <v>23.534982</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>14.540101</v>
+        <v>25.184194</v>
       </c>
       <c r="B118" t="n">
-        <v>13.984012</v>
+        <v>24.221019</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>15.322823</v>
+        <v>26.539908</v>
       </c>
       <c r="B119" t="n">
-        <v>14.376712</v>
+        <v>24.901195</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>16.105544</v>
+        <v>27.895621</v>
       </c>
       <c r="B120" t="n">
-        <v>14.766029</v>
+        <v>25.575513</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>16.888265</v>
+        <v>29.251334</v>
       </c>
       <c r="B121" t="n">
-        <v>15.151963</v>
+        <v>26.24397</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>17.670987</v>
+        <v>30.607047</v>
       </c>
       <c r="B122" t="n">
-        <v>15.534514</v>
+        <v>26.906568</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>18.453708</v>
+        <v>31.96276</v>
       </c>
       <c r="B123" t="n">
-        <v>15.913682</v>
+        <v>27.563306</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>19.236429</v>
+        <v>33.318473</v>
       </c>
       <c r="B124" t="n">
-        <v>16.289467</v>
+        <v>28.214185</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>20.019151</v>
+        <v>34.674186</v>
       </c>
       <c r="B125" t="n">
-        <v>16.661869</v>
+        <v>28.859203</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>20.801872</v>
+        <v>36.029899</v>
       </c>
       <c r="B126" t="n">
-        <v>17.030888</v>
+        <v>29.498363</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>21.584594</v>
+        <v>37.385613</v>
       </c>
       <c r="B127" t="n">
-        <v>17.396523</v>
+        <v>30.131662</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>22.367315</v>
+        <v>38.741326</v>
       </c>
       <c r="B128" t="n">
-        <v>17.758776</v>
+        <v>30.759102</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>23.150036</v>
+        <v>40.097039</v>
       </c>
       <c r="B129" t="n">
-        <v>18.117645</v>
+        <v>31.380682</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>23.932758</v>
+        <v>41.452752</v>
       </c>
       <c r="B130" t="n">
-        <v>18.473131</v>
+        <v>31.996402</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>24.715479</v>
+        <v>42.808465</v>
       </c>
       <c r="B131" t="n">
-        <v>18.825235</v>
+        <v>32.606263</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>25.4982</v>
+        <v>44.164178</v>
       </c>
       <c r="B132" t="n">
-        <v>19.173955</v>
+        <v>33.210264</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>26.280922</v>
+        <v>45.519891</v>
       </c>
       <c r="B133" t="n">
-        <v>19.519292</v>
+        <v>33.808405</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>27.063643</v>
+        <v>46.875605</v>
       </c>
       <c r="B134" t="n">
-        <v>19.861246</v>
+        <v>34.400687</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>27.846364</v>
+        <v>48.231318</v>
       </c>
       <c r="B135" t="n">
-        <v>20.199817</v>
+        <v>34.987109</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>28.629086</v>
+        <v>49.587031</v>
       </c>
       <c r="B136" t="n">
-        <v>20.535004</v>
+        <v>35.567671</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>29.411807</v>
+        <v>50.942744</v>
       </c>
       <c r="B137" t="n">
-        <v>20.866809</v>
+        <v>36.142374</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>30.194528</v>
+        <v>52.298457</v>
       </c>
       <c r="B138" t="n">
-        <v>21.195231</v>
+        <v>36.711216</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>30.97725</v>
+        <v>53.65417</v>
       </c>
       <c r="B139" t="n">
-        <v>21.520269</v>
+        <v>37.2742</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>31.759971</v>
+        <v>55.009883</v>
       </c>
       <c r="B140" t="n">
-        <v>21.841925</v>
+        <v>37.831323</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>32.542692</v>
+        <v>56.365597</v>
       </c>
       <c r="B141" t="n">
-        <v>22.160197</v>
+        <v>38.382587</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>33.325414</v>
+        <v>57.72131</v>
       </c>
       <c r="B142" t="n">
-        <v>22.475086</v>
+        <v>38.927991</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>34.108135</v>
+        <v>59.077023</v>
       </c>
       <c r="B143" t="n">
-        <v>22.786592</v>
+        <v>39.467536</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>34.890856</v>
+        <v>60.432736</v>
       </c>
       <c r="B144" t="n">
-        <v>23.094715</v>
+        <v>40.00122</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>35.673578</v>
+        <v>61.788449</v>
       </c>
       <c r="B145" t="n">
-        <v>23.399455</v>
+        <v>40.529046</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>36.456299</v>
+        <v>63.144162</v>
       </c>
       <c r="B146" t="n">
-        <v>23.700812</v>
+        <v>41.051011</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>37.23902</v>
+        <v>64.499875</v>
       </c>
       <c r="B147" t="n">
-        <v>23.998786</v>
+        <v>41.567117</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>38.021742</v>
+        <v>65.85558899999999</v>
       </c>
       <c r="B148" t="n">
-        <v>24.293377</v>
+        <v>42.077363</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>38.804463</v>
+        <v>67.211302</v>
       </c>
       <c r="B149" t="n">
-        <v>24.584584</v>
+        <v>42.581749</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>39.587184</v>
+        <v>68.567015</v>
       </c>
       <c r="B150" t="n">
-        <v>24.872409</v>
+        <v>43.080276</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>40.369906</v>
+        <v>69.92272800000001</v>
       </c>
       <c r="B151" t="n">
-        <v>25.15685</v>
+        <v>43.572943</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>41.152627</v>
+        <v>71.278441</v>
       </c>
       <c r="B152" t="n">
-        <v>25.437909</v>
+        <v>44.05975</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41.935348</v>
+        <v>72.634154</v>
       </c>
       <c r="B153" t="n">
-        <v>25.715584</v>
+        <v>44.540698</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>42.71807</v>
+        <v>73.989867</v>
       </c>
       <c r="B154" t="n">
-        <v>25.989876</v>
+        <v>45.015786</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>43.500791</v>
+        <v>75.34558</v>
       </c>
       <c r="B155" t="n">
-        <v>26.260785</v>
+        <v>45.485014</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>44.283513</v>
+        <v>76.701294</v>
       </c>
       <c r="B156" t="n">
-        <v>26.528311</v>
+        <v>45.948383</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>45.066234</v>
+        <v>78.057007</v>
       </c>
       <c r="B157" t="n">
-        <v>26.792454</v>
+        <v>46.405892</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>45.848955</v>
+        <v>79.41271999999999</v>
       </c>
       <c r="B158" t="n">
-        <v>27.053214</v>
+        <v>46.857541</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>46.631677</v>
+        <v>80.768433</v>
       </c>
       <c r="B159" t="n">
-        <v>27.310591</v>
+        <v>47.30333</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>47.414398</v>
+        <v>82.124146</v>
       </c>
       <c r="B160" t="n">
-        <v>27.564584</v>
+        <v>47.74326</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>48.197119</v>
+        <v>83.479859</v>
       </c>
       <c r="B161" t="n">
-        <v>27.815195</v>
+        <v>48.177331</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>48.979841</v>
+        <v>84.835572</v>
       </c>
       <c r="B162" t="n">
-        <v>28.062422</v>
+        <v>48.605541</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>49.762562</v>
+        <v>86.19128600000001</v>
       </c>
       <c r="B163" t="n">
-        <v>28.306267</v>
+        <v>49.027892</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>50.545283</v>
+        <v>87.546999</v>
       </c>
       <c r="B164" t="n">
-        <v>28.546728</v>
+        <v>49.444383</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>51.328005</v>
+        <v>88.90271199999999</v>
       </c>
       <c r="B165" t="n">
-        <v>28.783806</v>
+        <v>49.855014</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>52.110726</v>
+        <v>90.258425</v>
       </c>
       <c r="B166" t="n">
-        <v>29.017501</v>
+        <v>50.259786</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>52.893447</v>
+        <v>91.614138</v>
       </c>
       <c r="B167" t="n">
-        <v>29.247813</v>
+        <v>50.658698</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>53.676169</v>
+        <v>92.96985100000001</v>
       </c>
       <c r="B168" t="n">
-        <v>29.474742</v>
+        <v>51.051751</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>54.45889</v>
+        <v>94.325564</v>
       </c>
       <c r="B169" t="n">
-        <v>29.698288</v>
+        <v>51.438943</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>55.241611</v>
+        <v>95.68127800000001</v>
       </c>
       <c r="B170" t="n">
-        <v>29.918451</v>
+        <v>51.820276</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>56.024333</v>
+        <v>97.036991</v>
       </c>
       <c r="B171" t="n">
-        <v>30.13523</v>
+        <v>52.19575</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>56.807054</v>
+        <v>98.39270399999999</v>
       </c>
       <c r="B172" t="n">
-        <v>30.348627</v>
+        <v>52.565363</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>57.589775</v>
+        <v>99.748417</v>
       </c>
       <c r="B173" t="n">
-        <v>30.55864</v>
+        <v>52.929117</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>58.372497</v>
+        <v>101.10413</v>
       </c>
       <c r="B174" t="n">
-        <v>30.765271</v>
+        <v>53.287012</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>59.155218</v>
+        <v>102.459843</v>
       </c>
       <c r="B175" t="n">
-        <v>30.968518</v>
+        <v>53.639046</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>59.937939</v>
+        <v>103.815556</v>
       </c>
       <c r="B176" t="n">
-        <v>31.168382</v>
+        <v>53.985221</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>60.720661</v>
+        <v>105.171269</v>
       </c>
       <c r="B177" t="n">
-        <v>31.364863</v>
+        <v>54.325536</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>61.503382</v>
+        <v>106.526983</v>
       </c>
       <c r="B178" t="n">
-        <v>31.557961</v>
+        <v>54.659992</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>62.286103</v>
+        <v>107.882696</v>
       </c>
       <c r="B179" t="n">
-        <v>31.747676</v>
+        <v>54.988588</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>63.068825</v>
+        <v>109.238409</v>
       </c>
       <c r="B180" t="n">
-        <v>31.934008</v>
+        <v>55.311324</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>63.851546</v>
+        <v>110.594122</v>
       </c>
       <c r="B181" t="n">
-        <v>32.116957</v>
+        <v>55.628201</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>64.63426699999999</v>
+        <v>111.949835</v>
       </c>
       <c r="B182" t="n">
-        <v>32.296522</v>
+        <v>55.939217</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>65.416989</v>
+        <v>113.305548</v>
       </c>
       <c r="B183" t="n">
-        <v>32.472705</v>
+        <v>56.244375</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>66.19971</v>
+        <v>114.661261</v>
       </c>
       <c r="B184" t="n">
-        <v>32.645504</v>
+        <v>56.543672</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>66.982432</v>
+        <v>116.016975</v>
       </c>
       <c r="B185" t="n">
-        <v>32.814921</v>
+        <v>56.83711</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>67.765153</v>
+        <v>117.372688</v>
       </c>
       <c r="B186" t="n">
-        <v>32.980954</v>
+        <v>57.124688</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>68.54787399999999</v>
+        <v>118.728401</v>
       </c>
       <c r="B187" t="n">
-        <v>33.143604</v>
+        <v>57.406406</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>69.330596</v>
+        <v>120.084114</v>
       </c>
       <c r="B188" t="n">
-        <v>33.302871</v>
+        <v>57.682265</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>70.113317</v>
+        <v>121.439827</v>
       </c>
       <c r="B189" t="n">
-        <v>33.458755</v>
+        <v>57.952264</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>70.896038</v>
+        <v>122.79554</v>
       </c>
       <c r="B190" t="n">
-        <v>33.611256</v>
+        <v>58.216403</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>71.67876</v>
+        <v>124.151253</v>
       </c>
       <c r="B191" t="n">
-        <v>33.760374</v>
+        <v>58.474683</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>72.46148100000001</v>
+        <v>125.506967</v>
       </c>
       <c r="B192" t="n">
-        <v>33.906109</v>
+        <v>58.727103</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>73.244202</v>
+        <v>126.86268</v>
       </c>
       <c r="B193" t="n">
-        <v>34.04846</v>
+        <v>58.973663</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>74.02692399999999</v>
+        <v>128.218393</v>
       </c>
       <c r="B194" t="n">
-        <v>34.187429</v>
+        <v>59.214364</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>74.809645</v>
+        <v>129.574106</v>
       </c>
       <c r="B195" t="n">
-        <v>34.323015</v>
+        <v>59.449205</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>75.592366</v>
+        <v>130.929819</v>
       </c>
       <c r="B196" t="n">
-        <v>34.455217</v>
+        <v>59.678186</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>76.37508800000001</v>
+        <v>132.285532</v>
       </c>
       <c r="B197" t="n">
-        <v>34.584036</v>
+        <v>59.901308</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>77.157809</v>
+        <v>133.641245</v>
       </c>
       <c r="B198" t="n">
-        <v>34.709472</v>
+        <v>60.11857</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>77.94053</v>
+        <v>134.996959</v>
       </c>
       <c r="B199" t="n">
-        <v>34.831526</v>
+        <v>60.329972</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>78.723252</v>
+        <v>136.352672</v>
       </c>
       <c r="B200" t="n">
-        <v>34.950196</v>
+        <v>60.535515</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>

--- a/Bell_Nozzle_Divergent_Profile.xlsx
+++ b/Bell_Nozzle_Divergent_Profile.xlsx
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.188854</v>
+        <v>18.465557</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.022605</v>
+        <v>0.037307</v>
       </c>
       <c r="B3" t="n">
-        <v>11.188913</v>
+        <v>18.465655</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04521</v>
+        <v>0.074612</v>
       </c>
       <c r="B4" t="n">
-        <v>11.189093</v>
+        <v>18.465951</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.067813</v>
+        <v>0.111916</v>
       </c>
       <c r="B5" t="n">
-        <v>11.189392</v>
+        <v>18.466444</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.090415</v>
+        <v>0.149216</v>
       </c>
       <c r="B6" t="n">
-        <v>11.18981</v>
+        <v>18.467135</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.113014</v>
+        <v>0.186513</v>
       </c>
       <c r="B7" t="n">
-        <v>11.190348</v>
+        <v>18.468023</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.13561</v>
+        <v>0.223804</v>
       </c>
       <c r="B8" t="n">
-        <v>11.191005</v>
+        <v>18.469108</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.158202</v>
+        <v>0.261089</v>
       </c>
       <c r="B9" t="n">
-        <v>11.191782</v>
+        <v>18.47039</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.180789</v>
+        <v>0.298366</v>
       </c>
       <c r="B10" t="n">
-        <v>11.192679</v>
+        <v>18.47187</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.203372</v>
+        <v>0.335635</v>
       </c>
       <c r="B11" t="n">
-        <v>11.193695</v>
+        <v>18.473546</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.225949</v>
+        <v>0.372895</v>
       </c>
       <c r="B12" t="n">
-        <v>11.19483</v>
+        <v>18.47542</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.248519</v>
+        <v>0.410144</v>
       </c>
       <c r="B13" t="n">
-        <v>11.196085</v>
+        <v>18.477491</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.271083</v>
+        <v>0.447382</v>
       </c>
       <c r="B14" t="n">
-        <v>11.197459</v>
+        <v>18.479758</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.293639</v>
+        <v>0.484608</v>
       </c>
       <c r="B15" t="n">
-        <v>11.198952</v>
+        <v>18.482223</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.316187</v>
+        <v>0.52182</v>
       </c>
       <c r="B16" t="n">
-        <v>11.200565</v>
+        <v>18.484884</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.338726</v>
+        <v>0.559017</v>
       </c>
       <c r="B17" t="n">
-        <v>11.202297</v>
+        <v>18.487743</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.361255</v>
+        <v>0.596198</v>
       </c>
       <c r="B18" t="n">
-        <v>11.204148</v>
+        <v>18.490797</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.383774</v>
+        <v>0.633363</v>
       </c>
       <c r="B19" t="n">
-        <v>11.206118</v>
+        <v>18.494049</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.406283</v>
+        <v>0.6705100000000001</v>
       </c>
       <c r="B20" t="n">
-        <v>11.208207</v>
+        <v>18.497497</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.42878</v>
+        <v>0.707639</v>
       </c>
       <c r="B21" t="n">
-        <v>11.210415</v>
+        <v>18.501141</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.451266</v>
+        <v>0.744747</v>
       </c>
       <c r="B22" t="n">
-        <v>11.212743</v>
+        <v>18.504982</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.473738</v>
+        <v>0.7818349999999999</v>
       </c>
       <c r="B23" t="n">
-        <v>11.215189</v>
+        <v>18.509019</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.496198</v>
+        <v>0.818901</v>
       </c>
       <c r="B24" t="n">
-        <v>11.217754</v>
+        <v>18.513252</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.518643</v>
+        <v>0.855944</v>
       </c>
       <c r="B25" t="n">
-        <v>11.220437</v>
+        <v>18.517681</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5410740000000001</v>
+        <v>0.892963</v>
       </c>
       <c r="B26" t="n">
-        <v>11.22324</v>
+        <v>18.522306</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.56349</v>
+        <v>0.929957</v>
       </c>
       <c r="B27" t="n">
-        <v>11.226161</v>
+        <v>18.527127</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.58589</v>
+        <v>0.966925</v>
       </c>
       <c r="B28" t="n">
-        <v>11.2292</v>
+        <v>18.532143</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.608274</v>
+        <v>1.003866</v>
       </c>
       <c r="B29" t="n">
-        <v>11.232358</v>
+        <v>18.537355</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.630641</v>
+        <v>1.040779</v>
       </c>
       <c r="B30" t="n">
-        <v>11.235634</v>
+        <v>18.542761</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.65299</v>
+        <v>1.077663</v>
       </c>
       <c r="B31" t="n">
-        <v>11.239029</v>
+        <v>18.548364</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.67532</v>
+        <v>1.114517</v>
       </c>
       <c r="B32" t="n">
-        <v>11.242541</v>
+        <v>18.554161</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.697632</v>
+        <v>1.15134</v>
       </c>
       <c r="B33" t="n">
-        <v>11.246172</v>
+        <v>18.560153</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.719925</v>
+        <v>1.18813</v>
       </c>
       <c r="B34" t="n">
-        <v>11.249921</v>
+        <v>18.566339</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.742197</v>
+        <v>1.224887</v>
       </c>
       <c r="B35" t="n">
-        <v>11.253787</v>
+        <v>18.57272</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.764448</v>
+        <v>1.26161</v>
       </c>
       <c r="B36" t="n">
-        <v>11.257772</v>
+        <v>18.579296</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.786679</v>
+        <v>1.298297</v>
       </c>
       <c r="B37" t="n">
-        <v>11.261873</v>
+        <v>18.586065</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.808887</v>
+        <v>1.334948</v>
       </c>
       <c r="B38" t="n">
-        <v>11.266093</v>
+        <v>18.593029</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.831072</v>
+        <v>1.371562</v>
       </c>
       <c r="B39" t="n">
-        <v>11.27043</v>
+        <v>18.600186</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.853234</v>
+        <v>1.408138</v>
       </c>
       <c r="B40" t="n">
-        <v>11.274884</v>
+        <v>18.607537</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.875373</v>
+        <v>1.444674</v>
       </c>
       <c r="B41" t="n">
-        <v>11.279455</v>
+        <v>18.615081</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.897487</v>
+        <v>1.48117</v>
       </c>
       <c r="B42" t="n">
-        <v>11.284143</v>
+        <v>18.622818</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.919575</v>
+        <v>1.517624</v>
       </c>
       <c r="B43" t="n">
-        <v>11.288948</v>
+        <v>18.630748</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.941639</v>
+        <v>1.554036</v>
       </c>
       <c r="B44" t="n">
-        <v>11.29387</v>
+        <v>18.638871</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9636749999999999</v>
+        <v>1.590404</v>
       </c>
       <c r="B45" t="n">
-        <v>11.298909</v>
+        <v>18.647186</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.985685</v>
+        <v>1.626728</v>
       </c>
       <c r="B46" t="n">
-        <v>11.304064</v>
+        <v>18.655694</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.007667</v>
+        <v>1.663006</v>
       </c>
       <c r="B47" t="n">
-        <v>11.309335</v>
+        <v>18.664393</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1.029621</v>
+        <v>1.699238</v>
       </c>
       <c r="B48" t="n">
-        <v>11.314722</v>
+        <v>18.673285</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1.051546</v>
+        <v>1.735423</v>
       </c>
       <c r="B49" t="n">
-        <v>11.320226</v>
+        <v>18.682367</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.073442</v>
+        <v>1.771558</v>
       </c>
       <c r="B50" t="n">
-        <v>11.325845</v>
+        <v>18.691641</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.095308</v>
+        <v>1.807645</v>
       </c>
       <c r="B51" t="n">
-        <v>11.33158</v>
+        <v>18.701106</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.117143</v>
+        <v>1.84368</v>
       </c>
       <c r="B52" t="n">
-        <v>11.337431</v>
+        <v>18.710762</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.138947</v>
+        <v>1.879664</v>
       </c>
       <c r="B53" t="n">
-        <v>11.343397</v>
+        <v>18.720608</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.160719</v>
+        <v>1.915596</v>
       </c>
       <c r="B54" t="n">
-        <v>11.349479</v>
+        <v>18.730645</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.182458</v>
+        <v>1.951474</v>
       </c>
       <c r="B55" t="n">
-        <v>11.355675</v>
+        <v>18.740871</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.204165</v>
+        <v>1.987297</v>
       </c>
       <c r="B56" t="n">
-        <v>11.361986</v>
+        <v>18.751287</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.225838</v>
+        <v>2.023065</v>
       </c>
       <c r="B57" t="n">
-        <v>11.368412</v>
+        <v>18.761892</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.247476</v>
+        <v>2.058776</v>
       </c>
       <c r="B58" t="n">
-        <v>11.374953</v>
+        <v>18.772686</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.26908</v>
+        <v>2.09443</v>
       </c>
       <c r="B59" t="n">
-        <v>11.381608</v>
+        <v>18.783669</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.290648</v>
+        <v>2.130025</v>
       </c>
       <c r="B60" t="n">
-        <v>11.388377</v>
+        <v>18.79484</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.31218</v>
+        <v>2.16556</v>
       </c>
       <c r="B61" t="n">
-        <v>11.39526</v>
+        <v>18.8062</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.333675</v>
+        <v>2.201035</v>
       </c>
       <c r="B62" t="n">
-        <v>11.402257</v>
+        <v>18.817747</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.355133</v>
+        <v>2.236448</v>
       </c>
       <c r="B63" t="n">
-        <v>11.409367</v>
+        <v>18.829482</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.376553</v>
+        <v>2.271799</v>
       </c>
       <c r="B64" t="n">
-        <v>11.416591</v>
+        <v>18.841404</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.397935</v>
+        <v>2.307086</v>
       </c>
       <c r="B65" t="n">
-        <v>11.423928</v>
+        <v>18.853512</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.419277</v>
+        <v>2.342309</v>
       </c>
       <c r="B66" t="n">
-        <v>11.431378</v>
+        <v>18.865807</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.44058</v>
+        <v>2.377466</v>
       </c>
       <c r="B67" t="n">
-        <v>11.438941</v>
+        <v>18.878288</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.461843</v>
+        <v>2.412556</v>
       </c>
       <c r="B68" t="n">
-        <v>11.446616</v>
+        <v>18.890955</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.483064</v>
+        <v>2.447579</v>
       </c>
       <c r="B69" t="n">
-        <v>11.454403</v>
+        <v>18.903808</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.504244</v>
+        <v>2.482534</v>
       </c>
       <c r="B70" t="n">
-        <v>11.462303</v>
+        <v>18.916845</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.525382</v>
+        <v>2.517419</v>
       </c>
       <c r="B71" t="n">
-        <v>11.470315</v>
+        <v>18.930067</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1.546478</v>
+        <v>2.552234</v>
       </c>
       <c r="B72" t="n">
-        <v>11.478438</v>
+        <v>18.943474</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1.56753</v>
+        <v>2.586977</v>
       </c>
       <c r="B73" t="n">
-        <v>11.486673</v>
+        <v>18.957064</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1.588538</v>
+        <v>2.621648</v>
       </c>
       <c r="B74" t="n">
-        <v>11.495019</v>
+        <v>18.970838</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1.609502</v>
+        <v>2.656246</v>
       </c>
       <c r="B75" t="n">
-        <v>11.503476</v>
+        <v>18.984795</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1.630421</v>
+        <v>2.69077</v>
       </c>
       <c r="B76" t="n">
-        <v>11.512044</v>
+        <v>18.998935</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1.651294</v>
+        <v>2.725218</v>
       </c>
       <c r="B77" t="n">
-        <v>11.520722</v>
+        <v>19.013257</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1.672121</v>
+        <v>2.75959</v>
       </c>
       <c r="B78" t="n">
-        <v>11.529511</v>
+        <v>19.027761</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1.692901</v>
+        <v>2.793884</v>
       </c>
       <c r="B79" t="n">
-        <v>11.53841</v>
+        <v>19.042447</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1.713634</v>
+        <v>2.828101</v>
       </c>
       <c r="B80" t="n">
-        <v>11.547418</v>
+        <v>19.057314</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1.734319</v>
+        <v>2.862238</v>
       </c>
       <c r="B81" t="n">
-        <v>11.556536</v>
+        <v>19.072362</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1.754955</v>
+        <v>2.896296</v>
       </c>
       <c r="B82" t="n">
-        <v>11.565763</v>
+        <v>19.08759</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.775543</v>
+        <v>2.930272</v>
       </c>
       <c r="B83" t="n">
-        <v>11.575099</v>
+        <v>19.102998</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.79608</v>
+        <v>2.964167</v>
       </c>
       <c r="B84" t="n">
-        <v>11.584544</v>
+        <v>19.118586</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.816568</v>
+        <v>2.997978</v>
       </c>
       <c r="B85" t="n">
-        <v>11.594098</v>
+        <v>19.134352</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.837005</v>
+        <v>3.031706</v>
       </c>
       <c r="B86" t="n">
-        <v>11.603759</v>
+        <v>19.150298</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1.85739</v>
+        <v>3.065349</v>
       </c>
       <c r="B87" t="n">
-        <v>11.613529</v>
+        <v>19.166421</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.877723</v>
+        <v>3.098906</v>
       </c>
       <c r="B88" t="n">
-        <v>11.623406</v>
+        <v>19.182722</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.898004</v>
+        <v>3.132376</v>
       </c>
       <c r="B89" t="n">
-        <v>11.633391</v>
+        <v>19.1992</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1.918231</v>
+        <v>3.165759</v>
       </c>
       <c r="B90" t="n">
-        <v>11.643483</v>
+        <v>19.215855</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.938405</v>
+        <v>3.199053</v>
       </c>
       <c r="B91" t="n">
-        <v>11.653681</v>
+        <v>19.232687</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.958525</v>
+        <v>3.232258</v>
       </c>
       <c r="B92" t="n">
-        <v>11.663987</v>
+        <v>19.249694</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.97859</v>
+        <v>3.265372</v>
       </c>
       <c r="B93" t="n">
-        <v>11.674398</v>
+        <v>19.266876</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.9986</v>
+        <v>3.298395</v>
       </c>
       <c r="B94" t="n">
-        <v>11.684916</v>
+        <v>19.284234</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2.018554</v>
+        <v>3.331326</v>
       </c>
       <c r="B95" t="n">
-        <v>11.695539</v>
+        <v>19.301766</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2.038451</v>
+        <v>3.364163</v>
       </c>
       <c r="B96" t="n">
-        <v>11.706267</v>
+        <v>19.319472</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2.058291</v>
+        <v>3.396907</v>
       </c>
       <c r="B97" t="n">
-        <v>11.717101</v>
+        <v>19.337351</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2.078074</v>
+        <v>3.429555</v>
       </c>
       <c r="B98" t="n">
-        <v>11.728039</v>
+        <v>19.355403</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2.097798</v>
+        <v>3.462108</v>
       </c>
       <c r="B99" t="n">
-        <v>11.739082</v>
+        <v>19.373628</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2.117464</v>
+        <v>3.494563</v>
       </c>
       <c r="B100" t="n">
-        <v>11.750229</v>
+        <v>19.392024</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2.137071</v>
+        <v>3.526921</v>
       </c>
       <c r="B101" t="n">
-        <v>11.76148</v>
+        <v>19.410592</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>3.492784</v>
+        <v>5.433395</v>
       </c>
       <c r="B102" t="n">
-        <v>12.541271</v>
+        <v>20.507175</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4.848497</v>
+        <v>7.339869</v>
       </c>
       <c r="B103" t="n">
-        <v>13.315203</v>
+        <v>21.595518</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6.20421</v>
+        <v>9.246342</v>
       </c>
       <c r="B104" t="n">
-        <v>14.083275</v>
+        <v>22.675621</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>7.559924</v>
+        <v>11.152816</v>
       </c>
       <c r="B105" t="n">
-        <v>14.845488</v>
+        <v>23.747483</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>8.915637</v>
+        <v>13.05929</v>
       </c>
       <c r="B106" t="n">
-        <v>15.601841</v>
+        <v>24.811105</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>10.27135</v>
+        <v>14.965763</v>
       </c>
       <c r="B107" t="n">
-        <v>16.352334</v>
+        <v>25.866487</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>11.627063</v>
+        <v>16.872237</v>
       </c>
       <c r="B108" t="n">
-        <v>17.096967</v>
+        <v>26.913629</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>12.982776</v>
+        <v>18.778711</v>
       </c>
       <c r="B109" t="n">
-        <v>17.835741</v>
+        <v>27.952531</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>14.338489</v>
+        <v>20.685184</v>
       </c>
       <c r="B110" t="n">
-        <v>18.568655</v>
+        <v>28.983192</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>15.694202</v>
+        <v>22.591658</v>
       </c>
       <c r="B111" t="n">
-        <v>19.295709</v>
+        <v>30.005614</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>17.049916</v>
+        <v>24.498131</v>
       </c>
       <c r="B112" t="n">
-        <v>20.016904</v>
+        <v>31.019795</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>18.405629</v>
+        <v>26.404605</v>
       </c>
       <c r="B113" t="n">
-        <v>20.732239</v>
+        <v>32.025736</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>19.761342</v>
+        <v>28.311079</v>
       </c>
       <c r="B114" t="n">
-        <v>21.441714</v>
+        <v>33.023436</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>21.117055</v>
+        <v>30.217552</v>
       </c>
       <c r="B115" t="n">
-        <v>22.14533</v>
+        <v>34.012897</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>22.472768</v>
+        <v>32.124026</v>
       </c>
       <c r="B116" t="n">
-        <v>22.843086</v>
+        <v>34.994117</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>23.828481</v>
+        <v>34.0305</v>
       </c>
       <c r="B117" t="n">
-        <v>23.534982</v>
+        <v>35.967097</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>25.184194</v>
+        <v>35.936973</v>
       </c>
       <c r="B118" t="n">
-        <v>24.221019</v>
+        <v>36.931837</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>26.539908</v>
+        <v>37.843447</v>
       </c>
       <c r="B119" t="n">
-        <v>24.901195</v>
+        <v>37.888337</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>27.895621</v>
+        <v>39.749921</v>
       </c>
       <c r="B120" t="n">
-        <v>25.575513</v>
+        <v>38.836597</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>29.251334</v>
+        <v>41.656394</v>
       </c>
       <c r="B121" t="n">
-        <v>26.24397</v>
+        <v>39.776616</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>30.607047</v>
+        <v>43.562868</v>
       </c>
       <c r="B122" t="n">
-        <v>26.906568</v>
+        <v>40.708395</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>31.96276</v>
+        <v>45.469342</v>
       </c>
       <c r="B123" t="n">
-        <v>27.563306</v>
+        <v>41.631934</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>33.318473</v>
+        <v>47.375815</v>
       </c>
       <c r="B124" t="n">
-        <v>28.214185</v>
+        <v>42.547233</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>34.674186</v>
+        <v>49.282289</v>
       </c>
       <c r="B125" t="n">
-        <v>28.859203</v>
+        <v>43.454292</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>36.029899</v>
+        <v>51.188763</v>
       </c>
       <c r="B126" t="n">
-        <v>29.498363</v>
+        <v>44.35311</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>37.385613</v>
+        <v>53.095236</v>
       </c>
       <c r="B127" t="n">
-        <v>30.131662</v>
+        <v>45.243689</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>38.741326</v>
+        <v>55.00171</v>
       </c>
       <c r="B128" t="n">
-        <v>30.759102</v>
+        <v>46.126027</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>40.097039</v>
+        <v>56.908184</v>
       </c>
       <c r="B129" t="n">
-        <v>31.380682</v>
+        <v>47.000124</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>41.452752</v>
+        <v>58.814657</v>
       </c>
       <c r="B130" t="n">
-        <v>31.996402</v>
+        <v>47.865982</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>42.808465</v>
+        <v>60.721131</v>
       </c>
       <c r="B131" t="n">
-        <v>32.606263</v>
+        <v>48.7236</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>44.164178</v>
+        <v>62.627605</v>
       </c>
       <c r="B132" t="n">
-        <v>33.210264</v>
+        <v>49.572977</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>45.519891</v>
+        <v>64.53407799999999</v>
       </c>
       <c r="B133" t="n">
-        <v>33.808405</v>
+        <v>50.414114</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>46.875605</v>
+        <v>66.440552</v>
       </c>
       <c r="B134" t="n">
-        <v>34.400687</v>
+        <v>51.247011</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>48.231318</v>
+        <v>68.347026</v>
       </c>
       <c r="B135" t="n">
-        <v>34.987109</v>
+        <v>52.071668</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>49.587031</v>
+        <v>70.25349900000001</v>
       </c>
       <c r="B136" t="n">
-        <v>35.567671</v>
+        <v>52.888084</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>50.942744</v>
+        <v>72.15997299999999</v>
       </c>
       <c r="B137" t="n">
-        <v>36.142374</v>
+        <v>53.696261</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>52.298457</v>
+        <v>74.066446</v>
       </c>
       <c r="B138" t="n">
-        <v>36.711216</v>
+        <v>54.496197</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>53.65417</v>
+        <v>75.97292</v>
       </c>
       <c r="B139" t="n">
-        <v>37.2742</v>
+        <v>55.287893</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>55.009883</v>
+        <v>77.879394</v>
       </c>
       <c r="B140" t="n">
-        <v>37.831323</v>
+        <v>56.071349</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>56.365597</v>
+        <v>79.785867</v>
       </c>
       <c r="B141" t="n">
-        <v>38.382587</v>
+        <v>56.846564</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>57.72131</v>
+        <v>81.692341</v>
       </c>
       <c r="B142" t="n">
-        <v>38.927991</v>
+        <v>57.61354</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>59.077023</v>
+        <v>83.598815</v>
       </c>
       <c r="B143" t="n">
-        <v>39.467536</v>
+        <v>58.372275</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>60.432736</v>
+        <v>85.50528799999999</v>
       </c>
       <c r="B144" t="n">
-        <v>40.00122</v>
+        <v>59.12277</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>61.788449</v>
+        <v>87.411762</v>
       </c>
       <c r="B145" t="n">
-        <v>40.529046</v>
+        <v>59.865025</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>63.144162</v>
+        <v>89.318236</v>
       </c>
       <c r="B146" t="n">
-        <v>41.051011</v>
+        <v>60.59904</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>64.499875</v>
+        <v>91.224709</v>
       </c>
       <c r="B147" t="n">
-        <v>41.567117</v>
+        <v>61.324814</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>65.85558899999999</v>
+        <v>93.13118299999999</v>
       </c>
       <c r="B148" t="n">
-        <v>42.077363</v>
+        <v>62.042349</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>67.211302</v>
+        <v>95.037657</v>
       </c>
       <c r="B149" t="n">
-        <v>42.581749</v>
+        <v>62.751643</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>68.567015</v>
+        <v>96.94413</v>
       </c>
       <c r="B150" t="n">
-        <v>43.080276</v>
+        <v>63.452697</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>69.92272800000001</v>
+        <v>98.850604</v>
       </c>
       <c r="B151" t="n">
-        <v>43.572943</v>
+        <v>64.14551</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>71.278441</v>
+        <v>100.757078</v>
       </c>
       <c r="B152" t="n">
-        <v>44.05975</v>
+        <v>64.830084</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>72.634154</v>
+        <v>102.663551</v>
       </c>
       <c r="B153" t="n">
-        <v>44.540698</v>
+        <v>65.506417</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>73.989867</v>
+        <v>104.570025</v>
       </c>
       <c r="B154" t="n">
-        <v>45.015786</v>
+        <v>66.17451</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>75.34558</v>
+        <v>106.476499</v>
       </c>
       <c r="B155" t="n">
-        <v>45.485014</v>
+        <v>66.834363</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>76.701294</v>
+        <v>108.382972</v>
       </c>
       <c r="B156" t="n">
-        <v>45.948383</v>
+        <v>67.48597599999999</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>78.057007</v>
+        <v>110.289446</v>
       </c>
       <c r="B157" t="n">
-        <v>46.405892</v>
+        <v>68.129349</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>79.41271999999999</v>
+        <v>112.19592</v>
       </c>
       <c r="B158" t="n">
-        <v>46.857541</v>
+        <v>68.764481</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>80.768433</v>
+        <v>114.102393</v>
       </c>
       <c r="B159" t="n">
-        <v>47.30333</v>
+        <v>69.391373</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>82.124146</v>
+        <v>116.008867</v>
       </c>
       <c r="B160" t="n">
-        <v>47.74326</v>
+        <v>70.010025</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>83.479859</v>
+        <v>117.915341</v>
       </c>
       <c r="B161" t="n">
-        <v>48.177331</v>
+        <v>70.620437</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>84.835572</v>
+        <v>119.821814</v>
       </c>
       <c r="B162" t="n">
-        <v>48.605541</v>
+        <v>71.22260900000001</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>86.19128600000001</v>
+        <v>121.728288</v>
       </c>
       <c r="B163" t="n">
-        <v>49.027892</v>
+        <v>71.81654</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>87.546999</v>
+        <v>123.634761</v>
       </c>
       <c r="B164" t="n">
-        <v>49.444383</v>
+        <v>72.402232</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>88.90271199999999</v>
+        <v>125.541235</v>
       </c>
       <c r="B165" t="n">
-        <v>49.855014</v>
+        <v>72.97968299999999</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>90.258425</v>
+        <v>127.447709</v>
       </c>
       <c r="B166" t="n">
-        <v>50.259786</v>
+        <v>73.548894</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>91.614138</v>
+        <v>129.354182</v>
       </c>
       <c r="B167" t="n">
-        <v>50.658698</v>
+        <v>74.109864</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>92.96985100000001</v>
+        <v>131.260656</v>
       </c>
       <c r="B168" t="n">
-        <v>51.051751</v>
+        <v>74.662595</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>94.325564</v>
+        <v>133.16713</v>
       </c>
       <c r="B169" t="n">
-        <v>51.438943</v>
+        <v>75.20708500000001</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>95.68127800000001</v>
+        <v>135.073603</v>
       </c>
       <c r="B170" t="n">
-        <v>51.820276</v>
+        <v>75.743335</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>97.036991</v>
+        <v>136.980077</v>
       </c>
       <c r="B171" t="n">
-        <v>52.19575</v>
+        <v>76.271345</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>98.39270399999999</v>
+        <v>138.886551</v>
       </c>
       <c r="B172" t="n">
-        <v>52.565363</v>
+        <v>76.791115</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>99.748417</v>
+        <v>140.793024</v>
       </c>
       <c r="B173" t="n">
-        <v>52.929117</v>
+        <v>77.302645</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>101.10413</v>
+        <v>142.699498</v>
       </c>
       <c r="B174" t="n">
-        <v>53.287012</v>
+        <v>77.80593399999999</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>102.459843</v>
+        <v>144.605972</v>
       </c>
       <c r="B175" t="n">
-        <v>53.639046</v>
+        <v>78.300983</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>103.815556</v>
+        <v>146.512445</v>
       </c>
       <c r="B176" t="n">
-        <v>53.985221</v>
+        <v>78.787792</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>105.171269</v>
+        <v>148.418919</v>
       </c>
       <c r="B177" t="n">
-        <v>54.325536</v>
+        <v>79.266361</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>106.526983</v>
+        <v>150.325393</v>
       </c>
       <c r="B178" t="n">
-        <v>54.659992</v>
+        <v>79.73669</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>107.882696</v>
+        <v>152.231866</v>
       </c>
       <c r="B179" t="n">
-        <v>54.988588</v>
+        <v>80.198778</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>109.238409</v>
+        <v>154.13834</v>
       </c>
       <c r="B180" t="n">
-        <v>55.311324</v>
+        <v>80.652627</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>110.594122</v>
+        <v>156.044814</v>
       </c>
       <c r="B181" t="n">
-        <v>55.628201</v>
+        <v>81.098235</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>111.949835</v>
+        <v>157.951287</v>
       </c>
       <c r="B182" t="n">
-        <v>55.939217</v>
+        <v>81.53560299999999</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>113.305548</v>
+        <v>159.857761</v>
       </c>
       <c r="B183" t="n">
-        <v>56.244375</v>
+        <v>81.96473</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>114.661261</v>
+        <v>161.764235</v>
       </c>
       <c r="B184" t="n">
-        <v>56.543672</v>
+        <v>82.38561799999999</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>116.016975</v>
+        <v>163.670708</v>
       </c>
       <c r="B185" t="n">
-        <v>56.83711</v>
+        <v>82.798265</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>117.372688</v>
+        <v>165.577182</v>
       </c>
       <c r="B186" t="n">
-        <v>57.124688</v>
+        <v>83.20267200000001</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118.728401</v>
+        <v>167.483656</v>
       </c>
       <c r="B187" t="n">
-        <v>57.406406</v>
+        <v>83.598839</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120.084114</v>
+        <v>169.390129</v>
       </c>
       <c r="B188" t="n">
-        <v>57.682265</v>
+        <v>83.986766</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121.439827</v>
+        <v>171.296603</v>
       </c>
       <c r="B189" t="n">
-        <v>57.952264</v>
+        <v>84.366452</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122.79554</v>
+        <v>173.203076</v>
       </c>
       <c r="B190" t="n">
-        <v>58.216403</v>
+        <v>84.737899</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124.151253</v>
+        <v>175.10955</v>
       </c>
       <c r="B191" t="n">
-        <v>58.474683</v>
+        <v>85.101105</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125.506967</v>
+        <v>177.016024</v>
       </c>
       <c r="B192" t="n">
-        <v>58.727103</v>
+        <v>85.45607099999999</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126.86268</v>
+        <v>178.922497</v>
       </c>
       <c r="B193" t="n">
-        <v>58.973663</v>
+        <v>85.802797</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128.218393</v>
+        <v>180.828971</v>
       </c>
       <c r="B194" t="n">
-        <v>59.214364</v>
+        <v>86.141282</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129.574106</v>
+        <v>182.735445</v>
       </c>
       <c r="B195" t="n">
-        <v>59.449205</v>
+        <v>86.47152800000001</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130.929819</v>
+        <v>184.641918</v>
       </c>
       <c r="B196" t="n">
-        <v>59.678186</v>
+        <v>86.793533</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>132.285532</v>
+        <v>186.548392</v>
       </c>
       <c r="B197" t="n">
-        <v>59.901308</v>
+        <v>87.107298</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133.641245</v>
+        <v>188.454866</v>
       </c>
       <c r="B198" t="n">
-        <v>60.11857</v>
+        <v>87.412823</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134.996959</v>
+        <v>190.361339</v>
       </c>
       <c r="B199" t="n">
-        <v>60.329972</v>
+        <v>87.71010800000001</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>136.352672</v>
+        <v>192.267813</v>
       </c>
       <c r="B200" t="n">
-        <v>60.535515</v>
+        <v>87.999152</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>

--- a/Bell_Nozzle_Divergent_Profile.xlsx
+++ b/Bell_Nozzle_Divergent_Profile.xlsx
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.037307</v>
+        <v>0.146492</v>
       </c>
       <c r="B3" t="n">
-        <v>18.465655</v>
+        <v>18.465944</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.074612</v>
+        <v>0.292981</v>
       </c>
       <c r="B4" t="n">
-        <v>18.465951</v>
+        <v>18.467106</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.111916</v>
+        <v>0.439461</v>
       </c>
       <c r="B5" t="n">
-        <v>18.466444</v>
+        <v>18.469043</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.149216</v>
+        <v>0.585929</v>
       </c>
       <c r="B6" t="n">
-        <v>18.467135</v>
+        <v>18.471755</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.186513</v>
+        <v>0.73238</v>
       </c>
       <c r="B7" t="n">
-        <v>18.468023</v>
+        <v>18.475241</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.223804</v>
+        <v>0.878811</v>
       </c>
       <c r="B8" t="n">
-        <v>18.469108</v>
+        <v>18.479502</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.261089</v>
+        <v>1.025217</v>
       </c>
       <c r="B9" t="n">
-        <v>18.47039</v>
+        <v>18.484537</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.298366</v>
+        <v>1.171595</v>
       </c>
       <c r="B10" t="n">
-        <v>18.47187</v>
+        <v>18.490346</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.335635</v>
+        <v>1.31794</v>
       </c>
       <c r="B11" t="n">
-        <v>18.473546</v>
+        <v>18.496929</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.372895</v>
+        <v>1.464248</v>
       </c>
       <c r="B12" t="n">
-        <v>18.47542</v>
+        <v>18.504287</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.410144</v>
+        <v>1.610515</v>
       </c>
       <c r="B13" t="n">
-        <v>18.477491</v>
+        <v>18.512418</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.447382</v>
+        <v>1.756737</v>
       </c>
       <c r="B14" t="n">
-        <v>18.479758</v>
+        <v>18.521322</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.484608</v>
+        <v>1.90291</v>
       </c>
       <c r="B15" t="n">
-        <v>18.482223</v>
+        <v>18.531</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.52182</v>
+        <v>2.04903</v>
       </c>
       <c r="B16" t="n">
-        <v>18.484884</v>
+        <v>18.541451</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.559017</v>
+        <v>2.195092</v>
       </c>
       <c r="B17" t="n">
-        <v>18.487743</v>
+        <v>18.552674</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.596198</v>
+        <v>2.341093</v>
       </c>
       <c r="B18" t="n">
-        <v>18.490797</v>
+        <v>18.56467</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.633363</v>
+        <v>2.487028</v>
       </c>
       <c r="B19" t="n">
-        <v>18.494049</v>
+        <v>18.577437</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6705100000000001</v>
+        <v>2.632894</v>
       </c>
       <c r="B20" t="n">
-        <v>18.497497</v>
+        <v>18.590977</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.707639</v>
+        <v>2.778686</v>
       </c>
       <c r="B21" t="n">
-        <v>18.501141</v>
+        <v>18.605287</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.744747</v>
+        <v>2.924401</v>
       </c>
       <c r="B22" t="n">
-        <v>18.504982</v>
+        <v>18.620369</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.7818349999999999</v>
+        <v>3.070034</v>
       </c>
       <c r="B23" t="n">
-        <v>18.509019</v>
+        <v>18.636221</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.818901</v>
+        <v>3.21558</v>
       </c>
       <c r="B24" t="n">
-        <v>18.513252</v>
+        <v>18.652843</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.855944</v>
+        <v>3.361037</v>
       </c>
       <c r="B25" t="n">
-        <v>18.517681</v>
+        <v>18.670234</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.892963</v>
+        <v>3.5064</v>
       </c>
       <c r="B26" t="n">
-        <v>18.522306</v>
+        <v>18.688395</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.929957</v>
+        <v>3.651665</v>
       </c>
       <c r="B27" t="n">
-        <v>18.527127</v>
+        <v>18.707324</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.966925</v>
+        <v>3.796828</v>
       </c>
       <c r="B28" t="n">
-        <v>18.532143</v>
+        <v>18.727021</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.003866</v>
+        <v>3.941884</v>
       </c>
       <c r="B29" t="n">
-        <v>18.537355</v>
+        <v>18.747486</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1.040779</v>
+        <v>4.08683</v>
       </c>
       <c r="B30" t="n">
-        <v>18.542761</v>
+        <v>18.768717</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1.077663</v>
+        <v>4.231662</v>
       </c>
       <c r="B31" t="n">
-        <v>18.548364</v>
+        <v>18.790715</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1.114517</v>
+        <v>4.376376</v>
       </c>
       <c r="B32" t="n">
-        <v>18.554161</v>
+        <v>18.813478</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.15134</v>
+        <v>4.520967</v>
       </c>
       <c r="B33" t="n">
-        <v>18.560153</v>
+        <v>18.837007</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1.18813</v>
+        <v>4.665431</v>
       </c>
       <c r="B34" t="n">
-        <v>18.566339</v>
+        <v>18.8613</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.224887</v>
+        <v>4.809765</v>
       </c>
       <c r="B35" t="n">
-        <v>18.57272</v>
+        <v>18.886357</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.26161</v>
+        <v>4.953965</v>
       </c>
       <c r="B36" t="n">
-        <v>18.579296</v>
+        <v>18.912176</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.298297</v>
+        <v>5.098026</v>
       </c>
       <c r="B37" t="n">
-        <v>18.586065</v>
+        <v>18.938758</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.334948</v>
+        <v>5.241944</v>
       </c>
       <c r="B38" t="n">
-        <v>18.593029</v>
+        <v>18.966102</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.371562</v>
+        <v>5.385716</v>
       </c>
       <c r="B39" t="n">
-        <v>18.600186</v>
+        <v>18.994206</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1.408138</v>
+        <v>5.529337</v>
       </c>
       <c r="B40" t="n">
-        <v>18.607537</v>
+        <v>19.02307</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1.444674</v>
+        <v>5.672804</v>
       </c>
       <c r="B41" t="n">
-        <v>18.615081</v>
+        <v>19.052694</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1.48117</v>
+        <v>5.816111</v>
       </c>
       <c r="B42" t="n">
-        <v>18.622818</v>
+        <v>19.083075</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1.517624</v>
+        <v>5.959257</v>
       </c>
       <c r="B43" t="n">
-        <v>18.630748</v>
+        <v>19.114215</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1.554036</v>
+        <v>6.102235</v>
       </c>
       <c r="B44" t="n">
-        <v>18.638871</v>
+        <v>19.146111</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1.590404</v>
+        <v>6.245043</v>
       </c>
       <c r="B45" t="n">
-        <v>18.647186</v>
+        <v>19.178762</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1.626728</v>
+        <v>6.387676</v>
       </c>
       <c r="B46" t="n">
-        <v>18.655694</v>
+        <v>19.212169</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.663006</v>
+        <v>6.53013</v>
       </c>
       <c r="B47" t="n">
-        <v>18.664393</v>
+        <v>19.246329</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1.699238</v>
+        <v>6.672402</v>
       </c>
       <c r="B48" t="n">
-        <v>18.673285</v>
+        <v>19.281243</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1.735423</v>
+        <v>6.814487</v>
       </c>
       <c r="B49" t="n">
-        <v>18.682367</v>
+        <v>19.316908</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.771558</v>
+        <v>6.956381</v>
       </c>
       <c r="B50" t="n">
-        <v>18.691641</v>
+        <v>19.353324</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.807645</v>
+        <v>7.098081</v>
       </c>
       <c r="B51" t="n">
-        <v>18.701106</v>
+        <v>19.39049</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.84368</v>
+        <v>7.239582</v>
       </c>
       <c r="B52" t="n">
-        <v>18.710762</v>
+        <v>19.428406</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.879664</v>
+        <v>7.380881</v>
       </c>
       <c r="B53" t="n">
-        <v>18.720608</v>
+        <v>19.467069</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.915596</v>
+        <v>7.521973</v>
       </c>
       <c r="B54" t="n">
-        <v>18.730645</v>
+        <v>19.506478</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.951474</v>
+        <v>7.662855</v>
       </c>
       <c r="B55" t="n">
-        <v>18.740871</v>
+        <v>19.546634</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.987297</v>
+        <v>7.803523</v>
       </c>
       <c r="B56" t="n">
-        <v>18.751287</v>
+        <v>19.587534</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2.023065</v>
+        <v>7.943972</v>
       </c>
       <c r="B57" t="n">
-        <v>18.761892</v>
+        <v>19.629177</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2.058776</v>
+        <v>8.084199</v>
       </c>
       <c r="B58" t="n">
-        <v>18.772686</v>
+        <v>19.671563</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2.09443</v>
+        <v>8.2242</v>
       </c>
       <c r="B59" t="n">
-        <v>18.783669</v>
+        <v>19.714689</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2.130025</v>
+        <v>8.363970999999999</v>
       </c>
       <c r="B60" t="n">
-        <v>18.79484</v>
+        <v>19.758556</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2.16556</v>
+        <v>8.503508</v>
       </c>
       <c r="B61" t="n">
-        <v>18.8062</v>
+        <v>19.803161</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2.201035</v>
+        <v>8.642806999999999</v>
       </c>
       <c r="B62" t="n">
-        <v>18.817747</v>
+        <v>19.848503</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2.236448</v>
+        <v>8.781864000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>18.829482</v>
+        <v>19.894582</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2.271799</v>
+        <v>8.920676</v>
       </c>
       <c r="B64" t="n">
-        <v>18.841404</v>
+        <v>19.941395</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2.307086</v>
+        <v>9.059238000000001</v>
       </c>
       <c r="B65" t="n">
-        <v>18.853512</v>
+        <v>19.988942</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2.342309</v>
+        <v>9.197547</v>
       </c>
       <c r="B66" t="n">
-        <v>18.865807</v>
+        <v>20.037221</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2.377466</v>
+        <v>9.335597999999999</v>
       </c>
       <c r="B67" t="n">
-        <v>18.878288</v>
+        <v>20.086231</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2.412556</v>
+        <v>9.473388</v>
       </c>
       <c r="B68" t="n">
-        <v>18.890955</v>
+        <v>20.135971</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2.447579</v>
+        <v>9.610913999999999</v>
       </c>
       <c r="B69" t="n">
-        <v>18.903808</v>
+        <v>20.186438</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2.482534</v>
+        <v>9.74817</v>
       </c>
       <c r="B70" t="n">
-        <v>18.916845</v>
+        <v>20.237632</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2.517419</v>
+        <v>9.885154</v>
       </c>
       <c r="B71" t="n">
-        <v>18.930067</v>
+        <v>20.289551</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2.552234</v>
+        <v>10.021861</v>
       </c>
       <c r="B72" t="n">
-        <v>18.943474</v>
+        <v>20.342194</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2.586977</v>
+        <v>10.158288</v>
       </c>
       <c r="B73" t="n">
-        <v>18.957064</v>
+        <v>20.395559</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2.621648</v>
+        <v>10.294431</v>
       </c>
       <c r="B74" t="n">
-        <v>18.970838</v>
+        <v>20.449646</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2.656246</v>
+        <v>10.430286</v>
       </c>
       <c r="B75" t="n">
-        <v>18.984795</v>
+        <v>20.504451</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2.69077</v>
+        <v>10.565849</v>
       </c>
       <c r="B76" t="n">
-        <v>18.998935</v>
+        <v>20.559974</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2.725218</v>
+        <v>10.701117</v>
       </c>
       <c r="B77" t="n">
-        <v>19.013257</v>
+        <v>20.616213</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2.75959</v>
+        <v>10.836085</v>
       </c>
       <c r="B78" t="n">
-        <v>19.027761</v>
+        <v>20.673167</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2.793884</v>
+        <v>10.97075</v>
       </c>
       <c r="B79" t="n">
-        <v>19.042447</v>
+        <v>20.730834</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2.828101</v>
+        <v>11.105108</v>
       </c>
       <c r="B80" t="n">
-        <v>19.057314</v>
+        <v>20.789213</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2.862238</v>
+        <v>11.239156</v>
       </c>
       <c r="B81" t="n">
-        <v>19.072362</v>
+        <v>20.848301</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2.896296</v>
+        <v>11.372889</v>
       </c>
       <c r="B82" t="n">
-        <v>19.08759</v>
+        <v>20.908097</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2.930272</v>
+        <v>11.506304</v>
       </c>
       <c r="B83" t="n">
-        <v>19.102998</v>
+        <v>20.9686</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2.964167</v>
+        <v>11.639397</v>
       </c>
       <c r="B84" t="n">
-        <v>19.118586</v>
+        <v>21.029807</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2.997978</v>
+        <v>11.772165</v>
       </c>
       <c r="B85" t="n">
-        <v>19.134352</v>
+        <v>21.091718</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>3.031706</v>
+        <v>11.904603</v>
       </c>
       <c r="B86" t="n">
-        <v>19.150298</v>
+        <v>21.15433</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>3.065349</v>
+        <v>12.036709</v>
       </c>
       <c r="B87" t="n">
-        <v>19.166421</v>
+        <v>21.217641</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3.098906</v>
+        <v>12.168477</v>
       </c>
       <c r="B88" t="n">
-        <v>19.182722</v>
+        <v>21.281651</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>3.132376</v>
+        <v>12.299906</v>
       </c>
       <c r="B89" t="n">
-        <v>19.1992</v>
+        <v>21.346356</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3.165759</v>
+        <v>12.43099</v>
       </c>
       <c r="B90" t="n">
-        <v>19.215855</v>
+        <v>21.411755</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3.199053</v>
+        <v>12.561727</v>
       </c>
       <c r="B91" t="n">
-        <v>19.232687</v>
+        <v>21.477847</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>3.232258</v>
+        <v>12.692112</v>
       </c>
       <c r="B92" t="n">
-        <v>19.249694</v>
+        <v>21.54463</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>3.265372</v>
+        <v>12.822142</v>
       </c>
       <c r="B93" t="n">
-        <v>19.266876</v>
+        <v>21.612101</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>3.298395</v>
+        <v>12.951813</v>
       </c>
       <c r="B94" t="n">
-        <v>19.284234</v>
+        <v>21.680258</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>3.331326</v>
+        <v>13.081122</v>
       </c>
       <c r="B95" t="n">
-        <v>19.301766</v>
+        <v>21.749101</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>3.364163</v>
+        <v>13.210066</v>
       </c>
       <c r="B96" t="n">
-        <v>19.319472</v>
+        <v>21.818627</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>3.396907</v>
+        <v>13.338639</v>
       </c>
       <c r="B97" t="n">
-        <v>19.337351</v>
+        <v>21.888833</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3.429555</v>
+        <v>13.46684</v>
       </c>
       <c r="B98" t="n">
-        <v>19.355403</v>
+        <v>21.959719</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3.462108</v>
+        <v>13.594664</v>
       </c>
       <c r="B99" t="n">
-        <v>19.373628</v>
+        <v>22.031281</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>3.494563</v>
+        <v>13.722108</v>
       </c>
       <c r="B100" t="n">
-        <v>19.392024</v>
+        <v>22.103519</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3.526921</v>
+        <v>13.849167</v>
       </c>
       <c r="B101" t="n">
-        <v>19.410592</v>
+        <v>22.17643</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>5.433395</v>
+        <v>15.651376</v>
       </c>
       <c r="B102" t="n">
-        <v>20.507175</v>
+        <v>23.213041</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>7.339869</v>
+        <v>17.453585</v>
       </c>
       <c r="B103" t="n">
-        <v>21.595518</v>
+        <v>24.241862</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>9.246342</v>
+        <v>19.255793</v>
       </c>
       <c r="B104" t="n">
-        <v>22.675621</v>
+        <v>25.262894</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>11.152816</v>
+        <v>21.058002</v>
       </c>
       <c r="B105" t="n">
-        <v>23.747483</v>
+        <v>26.276136</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>13.05929</v>
+        <v>22.86021</v>
       </c>
       <c r="B106" t="n">
-        <v>24.811105</v>
+        <v>27.281589</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>14.965763</v>
+        <v>24.662419</v>
       </c>
       <c r="B107" t="n">
-        <v>25.866487</v>
+        <v>28.279252</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>16.872237</v>
+        <v>26.464627</v>
       </c>
       <c r="B108" t="n">
-        <v>26.913629</v>
+        <v>29.269125</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>18.778711</v>
+        <v>28.266836</v>
       </c>
       <c r="B109" t="n">
-        <v>27.952531</v>
+        <v>30.251209</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>20.685184</v>
+        <v>30.069044</v>
       </c>
       <c r="B110" t="n">
-        <v>28.983192</v>
+        <v>31.225504</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>22.591658</v>
+        <v>31.871253</v>
       </c>
       <c r="B111" t="n">
-        <v>30.005614</v>
+        <v>32.192009</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>24.498131</v>
+        <v>33.673461</v>
       </c>
       <c r="B112" t="n">
-        <v>31.019795</v>
+        <v>33.150725</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>26.404605</v>
+        <v>35.47567</v>
       </c>
       <c r="B113" t="n">
-        <v>32.025736</v>
+        <v>34.101651</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>28.311079</v>
+        <v>37.277878</v>
       </c>
       <c r="B114" t="n">
-        <v>33.023436</v>
+        <v>35.044787</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>30.217552</v>
+        <v>39.080087</v>
       </c>
       <c r="B115" t="n">
-        <v>34.012897</v>
+        <v>35.980134</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>32.124026</v>
+        <v>40.882296</v>
       </c>
       <c r="B116" t="n">
-        <v>34.994117</v>
+        <v>36.907691</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>34.0305</v>
+        <v>42.684504</v>
       </c>
       <c r="B117" t="n">
-        <v>35.967097</v>
+        <v>37.827459</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>35.936973</v>
+        <v>44.486713</v>
       </c>
       <c r="B118" t="n">
-        <v>36.931837</v>
+        <v>38.739437</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>37.843447</v>
+        <v>46.288921</v>
       </c>
       <c r="B119" t="n">
-        <v>37.888337</v>
+        <v>39.643626</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>39.749921</v>
+        <v>48.09113</v>
       </c>
       <c r="B120" t="n">
-        <v>38.836597</v>
+        <v>40.540025</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>41.656394</v>
+        <v>49.893338</v>
       </c>
       <c r="B121" t="n">
-        <v>39.776616</v>
+        <v>41.428635</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>43.562868</v>
+        <v>51.695547</v>
       </c>
       <c r="B122" t="n">
-        <v>40.708395</v>
+        <v>42.309455</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>45.469342</v>
+        <v>53.497755</v>
       </c>
       <c r="B123" t="n">
-        <v>41.631934</v>
+        <v>43.182486</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>47.375815</v>
+        <v>55.299964</v>
       </c>
       <c r="B124" t="n">
-        <v>42.547233</v>
+        <v>44.047727</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>49.282289</v>
+        <v>57.102172</v>
       </c>
       <c r="B125" t="n">
-        <v>43.454292</v>
+        <v>44.905179</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>51.188763</v>
+        <v>58.904381</v>
       </c>
       <c r="B126" t="n">
-        <v>44.35311</v>
+        <v>45.754841</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>53.095236</v>
+        <v>60.70659</v>
       </c>
       <c r="B127" t="n">
-        <v>45.243689</v>
+        <v>46.596713</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>55.00171</v>
+        <v>62.508798</v>
       </c>
       <c r="B128" t="n">
-        <v>46.126027</v>
+        <v>47.430796</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>56.908184</v>
+        <v>64.311007</v>
       </c>
       <c r="B129" t="n">
-        <v>47.000124</v>
+        <v>48.25709</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>58.814657</v>
+        <v>66.113215</v>
       </c>
       <c r="B130" t="n">
-        <v>47.865982</v>
+        <v>49.075593</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>60.721131</v>
+        <v>67.915424</v>
       </c>
       <c r="B131" t="n">
-        <v>48.7236</v>
+        <v>49.886308</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>62.627605</v>
+        <v>69.71763199999999</v>
       </c>
       <c r="B132" t="n">
-        <v>49.572977</v>
+        <v>50.689233</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>64.53407799999999</v>
+        <v>71.519841</v>
       </c>
       <c r="B133" t="n">
-        <v>50.414114</v>
+        <v>51.484368</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>66.440552</v>
+        <v>73.32204900000001</v>
       </c>
       <c r="B134" t="n">
-        <v>51.247011</v>
+        <v>52.271714</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>68.347026</v>
+        <v>75.124258</v>
       </c>
       <c r="B135" t="n">
-        <v>52.071668</v>
+        <v>53.05127</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>70.25349900000001</v>
+        <v>76.926466</v>
       </c>
       <c r="B136" t="n">
-        <v>52.888084</v>
+        <v>53.823037</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>72.15997299999999</v>
+        <v>78.728675</v>
       </c>
       <c r="B137" t="n">
-        <v>53.696261</v>
+        <v>54.587014</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>74.066446</v>
+        <v>80.530883</v>
       </c>
       <c r="B138" t="n">
-        <v>54.496197</v>
+        <v>55.343202</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>75.97292</v>
+        <v>82.33309199999999</v>
       </c>
       <c r="B139" t="n">
-        <v>55.287893</v>
+        <v>56.0916</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>77.879394</v>
+        <v>84.135301</v>
       </c>
       <c r="B140" t="n">
-        <v>56.071349</v>
+        <v>56.832208</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>79.785867</v>
+        <v>85.93750900000001</v>
       </c>
       <c r="B141" t="n">
-        <v>56.846564</v>
+        <v>57.565027</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>81.692341</v>
+        <v>87.739718</v>
       </c>
       <c r="B142" t="n">
-        <v>57.61354</v>
+        <v>58.290057</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>83.598815</v>
+        <v>89.541926</v>
       </c>
       <c r="B143" t="n">
-        <v>58.372275</v>
+        <v>59.007297</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>85.50528799999999</v>
+        <v>91.34413499999999</v>
       </c>
       <c r="B144" t="n">
-        <v>59.12277</v>
+        <v>59.716747</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>87.411762</v>
+        <v>93.146343</v>
       </c>
       <c r="B145" t="n">
-        <v>59.865025</v>
+        <v>60.418408</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>89.318236</v>
+        <v>94.94855200000001</v>
       </c>
       <c r="B146" t="n">
-        <v>60.59904</v>
+        <v>61.11228</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>91.224709</v>
+        <v>96.75076</v>
       </c>
       <c r="B147" t="n">
-        <v>61.324814</v>
+        <v>61.798361</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>93.13118299999999</v>
+        <v>98.552969</v>
       </c>
       <c r="B148" t="n">
-        <v>62.042349</v>
+        <v>62.476654</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>95.037657</v>
+        <v>100.355177</v>
       </c>
       <c r="B149" t="n">
-        <v>62.751643</v>
+        <v>63.147157</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>96.94413</v>
+        <v>102.157386</v>
       </c>
       <c r="B150" t="n">
-        <v>63.452697</v>
+        <v>63.80987</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>98.850604</v>
+        <v>103.959594</v>
       </c>
       <c r="B151" t="n">
-        <v>64.14551</v>
+        <v>64.464794</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>100.757078</v>
+        <v>105.761803</v>
       </c>
       <c r="B152" t="n">
-        <v>64.830084</v>
+        <v>65.11192800000001</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>102.663551</v>
+        <v>107.564012</v>
       </c>
       <c r="B153" t="n">
-        <v>65.506417</v>
+        <v>65.751272</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>104.570025</v>
+        <v>109.36622</v>
       </c>
       <c r="B154" t="n">
-        <v>66.17451</v>
+        <v>66.382828</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>106.476499</v>
+        <v>111.168429</v>
       </c>
       <c r="B155" t="n">
-        <v>66.834363</v>
+        <v>67.006593</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>108.382972</v>
+        <v>112.970637</v>
       </c>
       <c r="B156" t="n">
-        <v>67.48597599999999</v>
+        <v>67.622569</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>110.289446</v>
+        <v>114.772846</v>
       </c>
       <c r="B157" t="n">
-        <v>68.129349</v>
+        <v>68.230756</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>112.19592</v>
+        <v>116.575054</v>
       </c>
       <c r="B158" t="n">
-        <v>68.764481</v>
+        <v>68.831153</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>114.102393</v>
+        <v>118.377263</v>
       </c>
       <c r="B159" t="n">
-        <v>69.391373</v>
+        <v>69.42376</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>116.008867</v>
+        <v>120.179471</v>
       </c>
       <c r="B160" t="n">
-        <v>70.010025</v>
+        <v>70.008578</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>117.915341</v>
+        <v>121.98168</v>
       </c>
       <c r="B161" t="n">
-        <v>70.620437</v>
+        <v>70.585607</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119.821814</v>
+        <v>123.783888</v>
       </c>
       <c r="B162" t="n">
-        <v>71.22260900000001</v>
+        <v>71.15484499999999</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121.728288</v>
+        <v>125.586097</v>
       </c>
       <c r="B163" t="n">
-        <v>71.81654</v>
+        <v>71.716295</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>123.634761</v>
+        <v>127.388306</v>
       </c>
       <c r="B164" t="n">
-        <v>72.402232</v>
+        <v>72.269955</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125.541235</v>
+        <v>129.190514</v>
       </c>
       <c r="B165" t="n">
-        <v>72.97968299999999</v>
+        <v>72.815825</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127.447709</v>
+        <v>130.992723</v>
       </c>
       <c r="B166" t="n">
-        <v>73.548894</v>
+        <v>73.35390599999999</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129.354182</v>
+        <v>132.794931</v>
       </c>
       <c r="B167" t="n">
-        <v>74.109864</v>
+        <v>73.884197</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131.260656</v>
+        <v>134.59714</v>
       </c>
       <c r="B168" t="n">
-        <v>74.662595</v>
+        <v>74.40669800000001</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133.16713</v>
+        <v>136.399348</v>
       </c>
       <c r="B169" t="n">
-        <v>75.20708500000001</v>
+        <v>74.92141100000001</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>135.073603</v>
+        <v>138.201557</v>
       </c>
       <c r="B170" t="n">
-        <v>75.743335</v>
+        <v>75.42833299999999</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>136.980077</v>
+        <v>140.003765</v>
       </c>
       <c r="B171" t="n">
-        <v>76.271345</v>
+        <v>75.927466</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>138.886551</v>
+        <v>141.805974</v>
       </c>
       <c r="B172" t="n">
-        <v>76.791115</v>
+        <v>76.41880999999999</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>140.793024</v>
+        <v>143.608182</v>
       </c>
       <c r="B173" t="n">
-        <v>77.302645</v>
+        <v>76.90236400000001</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>142.699498</v>
+        <v>145.410391</v>
       </c>
       <c r="B174" t="n">
-        <v>77.80593399999999</v>
+        <v>77.378128</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>144.605972</v>
+        <v>147.212599</v>
       </c>
       <c r="B175" t="n">
-        <v>78.300983</v>
+        <v>77.846103</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>146.512445</v>
+        <v>149.014808</v>
       </c>
       <c r="B176" t="n">
-        <v>78.787792</v>
+        <v>78.30628900000001</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>148.418919</v>
+        <v>150.817017</v>
       </c>
       <c r="B177" t="n">
-        <v>79.266361</v>
+        <v>78.758685</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>150.325393</v>
+        <v>152.619225</v>
       </c>
       <c r="B178" t="n">
-        <v>79.73669</v>
+        <v>79.20329099999999</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>152.231866</v>
+        <v>154.421434</v>
       </c>
       <c r="B179" t="n">
-        <v>80.198778</v>
+        <v>79.640108</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>154.13834</v>
+        <v>156.223642</v>
       </c>
       <c r="B180" t="n">
-        <v>80.652627</v>
+        <v>80.069135</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>156.044814</v>
+        <v>158.025851</v>
       </c>
       <c r="B181" t="n">
-        <v>81.098235</v>
+        <v>80.49037300000001</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>157.951287</v>
+        <v>159.828059</v>
       </c>
       <c r="B182" t="n">
-        <v>81.53560299999999</v>
+        <v>80.90382099999999</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>159.857761</v>
+        <v>161.630268</v>
       </c>
       <c r="B183" t="n">
-        <v>81.96473</v>
+        <v>81.30947999999999</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>161.764235</v>
+        <v>163.432476</v>
       </c>
       <c r="B184" t="n">
-        <v>82.38561799999999</v>
+        <v>81.70734899999999</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>163.670708</v>
+        <v>165.234685</v>
       </c>
       <c r="B185" t="n">
-        <v>82.798265</v>
+        <v>82.09742799999999</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>165.577182</v>
+        <v>167.036893</v>
       </c>
       <c r="B186" t="n">
-        <v>83.20267200000001</v>
+        <v>82.479719</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>167.483656</v>
+        <v>168.839102</v>
       </c>
       <c r="B187" t="n">
-        <v>83.598839</v>
+        <v>82.854219</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>169.390129</v>
+        <v>170.641311</v>
       </c>
       <c r="B188" t="n">
-        <v>83.986766</v>
+        <v>83.22093</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>171.296603</v>
+        <v>172.443519</v>
       </c>
       <c r="B189" t="n">
-        <v>84.366452</v>
+        <v>83.579852</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>173.203076</v>
+        <v>174.245728</v>
       </c>
       <c r="B190" t="n">
-        <v>84.737899</v>
+        <v>83.930984</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>175.10955</v>
+        <v>176.047936</v>
       </c>
       <c r="B191" t="n">
-        <v>85.101105</v>
+        <v>84.274326</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>177.016024</v>
+        <v>177.850145</v>
       </c>
       <c r="B192" t="n">
-        <v>85.45607099999999</v>
+        <v>84.60987900000001</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>178.922497</v>
+        <v>179.652353</v>
       </c>
       <c r="B193" t="n">
-        <v>85.802797</v>
+        <v>84.937642</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>180.828971</v>
+        <v>181.454562</v>
       </c>
       <c r="B194" t="n">
-        <v>86.141282</v>
+        <v>85.257616</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>182.735445</v>
+        <v>183.25677</v>
       </c>
       <c r="B195" t="n">
-        <v>86.47152800000001</v>
+        <v>85.5698</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>184.641918</v>
+        <v>185.058979</v>
       </c>
       <c r="B196" t="n">
-        <v>86.793533</v>
+        <v>85.874195</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>186.548392</v>
+        <v>186.861187</v>
       </c>
       <c r="B197" t="n">
-        <v>87.107298</v>
+        <v>86.1708</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>188.454866</v>
+        <v>188.663396</v>
       </c>
       <c r="B198" t="n">
-        <v>87.412823</v>
+        <v>86.459616</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>190.361339</v>
+        <v>190.465604</v>
       </c>
       <c r="B199" t="n">
-        <v>87.71010800000001</v>
+        <v>86.74064199999999</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2628,7 +2628,7 @@
         <v>192.267813</v>
       </c>
       <c r="B200" t="n">
-        <v>87.999152</v>
+        <v>87.013879</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
